--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -572,134 +572,151 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>モノクロ印刷で潰れる図がある</t>
+          <t>色はカラーで進める（令和8年10月10日の指示）</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>15点の図で、系列の色がモノクロにすると同じ濃さになる。緑 RGB(46,158,107) と 青 RGB(61,134,198) はどちらもグレー値119で完全に一致する。成果品①はモノクロ印刷（仕様書5）であるため、身体障害者手帳と精神障害者保健福祉手帳の棒を見分けられない</t>
+          <t>図は他メンバー版に合わせてカラーで作る。印刷については確認事項として残す（仕様書5の成果品①はモノクロ・コピー・くるみ製本であり、仕様と図の作りが食い違っている）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>02シート。確認Ｓ-20・Ｍ-69</t>
+          <t>07シート。確認Ｍ-69・Ｓ-20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>出所がほとんど付いていない</t>
+          <t>ただし白黒コピーで潰れる組がある</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>表109点のうち、直後に出所らしき行があるのは7点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>10点の図で、系列の色をグレーにすると同じ濃さになる。緑 RGB(46,158,107) と 青 RGB(61,134,198) はどちらもグレー値119で完全に一致する。カラーで印刷しても、計画書は窓口で白黒コピーされることがある。当方が作る図は、カラーのままでも同じ図の中の系列のグレー値を25以上離す（緑と青を並べて使わない）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03シート。規約は06シート</t>
+          <t>02シート</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>図は画像であり数値を直せない</t>
+          <t>出所がほとんど付いていない</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>他メンバー版の図19点はすべて画像として貼られている。村の実績（Ｍ-19ほか）が入ると数値が変わるため、ほとんどの図を作り直すことになる。元データと作図の道具を他メンバーと共有しておく必要がある</t>
+          <t>表109点のうち、直後に出所らしき行があるのは7点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>確認Ｓ-19</t>
+          <t>03シート。規約は06シート</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>当方が作った図3点</t>
+          <t>図は画像であり数値を直せない</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>給付費の推移・サービス別の給付費・高齢化率の推移を、はじめからモノクロで判別できる作りで入れた（build_kitashiobara_graph.py）。数値は申し送りの表と正本の表から読み込むため、表が直れば図も作り直せる。濃さの差は256階調で25以上、接する面には45度・135度の網かけを足している</t>
+          <t>他メンバー版の図19点はすべて画像として貼られている。村の実績（Ｍ-19ほか）が入ると数値が変わるため、ほとんどの図を作り直すことになる。元データと作図の道具を他メンバーと共有しておく必要がある</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04シート。図の作り直しの手本</t>
+          <t>確認Ｓ-19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>図表目次がない</t>
+          <t>当方が作った図3点</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>約60頁の計画書に図表が120点以上ある。本文の目次だけでは図表にたどり着けないため、目次の後に図表目次を置く</t>
+          <t>給付費の推移・サービス別の給付費・高齢化率の推移を、他メンバー版と同じ色（緑）で入れた（build_kitashiobara_graph.py）。数値は申し送りの表と正本の表から読み込むため、表が直れば図も作り直せる。いずれも1系列であり、色で見分ける必要がない。2系列以上になるときは、グレー値が25以上離れる組（緑と橙。差52）を使う</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>06シート</t>
+          <t>04シート。図の作り方の手本</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>グラフにすべき表</t>
+          <t>図表目次がない</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>給付費の推移、サービス別の構成、高齢化率は当方のデータで今すぐグラフにできる。見込量と将来推計は村の実績が入ってから</t>
+          <t>約60頁の計画書に図表が120点以上ある。本文の目次だけでは図表にたどり着けないため、目次の後に図表目次を置く</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>04シート</t>
+          <t>06シート</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>足りない図</t>
+          <t>グラフにすべき表</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>施策体系図、関係機関との連携図（論点Ｒ-3）、地域生活支援拠点の5機能、緊急時の4場面、65歳到達時の判定の流れ。いずれも本文と表はあるが図がない</t>
+          <t>給付費の推移、サービス別の構成、高齢化率は当方のデータで今すぐグラフにできる。見込量と将来推計は村の実績が入ってから</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>05シート</t>
+          <t>04シート</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>足りない図</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>施策体系図、関係機関との連携図（論点Ｒ-3）、地域生活支援拠点の5機能、緊急時の4場面、65歳到達時の判定の流れ。いずれも本文と表はあるが図がない</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>05シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>図22点／表109点／規約8件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1233,9 +1250,9 @@
           <t>1344×892</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>潰れる</t>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1275,9 +1292,9 @@
           <t>1344×1034</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>潰れる</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1317,9 +1334,9 @@
           <t>1344×892</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>潰れる</t>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1359,9 +1376,9 @@
           <t>1344×828</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>潰れる</t>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1504,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>はじめからモノクロ</t>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1546,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>はじめからモノクロ</t>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1687,9 +1704,9 @@
           <t>128×128</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>潰れる</t>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1778,14 +1795,14 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>(204,239,254)</t>
+          <t>(202,239,254)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
         <v>230</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
     </row>
@@ -1802,14 +1819,14 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>(192,0,0)</t>
+          <t>(37,78,147)</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -1830,14 +1847,14 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>(31,56,100)</t>
+          <t>(192,0,0)</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -1858,18 +1875,18 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>(46,85,151)</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>81</v>
+          <t>(234,236,240)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>236</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
@@ -1886,11 +1903,11 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>(221,221,221)</t>
+          <t>(179,179,179)</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>0</v>
@@ -1914,11 +1931,11 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>(179,179,179)</t>
+          <t>(210,210,210)</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>0</v>
@@ -1954,52 +1971,60 @@
       <c r="F12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>図2</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>image2.png</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>(149,175,221)</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>172</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>図3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>image3.png</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>(34,127,166)</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>図2</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>image2.png</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>(210,74,74)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>136</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>図3</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>image3.png</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>(57,131,197)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2014,20 +2039,16 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>(61,134,198)</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>119</v>
+          <t>(215,125,35)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>142</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>137</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -2042,14 +2063,14 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>(234,244,250)</t>
+          <t>(20,104,65)</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>242</v>
+        <v>74</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
     </row>
@@ -2066,16 +2087,20 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>(217,130,43)</t>
+          <t>(234,244,238)</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>174</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2090,16 +2115,20 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>(31,111,74)</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>83</v>
+          <t>(121,90,166)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>108</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2114,100 +2143,96 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>(46,134,171)</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>112</v>
+          <t>(94,107,102)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>103</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>図4</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>image4.png</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>(53,129,196)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>図4</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>image4.png</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>(239,156,39)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>167</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
           <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>図3</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>image3.png</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>(122,91,166)</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>109</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>図3</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>image3.png</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>(184,211,235)</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>206</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>図3</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>image3.png</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>(235,186,136)</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>図4</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>image4.png</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>(142,207,164)</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>195</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
+        <v>183</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>ほかの系列と同じ濃さになる</t>
         </is>
@@ -2226,16 +2251,20 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>(61,134,198)</t>
+          <t>(227,232,229)</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>119</v>
+        <v>230</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>137</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -2250,18 +2279,18 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>(240,160,48)</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>171</v>
+          <t>(191,199,195)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>196</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>192</v>
+        <v>8</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
@@ -2278,264 +2307,260 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>(142,207,164)</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>183</v>
+          <t>(167,175,172)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>172</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>図5</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>image5.png</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>(37,154,101)</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>図4</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>image4.png</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>(222,234,245)</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>図5</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>image5.png</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>(53,129,196)</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>図5</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>image5.png</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>(229,234,231)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
         <v>232</v>
       </c>
-      <c r="E26" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>図4</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>image4.png</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>(172,203,231)</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>197</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>図4</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>image4.png</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>(249,214,166)</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>219</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="E28" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>図4</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>image4.png</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>(252,239,220)</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>241</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>図5</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>image5.png</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>(240,160,48)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>171</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>図4</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>image4.png</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>(191,199,195)</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>図5</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>image5.png</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>(186,194,190)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>図6</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>image6.png</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>(226,231,229)</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>229</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>図6</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>image6.png</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>(191,198,195)</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
         <v>196</v>
       </c>
-      <c r="E30" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="E32" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>図5</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>image5.png</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>図6</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>image6.png</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>(46,158,107)</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>119</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E33" s="8" t="n">
         <v>112</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>図5</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>image5.png</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>(61,134,198)</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>137</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>図5</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>image5.png</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>(240,160,48)</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>171</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>192</v>
-      </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>図5</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>image5.png</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>(234,238,236)</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>237</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>図6</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>image6.png</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>(155,167,161)</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>163</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
@@ -2544,24 +2569,24 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>図5</t>
+          <t>図7</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>image5.png</t>
+          <t>image7.png</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>(166,213,192)</t>
+          <t>(46,158,107)</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -2572,24 +2597,24 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>図5</t>
+          <t>図7</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>image5.png</t>
+          <t>image7.png</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>(82,175,132)</t>
+          <t>(61,134,198)</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -2600,68 +2625,64 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>図5</t>
+          <t>図7</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>image5.png</t>
+          <t>image7.png</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>(194,227,212)</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>215</v>
+          <t>(240,160,48)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>171</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>図5</t>
+          <t>図7</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>image5.png</t>
+          <t>image7.png</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>(186,194,190)</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>191</v>
+          <t>(148,115,192)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>134</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>図6</t>
+          <t>図8</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>image6.png</t>
+          <t>image8.png</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -2684,76 +2705,76 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>図6</t>
+          <t>図8</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>image6.png</t>
+          <t>image8.png</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>(46,158,107)</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>119</v>
+          <t>(42,156,104)</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>116</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>図6</t>
+          <t>図8</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>image6.png</t>
+          <t>image8.png</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>(191,198,195)</t>
+          <t>(240,159,46)</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>図6</t>
+          <t>図8</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>image6.png</t>
+          <t>image8.png</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>(155,167,161)</t>
+          <t>(191,198,195)</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
@@ -2762,160 +2783,164 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>図7</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>image7.png</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>(46,158,107)</t>
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>図8</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>image8.png</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>(61,134,198)</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
         <v>119</v>
       </c>
-      <c r="E43" s="6" t="n">
-        <v>112</v>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E43" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>図7</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>image7.png</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>(61,134,198)</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>137</v>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>図8</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>image8.png</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>(155,167,161)</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>163</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>図7</t>
+          <t>図9</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>image7.png</t>
+          <t>image9.png</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>(240,160,48)</t>
+          <t>(226,231,229)</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>192</v>
-      </c>
-      <c r="F45" s="5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>図8</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>image8.png</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>(46,158,107)</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="n">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>図9</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>image9.png</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>(191,198,195)</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>196</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>図9</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>image9.png</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>(61,134,198)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>図8</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>image8.png</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>(240,160,48)</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="n">
-        <v>171</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>192</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="E47" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>図8</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>image8.png</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>(226,231,229)</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>229</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>図9</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>image9.png</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>(155,167,161)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
@@ -2924,24 +2949,24 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>図8</t>
+          <t>図10</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>image8.png</t>
+          <t>image10.png</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>(61,134,198)</t>
+          <t>(46,158,107)</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
         <v>119</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
@@ -2952,132 +2977,128 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>図8</t>
+          <t>図10</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>image8.png</t>
+          <t>image10.png</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>(191,198,195)</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>196</v>
+          <t>(59,133,197)</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>118</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>7</v>
+        <v>138</v>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>図8</t>
+          <t>図10</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>image8.png</t>
+          <t>image10.png</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>(155,167,161)</t>
+          <t>(240,160,48)</t>
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>図9</t>
+          <t>図11</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>image9.png</t>
+          <t>survey_01.png</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>(226,231,229)</t>
+          <t>(40,155,103)</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>229</v>
+        <v>115</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>図9</t>
+          <t>図11</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>image9.png</t>
+          <t>survey_01.png</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>(61,134,198)</t>
+          <t>(165,177,170)</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>137</v>
-      </c>
-      <c r="F53" s="5" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>図9</t>
+          <t>図11</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>image9.png</t>
+          <t>survey_01.png</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>(191,198,195)</t>
+          <t>(182,193,188)</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -3088,24 +3109,24 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>図9</t>
+          <t>図11</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>image9.png</t>
+          <t>survey_01.png</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>(155,167,161)</t>
+          <t>(234,245,240)</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>163</v>
+        <v>241</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
@@ -3116,96 +3137,88 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>図10</t>
+          <t>図12</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>image10.png</t>
+          <t>survey_02.png</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>(46,158,107)</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="n">
-        <v>119</v>
+          <t>(21,105,66)</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>図10</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>image10.png</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>(61,134,198)</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>137</v>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>図13</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>survey_03.png</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>(53,129,196)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>図11</t>
+          <t>図13</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>survey_01.png</t>
+          <t>survey_03.png</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>(46,158,107)</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="n">
-        <v>119</v>
+          <t>(184,192,188)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>189</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>図11</t>
+          <t>図13</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>survey_01.png</t>
+          <t>survey_03.png</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -3226,192 +3239,184 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>図11</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>survey_01.png</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>図14</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>survey_04.png</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>(37,154,101)</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>図14</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>survey_04.png</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>(239,156,40)</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>199</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>図14</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>survey_04.png</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>(211,217,213)</t>
         </is>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D62" s="8" t="n">
         <v>215</v>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E62" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>図11</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>survey_01.png</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>(234,245,240)</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>241</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>図14</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>survey_04.png</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>(231,244,238)</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>239</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>図11</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>survey_01.png</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>(76,172,128)</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="n">
-        <v>138</v>
-      </c>
-      <c r="E62" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>図15</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>survey_05.png</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>(37,154,101)</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>図11</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>survey_01.png</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>(189,196,193)</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>194</v>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>図12</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>survey_02.png</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>(31,111,74)</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
-    </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>図12</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>survey_02.png</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>(169,212,188)</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="n">
-        <v>196</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>図15</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>survey_05.png</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>(239,156,39)</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>図12</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>survey_02.png</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>(200,220,211)</t>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>図15</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>survey_05.png</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>(53,129,196)</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>213</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
+        <v>114</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>ほかの系列と同じ濃さになる</t>
         </is>
@@ -3420,188 +3425,188 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>図13</t>
+          <t>図15</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>survey_03.png</t>
+          <t>survey_05.png</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>(61,134,198)</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="n">
-        <v>119</v>
+          <t>(234,246,243)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>242</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>図16</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>image11.png</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>(103,163,218)</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
           <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>図13</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>survey_03.png</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>(211,217,213)</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="n">
-        <v>215</v>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>図13</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>survey_03.png</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>(169,180,174)</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="n">
-        <v>176</v>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>図16</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>image11.png</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>(252,228,214)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>図13</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>survey_03.png</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>(89,151,206)</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="n">
-        <v>139</v>
-      </c>
-      <c r="E70" s="6" t="n">
-        <v>117</v>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>図16</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>image11.png</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>(175,212,150)</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>図16</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>image11.png</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>(137,192,106)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>図13</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>survey_03.png</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>(161,196,227)</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="n">
-        <v>189</v>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="F71" s="5" t="inlineStr"/>
-    </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>図13</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>survey_03.png</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>(184,192,188)</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>189</v>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>図16</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>image11.png</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>(219,234,223)</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>228</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>図14</t>
+          <t>図16</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>survey_04.png</t>
+          <t>image11.png</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>(46,158,107)</t>
+          <t>(210,230,211)</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>119</v>
+        <v>222</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -3610,160 +3615,164 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>図14</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>survey_04.png</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>(240,160,48)</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="n">
-        <v>171</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>192</v>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>図17</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>(37,154,100)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="F74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>図14</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>survey_04.png</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>(211,217,213)</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="n">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>図17</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>(221,221,221)</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>221</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>図17</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>(215,215,215)</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="n">
         <v>215</v>
       </c>
-      <c r="E75" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="E76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>図14</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>survey_04.png</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>(65,167,120)</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="n">
-        <v>131</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>102</v>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>図14</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>survey_04.png</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>(246,196,127)</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="n">
-        <v>203</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>119</v>
-      </c>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>図17</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>(129,129,129)</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>図14</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>survey_04.png</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>(252,236,213)</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="n">
-        <v>238</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>図17</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>(164,164,164)</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>図14</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>survey_04.png</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>(231,244,238)</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="n">
-        <v>239</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>図17</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>(90,90,90)</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
@@ -3772,138 +3781,134 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>図14</t>
+          <t>図18</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>survey_04.png</t>
+          <t>image17.png</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>(102,184,147)</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="n">
-        <v>155</v>
+          <t>(36,154,100)</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>113</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>図15</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>survey_05.png</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>(46,158,107)</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="E81" s="6" t="n">
-        <v>112</v>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>図18</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>(228,228,228)</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>228</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>図15</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>survey_05.png</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>(240,160,48)</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="n">
-        <v>171</v>
-      </c>
-      <c r="E82" s="6" t="n">
-        <v>192</v>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>図18</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>(211,206,208)</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>208</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>図15</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>survey_05.png</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>(61,134,198)</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="E83" s="6" t="n">
-        <v>137</v>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>図18</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>(81,81,81)</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>図15</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>survey_05.png</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>(234,246,243)</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="n">
-        <v>242</v>
-      </c>
-      <c r="E84" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>図18</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>(165,165,165)</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
@@ -3912,136 +3917,136 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>図15</t>
+          <t>図19</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>survey_05.png</t>
+          <t>image18.png</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>(77,173,131)</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="n">
-        <v>140</v>
+          <t>(217,217,217)</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>217</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>図15</t>
+          <t>図19</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>survey_05.png</t>
+          <t>image18.png</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>(114,190,155)</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="n">
-        <v>163</v>
+          <t>(227,227,227)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>227</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>図15</t>
+          <t>図19</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>survey_05.png</t>
+          <t>image18.png</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>(246,182,94)</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="n">
-        <v>191</v>
+          <t>(154,154,154)</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>154</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>図15</t>
+          <t>図19</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>survey_05.png</t>
+          <t>image18.png</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>(148,206,180)</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="n">
-        <v>186</v>
+          <t>(91,91,91)</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>91</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>図16</t>
+          <t>図20</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image12.png</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>(252,228,214)</t>
+          <t>(102,163,218)</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>234</v>
+        <v>151</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
@@ -4052,24 +4057,24 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>図16</t>
+          <t>図20</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image12.png</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>(103,163,218)</t>
+          <t>(222,100,134)</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
@@ -4080,1808 +4085,405 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>図16</t>
+          <t>図20</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image12.png</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>(194,218,240)</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="n">
-        <v>213</v>
+          <t>(239,181,63)</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>185</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="F91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>図16</t>
+          <t>図20</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image12.png</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>(147,190,229)</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="n">
-        <v>182</v>
+          <t>(27,52,97)</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>図16</t>
+          <t>図20</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image12.png</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>(227,237,248)</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="n">
-        <v>235</v>
+          <t>(210,231,197)</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>221</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>図16</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>image11.png</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
-        <is>
-          <t>(175,212,150)</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="n">
-        <v>194</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>(29,93,59)</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="F94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>図16</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>image11.png</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>(137,192,106)</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="n">
-        <v>166</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>(214,214,214)</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>図16</t>
+          <t>図22</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image14.jpeg</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>(210,230,211)</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="n">
-        <v>222</v>
+          <t>(227,215,193)</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>216</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>(164,164,164)</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="n">
-        <v>164</v>
-      </c>
-      <c r="E97" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>潰れる組</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>グレー値の差</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>どこに出るか</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>RGB(37, 78, 147) と RGB(192, 0, 0)</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>図2 ほか（image2.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>RGB(34, 127, 166) と RGB(57, 131, 197)</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>図3 ほか（image3.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>RGB(34, 127, 166) と RGB(121, 90, 166)</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>図3 ほか（image3.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>RGB(57, 131, 197) と RGB(121, 90, 166)</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>図3 ほか（image3.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>RGB(239, 156, 39) と RGB(142, 207, 164)</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>図4 ほか（image4.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>RGB(37, 154, 101) と RGB(53, 129, 196)</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>図5 ほか（image5.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>RGB(46, 158, 107) と RGB(61, 134, 198)</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>(90,90,90)</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="E98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>(129,129,129)</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="n">
-        <v>129</v>
-      </c>
-      <c r="E99" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>(221,221,221)</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="n">
-        <v>221</v>
-      </c>
-      <c r="E100" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>(114,114,114)</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="n">
-        <v>114</v>
-      </c>
-      <c r="E101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>(191,191,191)</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="n">
-        <v>191</v>
-      </c>
-      <c r="E102" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>(205,205,205)</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="n">
-        <v>205</v>
-      </c>
-      <c r="E103" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>(73,73,73)</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="E104" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>(228,228,228)</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="n">
-        <v>228</v>
-      </c>
-      <c r="E105" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t>(81,81,81)</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>RGB(46, 158, 107) と RGB(148, 115, 192)</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>(191,191,191)</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>RGB(61, 134, 198) と RGB(148, 115, 192)</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>(145,145,145)</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="n">
-        <v>145</v>
-      </c>
-      <c r="E108" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>RGB(42, 156, 104) と RGB(61, 134, 198)</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>図8 ほか（image8.png）</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>(119,119,119)</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="n">
-        <v>119</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>RGB(46, 158, 107) と RGB(59, 133, 197)</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>図10 ほか（image10.png）</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>(165,165,165)</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="n">
-        <v>165</v>
-      </c>
-      <c r="E110" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>RGB(103, 163, 218) と RGB(137, 192, 106)</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>図16 ほか（image11.png）</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>(210,210,210)</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="n">
-        <v>210</v>
-      </c>
-      <c r="E111" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>RGB(252, 228, 214) と RGB(219, 234, 223)</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>図16 ほか（image11.png）</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>図19</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>(217,217,217)</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="n">
-        <v>217</v>
-      </c>
-      <c r="E112" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>RGB(252, 228, 214) と RGB(210, 230, 211)</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>図16 ほか（image11.png）</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>図19</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>(235,235,235)</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="n">
-        <v>235</v>
-      </c>
-      <c r="E113" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>RGB(219, 234, 223) と RGB(210, 230, 211)</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>図16 ほか（image11.png）</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>図19</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>(91,91,91)</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="n">
-        <v>91</v>
-      </c>
-      <c r="E114" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>図19</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>(154,154,154)</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="n">
-        <v>154</v>
-      </c>
-      <c r="E115" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>図19</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>(176,176,176)</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="n">
-        <v>176</v>
-      </c>
-      <c r="E116" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>(232,241,251)</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="n">
-        <v>239</v>
-      </c>
-      <c r="E117" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>(251,227,234)</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="n">
-        <v>235</v>
-      </c>
-      <c r="E118" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>(31,56,100)</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="F119" s="4" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>(224,108,140)</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t>(116,171,221)</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="n">
-        <v>160</v>
-      </c>
-      <c r="E121" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t>(177,208,236)</t>
-        </is>
-      </c>
-      <c r="D122" s="9" t="n">
-        <v>202</v>
-      </c>
-      <c r="E122" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>(148,191,229)</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="n">
-        <v>182</v>
-      </c>
-      <c r="E123" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
-        <is>
-          <t>(200,222,242)</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="n">
-        <v>218</v>
-      </c>
-      <c r="E124" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>図21</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>image13.png</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>(29,93,59)</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="E125" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="F125" s="5" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>図22</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>image14.jpeg</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
-        <is>
-          <t>(227,215,193)</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="n">
-        <v>216</v>
-      </c>
-      <c r="E126" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>図22</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>image14.jpeg</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
-        <is>
-          <t>(212,200,178)</t>
-        </is>
-      </c>
-      <c r="D127" s="9" t="n">
-        <v>201</v>
-      </c>
-      <c r="E127" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>図22</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>image14.jpeg</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
-        <is>
-          <t>(241,229,207)</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="n">
-        <v>230</v>
-      </c>
-      <c r="E128" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="30" customHeight="1">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>潰れる組</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>グレー値の差</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>どこに出るか</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>RGB(192, 0, 0) と RGB(31, 56, 100)</t>
-        </is>
-      </c>
-      <c r="B131" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>図2 ほか（image2.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>RGB(192, 0, 0) と RGB(46, 85, 151)</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>図2 ほか（image2.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>RGB(61, 134, 198) と RGB(46, 134, 171)</t>
-        </is>
-      </c>
-      <c r="B133" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>RGB(61, 134, 198) と RGB(122, 91, 166)</t>
-        </is>
-      </c>
-      <c r="B134" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="10" t="inlineStr">
-        <is>
-          <t>RGB(46, 134, 171) と RGB(122, 91, 166)</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>RGB(184, 211, 235) と RGB(235, 186, 136)</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="n">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>RGB(102, 163, 218) と RGB(222, 100, 134)</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="10" t="inlineStr">
-        <is>
-          <t>RGB(240, 160, 48) と RGB(142, 207, 164)</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>図4 ほか（image4.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="10" t="inlineStr">
-        <is>
-          <t>RGB(142, 207, 164) と RGB(172, 203, 231)</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>図4 ほか（image4.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
-        <is>
-          <t>RGB(222, 234, 245) と RGB(249, 214, 166)</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>図4 ほか（image4.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="10" t="inlineStr">
-        <is>
-          <t>RGB(222, 234, 245) と RGB(252, 239, 220)</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>図4 ほか（image4.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="10" t="inlineStr">
-        <is>
-          <t>RGB(172, 203, 231) と RGB(249, 214, 166)</t>
-        </is>
-      </c>
-      <c r="B141" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>図4 ほか（image4.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="10" t="inlineStr">
-        <is>
-          <t>RGB(249, 214, 166) と RGB(252, 239, 220)</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>図4 ほか（image4.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="10" t="inlineStr">
-        <is>
-          <t>RGB(46, 158, 107) と RGB(61, 134, 198)</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>図5 ほか（image5.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>RGB(46, 158, 107) と RGB(82, 175, 132)</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>図5 ほか（image5.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>RGB(61, 134, 198) と RGB(82, 175, 132)</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>図5 ほか（image5.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>RGB(166, 213, 192) と RGB(194, 227, 212)</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>図5 ほか（image5.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="10" t="inlineStr">
-        <is>
-          <t>RGB(46, 158, 107) と RGB(76, 172, 128)</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>図11 ほか（survey_01.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="10" t="inlineStr">
-        <is>
-          <t>RGB(169, 212, 188) と RGB(200, 220, 211)</t>
-        </is>
-      </c>
-      <c r="B148" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>図12 ほか（survey_02.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="10" t="inlineStr">
-        <is>
-          <t>RGB(61, 134, 198) と RGB(89, 151, 206)</t>
-        </is>
-      </c>
-      <c r="B149" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>図13 ほか（survey_03.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="10" t="inlineStr">
-        <is>
-          <t>RGB(46, 158, 107) と RGB(65, 167, 120)</t>
-        </is>
-      </c>
-      <c r="B150" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>図14 ほか（survey_04.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="10" t="inlineStr">
-        <is>
-          <t>RGB(240, 160, 48) と RGB(102, 184, 147)</t>
-        </is>
-      </c>
-      <c r="B151" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>図14 ほか（survey_04.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>RGB(65, 167, 120) と RGB(102, 184, 147)</t>
-        </is>
-      </c>
-      <c r="B152" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>図14 ほか（survey_04.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="10" t="inlineStr">
-        <is>
-          <t>RGB(46, 158, 107) と RGB(77, 173, 131)</t>
-        </is>
-      </c>
-      <c r="B153" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>図15 ほか（survey_05.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="10" t="inlineStr">
-        <is>
-          <t>RGB(240, 160, 48) と RGB(114, 190, 155)</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>図15 ほか（survey_05.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="10" t="inlineStr">
-        <is>
-          <t>RGB(240, 160, 48) と RGB(246, 182, 94)</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>図15 ほか（survey_05.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="10" t="inlineStr">
-        <is>
-          <t>RGB(240, 160, 48) と RGB(148, 206, 180)</t>
-        </is>
-      </c>
-      <c r="B156" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>図15 ほか（survey_05.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="10" t="inlineStr">
-        <is>
-          <t>RGB(61, 134, 198) と RGB(77, 173, 131)</t>
-        </is>
-      </c>
-      <c r="B157" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>図15 ほか（survey_05.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="10" t="inlineStr">
-        <is>
-          <t>RGB(77, 173, 131) と RGB(114, 190, 155)</t>
-        </is>
-      </c>
-      <c r="B158" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>図15 ほか（survey_05.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="10" t="inlineStr">
-        <is>
-          <t>RGB(114, 190, 155) と RGB(148, 206, 180)</t>
-        </is>
-      </c>
-      <c r="B159" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>図15 ほか（survey_05.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="10" t="inlineStr">
-        <is>
-          <t>RGB(246, 182, 94) と RGB(148, 206, 180)</t>
-        </is>
-      </c>
-      <c r="B160" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>図15 ほか（survey_05.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="10" t="inlineStr">
-        <is>
-          <t>RGB(252, 228, 214) と RGB(194, 218, 240)</t>
-        </is>
-      </c>
-      <c r="B161" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="10" t="inlineStr">
-        <is>
-          <t>RGB(252, 228, 214) と RGB(227, 237, 248)</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="10" t="inlineStr">
-        <is>
-          <t>RGB(252, 228, 214) と RGB(210, 230, 211)</t>
-        </is>
-      </c>
-      <c r="B163" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="10" t="inlineStr">
-        <is>
-          <t>RGB(103, 163, 218) と RGB(137, 192, 106)</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="10" t="inlineStr">
-        <is>
-          <t>RGB(194, 218, 240) と RGB(227, 237, 248)</t>
-        </is>
-      </c>
-      <c r="B165" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="10" t="inlineStr">
-        <is>
-          <t>RGB(194, 218, 240) と RGB(175, 212, 150)</t>
-        </is>
-      </c>
-      <c r="B166" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="10" t="inlineStr">
-        <is>
-          <t>RGB(194, 218, 240) と RGB(210, 230, 211)</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="10" t="inlineStr">
-        <is>
-          <t>RGB(147, 190, 229) と RGB(175, 212, 150)</t>
-        </is>
-      </c>
-      <c r="B168" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="10" t="inlineStr">
-        <is>
-          <t>RGB(147, 190, 229) と RGB(137, 192, 106)</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="10" t="inlineStr">
-        <is>
-          <t>RGB(227, 237, 248) と RGB(210, 230, 211)</t>
-        </is>
-      </c>
-      <c r="B170" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="10" t="inlineStr">
-        <is>
-          <t>RGB(232, 241, 251) と RGB(251, 227, 234)</t>
-        </is>
-      </c>
-      <c r="B171" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>図20 ほか（image12.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="10" t="inlineStr">
-        <is>
-          <t>RGB(232, 241, 251) と RGB(200, 222, 242)</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>図20 ほか（image12.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="10" t="inlineStr">
-        <is>
-          <t>RGB(251, 227, 234) と RGB(200, 222, 242)</t>
-        </is>
-      </c>
-      <c r="B173" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>図20 ほか（image12.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="10" t="inlineStr">
-        <is>
-          <t>RGB(224, 108, 140) と RGB(116, 171, 221)</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>図20 ほか（image12.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="10" t="inlineStr">
-        <is>
-          <t>RGB(116, 171, 221) と RGB(148, 191, 229)</t>
-        </is>
-      </c>
-      <c r="B175" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>図20 ほか（image12.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="10" t="inlineStr">
-        <is>
-          <t>RGB(177, 208, 236) と RGB(148, 191, 229)</t>
-        </is>
-      </c>
-      <c r="B176" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>図20 ほか（image12.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="10" t="inlineStr">
-        <is>
-          <t>RGB(177, 208, 236) と RGB(200, 222, 242)</t>
-        </is>
-      </c>
-      <c r="B177" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>図20 ほか（image12.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="10" t="inlineStr">
-        <is>
-          <t>RGB(227, 215, 193) と RGB(212, 200, 178)</t>
-        </is>
-      </c>
-      <c r="B178" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>図22 ほか（image14.jpeg）</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="10" t="inlineStr">
-        <is>
-          <t>RGB(227, 215, 193) と RGB(241, 229, 207)</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>図22 ほか（image14.jpeg）</t>
         </is>
       </c>
     </row>
@@ -10037,17 +8639,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>モノクロで作る</t>
+          <t>色の使い方</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>系列はグレーの濃淡と45度・135度の網かけで分け、色だけで分けない。濃さの差は256階調で25以上空ける</t>
+          <t>他メンバー版と同じ3色（緑・橙・青）から使う。同じ図の中で系列が2つ以上あるときは、グレー値が25以上離れる組を選ぶ（緑と橙は52離れる。緑と青はいずれも119で同じ濃さになるため並べて使わない）。系列が接する積み上げでは網かけ（45度・135度）も足す</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>成果品①はモノクロ印刷である（仕様書5）。いまの図は緑と青が同じ濃さになり、印刷すると見分けられない</t>
+          <t>図はカラーで進めるが、計画書は窓口で白黒コピーされることがある。色のほかにもう一つ手がかりを残しておけば、コピーされても系列を追える</t>
         </is>
       </c>
     </row>
@@ -10174,12 +8776,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>モノクロ印刷への対応</t>
+          <t>緑と青の組合せ</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>緑と青が同じ濃さになるため、モノクロ印刷すると身体障害者手帳と精神障害者保健福祉手帳の棒を見分けられない。グレーの濃淡と網かけで作り直すか、カラー印刷に変えるかを決めたい</t>
+          <t>図はカラーで進めることとしたが、緑 RGB(46,158,107) と 青 RGB(61,134,198) はグレー値がいずれも119で、白黒コピーすると見分けられない。手帳の種類別のように3系列並べる図では、青を橙（グレー値171）に替えるか、網かけを足すことを提案したい</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -10206,7 +8808,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>仕様書5はモノクロとあるが、図をカラーにする場合の費用と部数の扱いを確認したい。カラーにしない場合は、図をグレーの濃淡で作り直す</t>
+          <t>仕様書5の成果品①は「モノクロ・コピー・くるみ製本」であるが、図はカラーで作成している。①カラー印刷とする場合の費用と部数の扱い②モノクロ印刷とする場合に図を作り直す必要があること③窓口での白黒コピーを想定するかどうか、を確認したい</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図22点／表109点（データ表75・注記ボックス34）。図表番号は0件、図表目次もない</t>
+          <t>図27点／表109点（データ表75・注記ボックス34）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図22点／表109点／規約8件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図27点／表109点／規約8件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1432,37 +1432,37 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のため</t>
+          <t>３　基本施策の目標値と本計画</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>本村には障がい福祉サービスの事業所が３カ所しかありませんが、介護保険の事業所</t>
+          <t>第４次北塩原村障がい者計画では、７つの基本施策ごとに令和11年度の目標値を設</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>（５）障がい児支援の提供体制の確保</t>
+          <t>計画の体系</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image19.png</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>1312×809</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>潰れる</t>
+          <t>1307×1045</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係</t>
+          <t>２　令和11年度に向けた成果</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>（１）給付費の推移</t>
+          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>地域生活支援拠点等の５つの機能</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image21.png</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>1112×614</t>
+          <t>1307×697</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -1521,32 +1521,32 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係</t>
+          <t>２　必要な見込量の確保のため</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>（３）サービス別の構成（令和７年度）</t>
+          <t>本村には障がい福祉サービスの事業所が３カ所しかありませんが、介護保険の事業所</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>サービス別の給付費（令和７年度）</t>
+          <t>（５）障がい児支援の提供体制の確保</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image11.png</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>1210×638</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>見分けられる</t>
+          <t>1312×809</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>潰れる</t>
         </is>
       </c>
     </row>
@@ -1558,37 +1558,37 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>２　必要な見込量の確保のため</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>（１）高齢化率</t>
+          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。どの場面</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>image18.png</t>
+          <t>image22.png</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>1046×591</t>
+          <t>1307×747</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>はじめからモノクロ</t>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1600,37 +1600,37 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>５　年齢到達に伴うサービスの</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>本計画の推進にあたっては、本村の関連計画と整合を図り、連携して施策を推進する</t>
+          <t>65歳到達時に介護保険へ移行するかどうかは、サービスの種類により扱いが異なり</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッドヘルスプランと</t>
+          <t>65歳到達時の判定の流れ</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>image12.png</t>
+          <t>image23.png</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>1223×1286</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>潰れる</t>
+          <t>1307×1220</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1642,33 +1642,37 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>0241－23－3113（直通）</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
+          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>関係機関との連携</t>
+        </is>
+      </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>image13.png</t>
+          <t>image20.png</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>501×132</t>
+          <t>1307×884</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>見分けられる</t>
+          <t>はじめからモノクロ</t>
         </is>
       </c>
     </row>
@@ -1680,31 +1684,237 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>第５章　障がい福祉サ</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>７　障がい福祉サービス等に係</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>（１）給付費の推移</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉サービス等に係る給付費の推移</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>1112×614</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>図23</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>第５章　障がい福祉サ</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>７　障がい福祉サービス等に係</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>（３）サービス別の構成（令和７年度）</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>サービス別の給付費（令和７年度）</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>1210×638</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>図24</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>第６章　成年後見制度</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>１　現状と課題</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>（１）高齢化率</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>高齢化率の推移</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>1046×591</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>はじめからモノクロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>４　制度の見直しへの対応</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>本計画の推進にあたっては、本村の関連計画と整合を図り、連携して施策を推進する</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>１　第３次健康21・北塩原村グッドヘルスプランと</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>1223×1286</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>潰れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>第８章　資料編</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>５　用語解説</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>0241－23－3113（直通）</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>501×132</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>0241－23－3113（直通）</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>image14.jpeg</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>128×128</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>見分けられる</t>
         </is>
@@ -1725,7 +1935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3458,23 +3668,23 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image19.png</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>(103,163,218)</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="n">
-        <v>151</v>
+          <t>(234,244,238)</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>240</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
@@ -3486,25 +3696,21 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image19.png</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>(252,228,214)</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="n">
-        <v>234</v>
+          <t>(244,184,101)</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>192</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -3514,21 +3720,25 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image19.png</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>(175,212,150)</t>
+          <t>(178,178,178)</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="F70" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -3538,25 +3748,21 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image19.png</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>(137,192,106)</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="n">
-        <v>166</v>
+          <t>(86,177,136)</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>145</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -3566,23 +3772,23 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image19.png</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>(219,234,223)</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="n">
-        <v>228</v>
+          <t>(185,185,185)</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>185</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>ほかの系列と同じ濃さになる</t>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
@@ -3594,49 +3800,49 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>image11.png</t>
+          <t>image19.png</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>(210,230,211)</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="n">
-        <v>222</v>
+          <t>(255,246,231)</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>247</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>図17</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>(37,154,100)</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="n">
-        <v>113</v>
-      </c>
-      <c r="E74" s="6" t="n">
-        <v>117</v>
-      </c>
-      <c r="F74" s="5" t="inlineStr"/>
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>図16</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>image19.png</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>(133,133,133)</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -3646,19 +3852,19 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image21.png</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>(221,221,221)</t>
+          <t>(234,244,238)</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
@@ -3674,16 +3880,16 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image21.png</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>(215,215,215)</t>
+          <t>(168,168,168)</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>0</v>
@@ -3702,16 +3908,16 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image21.png</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>(129,129,129)</t>
+          <t>(212,212,212)</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>0</v>
@@ -3730,25 +3936,21 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image21.png</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>(164,164,164)</t>
+          <t>(47,159,108)</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -3758,73 +3960,73 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image21.png</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>(90,90,90)</t>
+          <t>(244,183,98)</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="E79" s="6" t="n">
+        <v>146</v>
+      </c>
+      <c r="F79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>図17</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>image21.png</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>(136,136,136)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="E80" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>(36,154,100)</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>118</v>
-      </c>
-      <c r="F80" s="4" t="inlineStr"/>
-    </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>図18</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>(228,228,228)</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>228</v>
-      </c>
-      <c r="E81" s="8" t="n">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>図17</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>image21.png</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>(95,95,95)</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="E81" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
@@ -3838,23 +4040,23 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image11.png</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>(211,206,208)</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="n">
-        <v>208</v>
+          <t>(103,163,218)</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>151</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
@@ -3866,23 +4068,23 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image11.png</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>(81,81,81)</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="n">
-        <v>81</v>
+          <t>(252,228,214)</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>234</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
@@ -3894,107 +4096,103 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image11.png</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>(165,165,165)</t>
+          <t>(175,212,150)</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>図19</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>(217,217,217)</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="n">
-        <v>217</v>
-      </c>
-      <c r="E85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>図18</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>image11.png</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>(137,192,106)</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>図19</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>(227,227,227)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="n">
-        <v>227</v>
-      </c>
-      <c r="E86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>図18</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>image11.png</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>(219,234,223)</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>228</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>図19</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>(154,154,154)</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="n">
-        <v>154</v>
-      </c>
-      <c r="E87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>図18</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>image11.png</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>(210,230,211)</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>222</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
         </is>
       </c>
     </row>
@@ -4006,201 +4204,205 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>image18.png</t>
+          <t>image22.png</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>(91,91,91)</t>
+          <t>(240,163,54)</t>
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="E88" s="6" t="n">
+        <v>186</v>
+      </c>
+      <c r="F88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>図19</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>image22.png</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>(155,155,155)</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="E89" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>(102,163,218)</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="n">
-        <v>151</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
-        </is>
-      </c>
-    </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>(222,100,134)</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="n">
-        <v>140</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>図19</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>image22.png</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>(201,201,201)</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>(239,181,63)</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="n">
-        <v>185</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>176</v>
-      </c>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>図19</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>image22.png</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>(233,245,240)</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>241</v>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>(27,52,97)</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>図19</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>image22.png</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>(53,161,112)</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="F92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>図20</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>(210,231,197)</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="n">
-        <v>221</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>図19</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>image22.png</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>(134,134,134)</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>図21</t>
+          <t>図19</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>image13.png</t>
+          <t>image22.png</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>(29,93,59)</t>
+          <t>(255,246,231)</t>
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>70</v>
+        <v>247</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>図21</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>image13.png</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>(214,214,214)</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="n">
-        <v>214</v>
-      </c>
-      <c r="E95" s="6" t="n">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>図20</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>(153,153,153)</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>153</v>
+      </c>
+      <c r="E95" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
@@ -4209,281 +4411,1145 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
+          <t>図20</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>(181,181,181)</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>181</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>図20</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>(234,244,238)</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>図20</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>(132,132,132)</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>図20</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>(105,186,149)</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="F99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>図20</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>(244,187,107)</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>image20.png</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>(149,149,149)</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>149</v>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>image20.png</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>(201,201,201)</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>image20.png</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>(234,244,238)</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>image20.png</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>(114,114,114)</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>image20.png</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>(98,98,98)</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="E105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
           <t>図22</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>(37,154,100)</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="F106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>図22</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>(221,221,221)</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>221</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>図22</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>(215,215,215)</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>図22</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>(129,129,129)</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>図22</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>(164,164,164)</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="n">
+        <v>164</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>図22</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>(90,90,90)</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>図23</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>(36,154,100)</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="F112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>図23</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>(228,228,228)</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="E113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>図23</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>(211,206,208)</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>図23</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>(81,81,81)</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>図23</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>(165,165,165)</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>図24</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>(217,217,217)</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>図24</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>(227,227,227)</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>図24</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>(154,154,154)</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>154</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>図24</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>(91,91,91)</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>(102,163,218)</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>(222,100,134)</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>(239,181,63)</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>(27,52,97)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>(210,231,197)</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>221</v>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>(29,93,59)</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="F126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>(214,214,214)</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="n">
+        <v>214</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>image14.jpeg</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>(227,215,193)</t>
         </is>
       </c>
-      <c r="D96" s="8" t="n">
+      <c r="D128" s="6" t="n">
         <v>216</v>
       </c>
-      <c r="E96" s="8" t="n">
+      <c r="E128" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr"/>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>潰れる組</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>グレー値の差</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>どこに出るか</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>RGB(37, 78, 147) と RGB(192, 0, 0)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="n">
+      <c r="B131" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>図2 ほか（image2.png）</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>RGB(34, 127, 166) と RGB(57, 131, 197)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="n">
+      <c r="B132" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>RGB(34, 127, 166) と RGB(121, 90, 166)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="n">
+      <c r="B133" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr">
         <is>
           <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>RGB(57, 131, 197) と RGB(121, 90, 166)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="n">
+      <c r="B134" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>RGB(239, 156, 39) と RGB(142, 207, 164)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="n">
+      <c r="B135" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>図4 ほか（image4.png）</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>RGB(37, 154, 101) と RGB(53, 129, 196)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="n">
+      <c r="B136" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
         <is>
           <t>図5 ほか（image5.png）</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>RGB(46, 158, 107) と RGB(61, 134, 198)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="n">
+      <c r="B137" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>RGB(46, 158, 107) と RGB(148, 115, 192)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="n">
+      <c r="B138" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C138" s="4" t="inlineStr">
         <is>
           <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="10" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>RGB(61, 134, 198) と RGB(148, 115, 192)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="n">
+      <c r="B139" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
         <is>
           <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="10" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
         <is>
           <t>RGB(42, 156, 104) と RGB(61, 134, 198)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="n">
+      <c r="B140" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>図8 ほか（image8.png）</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
         <is>
           <t>RGB(46, 158, 107) と RGB(59, 133, 197)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="n">
+      <c r="B141" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
         <is>
           <t>図10 ほか（image10.png）</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="10" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>RGB(103, 163, 218) と RGB(137, 192, 106)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="n">
+      <c r="B142" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
         <is>
           <t>RGB(252, 228, 214) と RGB(219, 234, 223)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="n">
+      <c r="B143" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="10" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>RGB(252, 228, 214) と RGB(210, 230, 211)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="n">
+      <c r="B144" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>RGB(219, 234, 223) と RGB(210, 230, 211)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="n">
+      <c r="B145" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>図16 ほか（image11.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="10" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>RGB(102, 163, 218) と RGB(222, 100, 134)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="n">
+      <c r="B146" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>図20 ほか（image12.png）</t>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>図25 ほか（image12.png）</t>
         </is>
       </c>
     </row>
@@ -8240,14 +9306,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -8290,6 +9357,11 @@
           <t>扱い</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -8317,6 +9389,11 @@
           <t>作り直し</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>未着手（元データがないため。Ｓ-19）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -8344,6 +9421,11 @@
           <t>新しく作る</t>
         </is>
       </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>作成済み（図Z-4）。基本目標と基本施策の対応は第4次障がい者計画の体系図にしかなく当方は未入手のため、線で結ばず図中に注記した</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -8371,6 +9453,11 @@
           <t>新しく作る</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>作成済み（図Z-5）。移植19の表の11機関を7分野に分け、相談の入口である村保健福祉課を中心に置いた</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -8398,6 +9485,11 @@
           <t>新しく作る</t>
         </is>
       </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>作成済み（図Z-6）。W-3の表から5機能を起こし、4町村の拠点と本村の関わりを上下に置いた</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -8425,6 +9517,11 @@
           <t>新しく作る（表で足りるなら不要）</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>作成済み（図Z-7）。平時・急病時は高齢者施策であり障がいのある方が対象かを確認していないこと（Ｍ-50・Ｍ-52）を図中に明示した</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -8452,6 +9549,11 @@
           <t>新しく作る</t>
         </is>
       </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>作成済み（図Z-8）。4段の判定と3つの結論、W-1の記録6項目を1枚にした</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -8479,11 +9581,16 @@
           <t>確認のみ</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>未着手（他メンバーの図との突合が要るため）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図27点／表109点（データ表75・注記ボックス34）。図表番号は0件、図表目次もない</t>
+          <t>図27点／表121点（データ表79・注記ボックス42）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表109点のうち、直後に出所らしき行があるのは7点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表121点のうち、直後に出所らしき行があるのは6点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図27点／表109点／規約8件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図27点／表121点／規約8件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -5568,7 +5568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6964,7 +6964,7 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -6978,27 +6978,23 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -7012,23 +7008,27 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7042,23 +7042,27 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7072,22 +7076,18 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr"/>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>3</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7234,27 +7234,23 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -7268,23 +7264,27 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7294,48 +7294,52 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr"/>
@@ -7344,28 +7348,28 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
@@ -7374,7 +7378,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7391,11 +7395,11 @@
         <v>11</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr"/>
@@ -7404,7 +7408,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7418,7 +7422,7 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>5</v>
@@ -7434,7 +7438,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7448,7 +7452,7 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E63" s="8" t="n">
         <v>5</v>
@@ -7464,7 +7468,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7478,14 +7482,14 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E64" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E64" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -7494,7 +7498,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7508,27 +7512,23 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -7542,14 +7542,14 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -7558,7 +7558,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -7572,23 +7572,27 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -7602,27 +7606,23 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援４人、生活介護及び就労継続支援Ｂ型の利用者について、計画期間の開始前から引き続き利用</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
@@ -7652,7 +7652,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -7666,23 +7666,27 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -7696,23 +7700,27 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-23）】施設入所支援４人、生活介護及び就労継続支援Ｂ型の利用者について、計画期間の開始前から引き続き利用</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -7726,14 +7734,14 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -7742,7 +7750,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -7752,18 +7760,18 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
@@ -7772,7 +7780,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -7782,31 +7790,27 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7816,31 +7820,27 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -7870,7 +7870,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7884,23 +7884,27 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -7914,14 +7918,14 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
@@ -7930,7 +7934,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7944,18 +7948,22 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -7981,7 +7989,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -7994,7 +8002,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8008,14 +8016,14 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr"/>
@@ -8024,7 +8032,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8038,27 +8046,23 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr"/>
+          <t>備える事項 / 本村の取組み</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8068,18 +8072,18 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr"/>
@@ -8088,7 +8092,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8098,27 +8102,31 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8128,31 +8136,27 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8162,27 +8166,31 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8192,18 +8200,18 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
@@ -8222,7 +8230,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D88" s="6" t="n">
@@ -8233,7 +8241,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -8246,7 +8254,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8256,31 +8264,27 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8290,18 +8294,18 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr"/>
@@ -8310,7 +8314,7 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8320,27 +8324,31 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8350,31 +8358,27 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8384,18 +8388,18 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr"/>
@@ -8414,7 +8418,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D94" s="6" t="n">
@@ -8425,7 +8429,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -8438,7 +8442,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8448,27 +8452,31 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8478,18 +8486,18 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E96" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr"/>
@@ -8498,7 +8506,7 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -8508,31 +8516,27 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -8542,27 +8546,31 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -8572,7 +8580,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D99" s="8" t="n">
@@ -8583,7 +8591,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
@@ -8592,7 +8600,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -8602,31 +8610,31 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -8636,52 +8644,48 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr"/>
+          <t>確認する事項 / 確認の内容</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr"/>
@@ -8690,62 +8694,62 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>分野 / 関係機関 / 連携の内容</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr"/>
@@ -8754,32 +8758,36 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -8789,12 +8797,12 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
@@ -8805,7 +8813,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -8818,28 +8826,28 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
@@ -8848,28 +8856,28 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr"/>
@@ -8878,32 +8886,36 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr"/>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -8913,12 +8925,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D110" s="6" t="n">
@@ -8929,7 +8941,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -8937,37 +8949,33 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H110" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E111" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
@@ -8976,58 +8984,62 @@
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr"/>
@@ -9036,32 +9048,408 @@
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>第６章　成年後見制度</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>３　今後の取組み</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>表６-4</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>第６章　成年後見制度</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>３　今後の取組み</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>第６章　成年後見制度</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>４　制度の見直しへの対応</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>表７-1</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>１　第３次健康21・北塩原村グッ</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>表７-2</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>２　北塩原村第五次総合振興計画と</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>表７-3</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>表７-4</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>４　北塩原村こども・子育て計画と</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>確かめる事項 / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="9" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>４　北塩原村こども・子育て計画と</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>表８-1</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>２　北塩原村障がい者自立支援協議</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="9" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>表８-2</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>３　計画の策定経過</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="9" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
           <t>表８-4</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>第８章　資料編</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>５　用語解説</t>
         </is>
       </c>
-      <c r="D114" s="6" t="n">
+      <c r="D126" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="E114" s="6" t="n">
+      <c r="E126" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F114" s="5" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="9" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図27点／表121点（データ表79・注記ボックス42）。図表番号は0件、図表目次もない</t>
+          <t>図27点／表129点（データ表84・注記ボックス45）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表121点のうち、直後に出所らしき行があるのは6点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表129点のうち、直後に出所らしき行があるのは6点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図27点／表121点／規約8件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図27点／表129点／規約8件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -5568,7 +5568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6008,41 +6008,37 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>表２-1</t>
+          <t>表１-10</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>第２章　本村の障がい</t>
+          <t>第１章　計画の策定に</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>１　人口の推移</t>
+          <t>６　計画の推進体制</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和８年度 （現状） / 令和９年度 / 令和10年度</t>
+          <t>順 / 確かめること</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表２-1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -6052,31 +6048,31 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>２　障がい者手帳の所持者数</t>
+          <t>１　人口の推移</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-32）】手帳を所持していないが対象疾病に該当してサービスを利用している方、又は利用しうる方の人数を確認し</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr"/>
+          <t>区分 / 令和８年度 （現状） / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>表２-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -6086,27 +6082,31 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>６　障がい児の就学状況</t>
+          <t>２　障がい者手帳の所持者数</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>学校名 / 小学部 / 中学部 / 高等部</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-32）】手帳を所持していないが対象疾病に該当してサービスを利用している方、又は利用しうる方の人数を確認し</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>表２-3</t>
+          <t>表２-2</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -6120,14 +6120,14 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>学校名 / 在籍者数</t>
+          <t>学校名 / 小学部 / 中学部 / 高等部</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr"/>
@@ -6136,7 +6136,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>表２-4</t>
+          <t>表２-3</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -6146,18 +6146,18 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>７　アンケート調査の実施と結果</t>
+          <t>６　障がい児の就学状況</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>項目 / 障がい者調査 / 障がい児調査</t>
+          <t>学校名 / 在籍者数</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
@@ -6166,7 +6166,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>表２-5</t>
+          <t>表２-4</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -6183,11 +6183,11 @@
         <v>4</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>調査区分 / 配布数 / 有効回答数 / 有効回答率</t>
+          <t>項目 / 障がい者調査 / 障がい児調査</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr"/>
@@ -6196,7 +6196,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>表２-6</t>
+          <t>表２-5</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -6210,14 +6210,14 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>分野 / 主な調査結果 / 割合</t>
+          <t>調査区分 / 配布数 / 有効回答数 / 有効回答率</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -6226,7 +6226,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>表２-7</t>
+          <t>表２-6</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -6240,27 +6240,23 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>項目 / 全体 （n=38） / 身体障がい （n=29） / 知的障がい （n=2）</t>
+          <t>分野 / 主な調査結果 / 割合</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>表２-8</t>
+          <t>表２-7</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -6274,57 +6270,57 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>主な課題 / 主な調査結果 / 本計画での主な対応（関連箇所）</t>
+          <t>項目 / 全体 （n=38） / 身体障がい （n=29） / 知的障がい （n=2）</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表２-8</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>第３章　第４次北塩原</t>
+          <t>第２章　本村の障がい</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>１　基本理念</t>
+          <t>７　アンケート調査の実施と結果</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr"/>
+          <t>主な課題 / 主な調査結果 / 本計画での主な対応（関連箇所）</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>表３-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -6334,27 +6330,31 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>３　基本施策の目標値と本計画期間</t>
+          <t>１　基本理念</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>基本施策 / 指標項目 / 現状 （R5） / 目標 （R11）</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
+          <t>「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>表３-2</t>
+          <t>表３-1</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -6368,14 +6368,14 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>区分 / 意味</t>
+          <t>基本施策 / 指標項目 / 現状 （R5） / 目標 （R11）</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr"/>
@@ -6384,28 +6384,28 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>表４-1</t>
+          <t>表３-2</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第４章　障がい福祉計</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>１　第７期計画の成果目標の達成状</t>
+          <t>３　基本施策の目標値と本計画期間</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+          <t>区分 / 意味</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -6414,7 +6414,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -6424,31 +6424,27 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>２　令和11年度に向けた成果目標</t>
+          <t>１　第７期計画の成果目標の達成状</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr"/>
+          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>表４-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -6462,23 +6458,27 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>表４-3</t>
+          <t>表４-2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -6492,14 +6492,14 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr"/>
@@ -6508,7 +6508,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-3</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -6522,22 +6522,18 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr"/>
+          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -6563,7 +6559,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+          <t>【村へ確認（M-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -6576,7 +6572,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>表４-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -6590,23 +6586,27 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>表４-5</t>
+          <t>表４-4</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -6620,14 +6620,14 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr"/>
@@ -6636,7 +6636,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>表４-6</t>
+          <t>表４-5</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -6650,14 +6650,14 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>項目 / 値 / 考え方</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -6666,7 +6666,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-6</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -6680,26 +6680,18 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-６）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>項目 / 値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -6725,7 +6717,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【県へ確認（Ｓ-６）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -6733,7 +6725,11 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -6759,7 +6755,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+          <t>【村へ確認（M-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -6772,7 +6768,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>表４-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -6786,23 +6782,27 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>表４-7</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -6816,14 +6816,14 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr"/>
@@ -6832,7 +6832,7 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -6846,22 +6846,18 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -6887,7 +6883,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -6900,7 +6896,7 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -6914,23 +6910,27 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -6944,27 +6944,23 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -6978,23 +6974,27 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -7008,22 +7008,18 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -7049,7 +7045,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -7062,7 +7058,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7076,23 +7072,27 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr"/>
-      <c r="H51" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -7106,14 +7106,14 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr"/>
@@ -7122,7 +7122,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -7136,27 +7136,23 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr"/>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -7170,23 +7166,27 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -7200,27 +7200,23 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7234,23 +7230,27 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -7264,22 +7264,18 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -7305,7 +7301,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -7318,7 +7314,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7332,23 +7328,27 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7358,18 +7358,18 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
@@ -7378,28 +7378,28 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr"/>
@@ -7408,7 +7408,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7425,11 +7425,11 @@
         <v>11</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7482,14 +7482,14 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -7498,7 +7498,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr"/>
@@ -7528,7 +7528,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -7542,14 +7542,14 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E66" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E66" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -7558,7 +7558,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -7572,27 +7572,23 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr"/>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -7606,23 +7602,27 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
@@ -7652,7 +7652,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -7666,22 +7666,18 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -7707,7 +7703,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援４人、生活介護及び就労継続支援Ｂ型の利用者について、計画期間の開始前から引き続き利用</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -7720,7 +7716,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -7734,23 +7730,27 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-23）】施設入所支援４人、生活介護及び就労継続支援Ｂ型の利用者について、計画期間の開始前から引き続き利用</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
@@ -7780,7 +7780,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -7794,14 +7794,14 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E74" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -7810,7 +7810,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -7850,18 +7850,18 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E76" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E76" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -7870,7 +7870,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7884,27 +7884,23 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -7918,23 +7914,27 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -7948,22 +7948,18 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -7989,7 +7985,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -8002,7 +7998,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8016,23 +8012,27 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8046,14 +8046,14 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
@@ -8062,7 +8062,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8076,14 +8076,14 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr"/>
@@ -8092,7 +8092,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8106,27 +8106,23 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8140,23 +8136,27 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8170,27 +8170,23 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8204,23 +8200,27 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8234,27 +8234,23 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8264,27 +8260,31 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8294,18 +8294,18 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr"/>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D91" s="8" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8358,18 +8358,18 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr"/>
@@ -8378,7 +8378,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8388,27 +8388,31 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8418,26 +8422,22 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D95" s="8" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
@@ -8476,7 +8476,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8486,18 +8486,18 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -8516,18 +8516,18 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D98" s="6" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -8570,7 +8570,7 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -8580,18 +8580,18 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E99" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
@@ -8600,7 +8600,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -8610,31 +8610,27 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -8644,27 +8640,31 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -8674,27 +8674,31 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -8704,31 +8708,27 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr"/>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -8738,18 +8738,18 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E104" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr"/>
@@ -8758,7 +8758,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -8768,26 +8768,22 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -8802,7 +8798,7 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
@@ -8813,7 +8809,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -8836,18 +8832,18 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
@@ -8856,7 +8852,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -8866,27 +8862,31 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -8896,31 +8896,27 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -8930,120 +8926,120 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>分野 / 関係機関 / 連携の内容</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -9053,12 +9049,12 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
@@ -9069,7 +9065,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -9082,28 +9078,28 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D115" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
@@ -9112,122 +9108,126 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E117" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="9" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
@@ -9236,62 +9236,62 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9305,12 +9305,12 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -9334,28 +9334,28 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr"/>
@@ -9364,58 +9364,62 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9424,32 +9428,280 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E126" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr"/>
       <c r="H126" s="9" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>表７-3</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>表７-4</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>４　北塩原村こども・子育て計画と</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>確かめる事項 / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>４　北塩原村こども・子育て計画と</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>表８-1</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>２　北塩原村障がい者自立支援協議</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="9" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>表８-2</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>３　計画の策定経過</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="9" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表129点のうち、直後に出所らしき行があるのは6点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表129点のうち、直後に出所らしき行があるのは20点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図27点／表129点／規約8件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図27点／表129点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>なお、本計画の策定にあたっては、国の基本指針に即するとともに、福島県の障がい</t>
+          <t>表１-１　本計画を構成する計画と根拠法令</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>また、北塩原村第五次総合振興計画の施策体系におい</t>
+          <t>図１-１　計画の位置づけ</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>第２章　本村の障がい者の現状</t>
+          <t>図１-２　障がい福祉計画におけるＰＤＣＡサイクル</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>資料：住民基本台帳（各年４月１日現在）</t>
+          <t>図２-１　年齢３区分別人口の推移</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>（各年４月１日現在）</t>
+          <t>図２-２　障がい者手帳所持者数の推移</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>（各年４月１日現在）</t>
+          <t>図２-３　身体障がい者の推移</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>（令和８年４月１日現在）</t>
+          <t>図２-４　身体障害者手帳所持者の障がい種別の内訳</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>（各年４月１日現在）</t>
+          <t>図２-５　知的障がい者の推移</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>（各年４月１日現在）</t>
+          <t>図２-６　精神障がい者の推移</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>（令和８年４月１日現在）</t>
+          <t>図２-７　精神障害者保健福祉手帳所持者の障がい程</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>資料：障がい福祉に関するアンケート調査（令和８年</t>
+          <t>図２-８　外出するときに困ること</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>資料：障がい福祉に関するアンケート調査（令和８年</t>
+          <t>図２-９　現在利用しているサービスと今後３年間で</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>資料：障がい福祉に関するアンケート調査（令和８年</t>
+          <t>図２-10　災害時に不安なこと</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>資料：障がい福祉に関するアンケート調査（令和８年</t>
+          <t>図２-11　今後、村が特に力を入れるべきこと（３</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>（障がい者調査、割合は各区分の回答者数に対する割合）</t>
+          <t>資料：障がい福祉に関するアンケート調査（令和８年）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>資料：障がい福祉に関するアンケート調査（令和８年</t>
+          <t>図２-12　主な項目の障がい別の状況（障がい者調</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>計画の体系</t>
+          <t>図３-１　計画の体系</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等には、相談、緊急時の受入れ及び対応、体験の機会及び場、専門</t>
+          <t>表４-12　地域生活支援拠点等の５つの機能と記録する実績</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等の５つの機能</t>
+          <t>図４-１　地域生活支援拠点等の５つの機能</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>（５）障がい児支援の提供体制の確保</t>
+          <t>図５-１　北塩原村の障がい福祉に関する圏域（概念</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>本村では、本人の身に何か起きたときの備えが場面ごとに分かれています。どの場面</t>
+          <t>表５-15　緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>緊急時に働く仕組み（４つの場面）</t>
+          <t>図５-２　緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時に介護保険へ移行するかどうかは、サービスの種類により扱いが異なり</t>
+          <t>表５-30　65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>65歳到達時の判定の流れ</t>
+          <t>図５-３　65歳到達時の判定の流れ</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>本村は人口2,316人（令和８年４月１日現在）の小規模な自治体であり、村内で</t>
+          <t>表５-33　関係機関と連携の内容</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>関係機関との連携</t>
+          <t>図５-４　関係機関との連携</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>（１）給付費の推移</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉サービス等に係る給付費の推移</t>
+          <t>図５-５　障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>（３）サービス別の構成（令和７年度）</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>サービス別の給付費（令和７年度）</t>
+          <t>図５-６　サービス別の給付費（令和７年度）</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>（１）高齢化率</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>高齢化率の推移</t>
+          <t>図６-１　高齢化率の推移</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッドヘルスプランと</t>
+          <t>図７-１　他の計画との関係</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -6221,7 +6221,11 @@
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="9" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -6251,7 +6255,11 @@
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="9" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6379,7 +6387,11 @@
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="9" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -6439,7 +6451,11 @@
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="9" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -7463,7 +7479,11 @@
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="9" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -7523,7 +7543,11 @@
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="9" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -7647,7 +7671,11 @@
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="9" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -7775,7 +7803,11 @@
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="9" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -7835,7 +7867,11 @@
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="9" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -8501,7 +8537,11 @@
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="9" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -9103,7 +9143,11 @@
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="9" t="inlineStr"/>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -9133,7 +9177,11 @@
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="9" t="inlineStr"/>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
@@ -9231,7 +9279,11 @@
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
-      <c r="H119" s="9" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -9295,7 +9347,11 @@
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="9" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -10242,7 +10298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10403,15 +10459,32 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>出所を付けない表</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>手順・区分・確認事項を整理しただけの表（「確かめること／確かめ方」等）には出所を書かない。村の実績・アンケート・外部資料から数値を引いた図表にのみ付ける。表に「（単位：人、令和８年４月１日現在）」のような添え書きが既にあるときは、出所に基準日を重ねて書かない</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>整理の表は本計画の記述そのものであり、出所を書くと出どころが二重になる。令和8年10月10日の番号付与で足した補足（図表番号一覧 00シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>値のラベル</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>表が併記されている図は、最新年度と最大・最小だけにラベルを付ける。表がない図は全ての値にラベルを付ける</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>同じ数値を表と図の両方に全部書くと、直すときに片方が取り残される</t>
         </is>
@@ -10582,7 +10655,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>図表番号を振り、目次の後に図表目次を置くことを提案したい。番号の形（図１-１・表１-１）と、注記ボックスには番号を振らないことを合わせたい</t>
+          <t>図表番号を振り、目次の後に図表目次を置くことを提案したい。番号の形（図１-１・表１-１）と、注記ボックスには番号を振らないことを合わせたい。令和8年10月10日に当方で図24点・表84点に番号と表題を付け、図表目次を置いた（北塩原村_図表番号一覧.xlsx）。これに伴う確認3件はＳ-22〜Ｓ-24として同書に立てている</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図27点／表129点（データ表84・注記ボックス45）。図表番号は0件、図表目次もない</t>
+          <t>図28点／表132点（データ表86・注記ボックス46）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表129点のうち、直後に出所らしき行があるのは20点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表132点のうち、直後に出所らしき行があるのは20点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図27点／表129点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図28点／表132点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>表５-15　緊急時に働く仕組み（４つの場面）</t>
+          <t>表５-17　緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>表５-30　65歳到達時のサービスの区分</t>
+          <t>表５-30　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>図５-３　65歳到達時の判定の流れ</t>
+          <t>図５-３　ライフコースと制度の移行</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>1307×1220</t>
+          <t>1307×1312</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -1647,32 +1647,32 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>表５-33　関係機関と連携の内容</t>
+          <t>表５-32　65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>図５-４　関係機関との連携</t>
+          <t>図５-４　65歳到達時の判定の流れ</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>image20.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>1307×884</t>
+          <t>1307×1220</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>はじめからモノクロ</t>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>資料：村提供の障がいサービス給付実績</t>
+          <t>表５-35　関係機関と連携の内容</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>図５-５　障がい福祉サービス等に係る給付費の推移</t>
+          <t>図５-５　関係機関との連携</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image20.png</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>1112×614</t>
+          <t>1307×876</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>見分けられる</t>
+          <t>はじめからモノクロ</t>
         </is>
       </c>
     </row>
@@ -1741,17 +1741,17 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>図５-６　サービス別の給付費（令和７年度）</t>
+          <t>図５-６　障がい福祉サービス等に係る給付費の推移</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image16.png</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>1210×638</t>
+          <t>1112×614</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -1768,37 +1768,37 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>資料：北塩原村</t>
+          <t>資料：村提供の障がいサービス給付実績</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>図６-１　高齢化率の推移</t>
+          <t>図５-７　サービス別の給付費（令和７年度）</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>image18.png</t>
+          <t>image17.png</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>1046×591</t>
+          <t>1210×638</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>はじめからモノクロ</t>
+          <t>見分けられる</t>
         </is>
       </c>
     </row>
@@ -1810,37 +1810,37 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>本計画の推進にあたっては、本村の関連計画と整合を図り、連携して施策を推進する</t>
+          <t>資料：北塩原村</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>図７-１　他の計画との関係</t>
+          <t>図６-１　高齢化率の推移</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>image12.png</t>
+          <t>image18.png</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>1223×1286</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>潰れる</t>
+          <t>1046×591</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>はじめからモノクロ</t>
         </is>
       </c>
     </row>
@@ -1852,33 +1852,37 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0241－23－3113（直通）</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
+          <t>本計画の推進にあたっては、本村の関連計画と整合を図り、連携して施策を推進する</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>図７-１　他の計画との関係</t>
+        </is>
+      </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>image13.png</t>
+          <t>image12.png</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>501×132</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>見分けられる</t>
+          <t>1223×1286</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>潰れる</t>
         </is>
       </c>
     </row>
@@ -1906,15 +1910,53 @@
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>501×132</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>図28</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>0241－23－3113（直通）</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
           <t>image14.jpeg</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>128×128</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>見分けられる</t>
         </is>
@@ -1935,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4393,20 +4435,16 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>(153,153,153)</t>
+          <t>(244,189,112)</t>
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -4421,11 +4459,11 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>(181,181,181)</t>
+          <t>(176,176,176)</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E96" s="8" t="n">
         <v>0</v>
@@ -4449,14 +4487,14 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>(234,244,238)</t>
+          <t>(223,223,223)</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
@@ -4477,20 +4515,16 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>(132,132,132)</t>
+          <t>(128,196,165)</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -4505,16 +4539,20 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>(105,186,149)</t>
+          <t>(206,206,206)</t>
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="F99" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
@@ -4529,44 +4567,44 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>(244,187,107)</t>
+          <t>(138,138,138)</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>137</v>
-      </c>
-      <c r="F100" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>図21</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>image20.png</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>(149,149,149)</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="n">
-        <v>149</v>
-      </c>
-      <c r="E101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>図20</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>(255,246,231)</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>247</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -4576,16 +4614,16 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>image20.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>(201,201,201)</t>
+          <t>(153,153,153)</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="E102" s="6" t="n">
         <v>0</v>
@@ -4604,19 +4642,19 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>image20.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>(234,244,238)</t>
+          <t>(181,181,181)</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
@@ -4632,19 +4670,19 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>image20.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>(114,114,114)</t>
+          <t>(234,244,238)</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>114</v>
+        <v>240</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -4660,16 +4698,16 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>image20.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>(98,98,98)</t>
+          <t>(132,132,132)</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="E105" s="6" t="n">
         <v>0</v>
@@ -4681,56 +4719,52 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>図22</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="inlineStr">
-        <is>
-          <t>(37,154,100)</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="F106" s="4" t="inlineStr"/>
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>image24.png</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>(105,186,149)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="F106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>図22</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>image16.png</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>(221,221,221)</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="n">
-        <v>221</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>図21</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>image24.png</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>(244,187,107)</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="E107" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="F107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -4740,16 +4774,16 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image20.png</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>(215,215,215)</t>
+          <t>(152,152,152)</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="E108" s="8" t="n">
         <v>0</v>
@@ -4768,16 +4802,16 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image20.png</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>(129,129,129)</t>
+          <t>(212,212,212)</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="E109" s="8" t="n">
         <v>0</v>
@@ -4796,19 +4830,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image20.png</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>(164,164,164)</t>
+          <t>(234,244,238)</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
@@ -4824,16 +4858,16 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>image16.png</t>
+          <t>image20.png</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>(90,90,90)</t>
+          <t>(101,101,101)</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E111" s="8" t="n">
         <v>0</v>
@@ -4845,28 +4879,32 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>図23</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>image17.png</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>(36,154,100)</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="n">
-        <v>113</v>
-      </c>
-      <c r="E112" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="F112" s="5" t="inlineStr"/>
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>図22</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>image20.png</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>(100,100,100)</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -4876,25 +4914,21 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image16.png</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>(228,228,228)</t>
+          <t>(37,154,100)</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>228</v>
+        <v>113</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="F113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -4904,19 +4938,19 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image16.png</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>(211,206,208)</t>
+          <t>(221,221,221)</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
@@ -4932,16 +4966,16 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image16.png</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>(81,81,81)</t>
+          <t>(215,215,215)</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="E115" s="6" t="n">
         <v>0</v>
@@ -4960,16 +4994,16 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>image17.png</t>
+          <t>image16.png</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>(165,165,165)</t>
+          <t>(129,129,129)</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E116" s="6" t="n">
         <v>0</v>
@@ -4981,56 +5015,56 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t>図24</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>(217,217,217)</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="n">
-        <v>217</v>
-      </c>
-      <c r="E117" s="8" t="n">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>図23</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>(164,164,164)</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="E117" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="F117" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>図24</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>image18.png</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>(227,227,227)</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="n">
-        <v>227</v>
-      </c>
-      <c r="E118" s="8" t="n">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>図23</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>image16.png</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>(90,90,90)</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E118" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
@@ -5044,25 +5078,21 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>image18.png</t>
+          <t>image17.png</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>(154,154,154)</t>
+          <t>(36,154,100)</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="F119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -5072,16 +5102,16 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>image18.png</t>
+          <t>image17.png</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>(91,91,91)</t>
+          <t>(228,228,228)</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>91</v>
+        <v>228</v>
       </c>
       <c r="E120" s="8" t="n">
         <v>0</v>
@@ -5093,84 +5123,88 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>図25</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>(102,163,218)</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="n">
-        <v>151</v>
-      </c>
-      <c r="E121" s="6" t="n">
-        <v>116</v>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>図24</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>(211,206,208)</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>208</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>図25</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>(222,100,134)</t>
-        </is>
-      </c>
-      <c r="D122" s="9" t="n">
-        <v>140</v>
-      </c>
-      <c r="E122" s="6" t="n">
-        <v>122</v>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>図24</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>(81,81,81)</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>図25</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>(239,181,63)</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="n">
-        <v>185</v>
-      </c>
-      <c r="E123" s="6" t="n">
-        <v>176</v>
-      </c>
-      <c r="F123" s="5" t="inlineStr"/>
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>図24</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>image17.png</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>(165,165,165)</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -5180,21 +5214,25 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>image12.png</t>
+          <t>image18.png</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>(27,52,97)</t>
+          <t>(217,217,217)</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>50</v>
+        <v>217</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="F124" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -5204,352 +5242,540 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>(227,227,227)</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>227</v>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>(154,154,154)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="n">
+        <v>154</v>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>(91,91,91)</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E127" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
           <t>image12.png</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>(102,163,218)</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>116</v>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>(222,100,134)</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>(239,181,63)</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="n">
+        <v>185</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>176</v>
+      </c>
+      <c r="F130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>(27,52,97)</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="F131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
         <is>
           <t>(210,231,197)</t>
         </is>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D132" s="8" t="n">
         <v>221</v>
       </c>
-      <c r="E125" s="6" t="n">
+      <c r="E132" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="F125" s="5" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>図26</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="F132" s="4" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>image13.png</t>
         </is>
       </c>
-      <c r="C126" s="8" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
         <is>
           <t>(29,93,59)</t>
         </is>
       </c>
-      <c r="D126" s="8" t="n">
+      <c r="D133" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="E126" s="8" t="n">
+      <c r="E133" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="F126" s="4" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>図26</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>image13.png</t>
         </is>
       </c>
-      <c r="C127" s="8" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>(214,214,214)</t>
         </is>
       </c>
-      <c r="D127" s="8" t="n">
+      <c r="D134" s="6" t="n">
         <v>214</v>
       </c>
-      <c r="E127" s="8" t="n">
+      <c r="E134" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="4" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
         <is>
           <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>図27</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>図28</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>image14.jpeg</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C135" s="8" t="inlineStr">
         <is>
           <t>(227,215,193)</t>
         </is>
       </c>
-      <c r="D128" s="6" t="n">
+      <c r="D135" s="8" t="n">
         <v>216</v>
       </c>
-      <c r="E128" s="6" t="n">
+      <c r="E135" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="F128" s="5" t="inlineStr"/>
-    </row>
-    <row r="130" ht="30" customHeight="1">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="F135" s="4" t="inlineStr"/>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>潰れる組</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>グレー値の差</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>どこに出るか</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>RGB(37, 78, 147) と RGB(192, 0, 0)</t>
-        </is>
-      </c>
-      <c r="B131" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>図2 ほか（image2.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>RGB(34, 127, 166) と RGB(57, 131, 197)</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>RGB(34, 127, 166) と RGB(121, 90, 166)</t>
-        </is>
-      </c>
-      <c r="B133" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>RGB(57, 131, 197) と RGB(121, 90, 166)</t>
-        </is>
-      </c>
-      <c r="B134" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="10" t="inlineStr">
-        <is>
-          <t>RGB(239, 156, 39) と RGB(142, 207, 164)</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>図4 ほか（image4.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>RGB(37, 154, 101) と RGB(53, 129, 196)</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>図5 ほか（image5.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="10" t="inlineStr">
-        <is>
-          <t>RGB(46, 158, 107) と RGB(61, 134, 198)</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>RGB(46, 158, 107) と RGB(148, 115, 192)</t>
+          <t>RGB(37, 78, 147) と RGB(192, 0, 0)</t>
         </is>
       </c>
       <c r="B138" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>図7 ほか（image7.png）</t>
+          <t>図2 ほか（image2.png）</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>RGB(61, 134, 198) と RGB(148, 115, 192)</t>
+          <t>RGB(34, 127, 166) と RGB(57, 131, 197)</t>
         </is>
       </c>
       <c r="B139" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>図7 ほか（image7.png）</t>
+          <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>RGB(42, 156, 104) と RGB(61, 134, 198)</t>
+          <t>RGB(34, 127, 166) と RGB(121, 90, 166)</t>
         </is>
       </c>
       <c r="B140" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>図8 ほか（image8.png）</t>
+          <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>RGB(46, 158, 107) と RGB(59, 133, 197)</t>
+          <t>RGB(57, 131, 197) と RGB(121, 90, 166)</t>
         </is>
       </c>
       <c r="B141" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>図10 ほか（image10.png）</t>
+          <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>RGB(103, 163, 218) と RGB(137, 192, 106)</t>
+          <t>RGB(239, 156, 39) と RGB(142, 207, 164)</t>
         </is>
       </c>
       <c r="B142" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>図18 ほか（image11.png）</t>
+          <t>図4 ほか（image4.png）</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>RGB(252, 228, 214) と RGB(219, 234, 223)</t>
+          <t>RGB(37, 154, 101) と RGB(53, 129, 196)</t>
         </is>
       </c>
       <c r="B143" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>図18 ほか（image11.png）</t>
+          <t>図5 ほか（image5.png）</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>RGB(252, 228, 214) と RGB(210, 230, 211)</t>
+          <t>RGB(46, 158, 107) と RGB(61, 134, 198)</t>
         </is>
       </c>
       <c r="B144" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>図18 ほか（image11.png）</t>
+          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>RGB(219, 234, 223) と RGB(210, 230, 211)</t>
+          <t>RGB(46, 158, 107) と RGB(148, 115, 192)</t>
         </is>
       </c>
       <c r="B145" s="8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>図18 ほか（image11.png）</t>
+          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
+          <t>RGB(61, 134, 198) と RGB(148, 115, 192)</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>図7 ほか（image7.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>RGB(42, 156, 104) と RGB(61, 134, 198)</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>図8 ほか（image8.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>RGB(46, 158, 107) と RGB(59, 133, 197)</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>図10 ほか（image10.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>RGB(103, 163, 218) と RGB(137, 192, 106)</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>RGB(252, 228, 214) と RGB(219, 234, 223)</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>RGB(252, 228, 214) と RGB(210, 230, 211)</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>RGB(219, 234, 223) と RGB(210, 230, 211)</t>
+        </is>
+      </c>
+      <c r="B152" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
           <t>RGB(102, 163, 218) と RGB(222, 100, 134)</t>
         </is>
       </c>
-      <c r="B146" s="8" t="n">
+      <c r="B153" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>図25 ほか（image12.png）</t>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>図26 ほか（image12.png）</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7468,22 +7694,18 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -7509,11 +7731,15 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -7532,22 +7758,18 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E65" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -7566,14 +7788,14 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -7582,7 +7804,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -7596,23 +7818,27 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -7626,22 +7852,22 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -7660,22 +7886,18 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E69" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -7694,14 +7916,14 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -7731,7 +7953,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -7744,7 +7966,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -7758,27 +7980,27 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援４人、生活介護及び就労継続支援Ｂ型の利用者について、計画期間の開始前から引き続き利用</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -7799,20 +8021,16 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -7826,23 +8044,27 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -7856,27 +8078,27 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-23）】施設入所支援４人、生活介護及び就労継続支援Ｂ型の利用者について、計画期間の開始前から引き続き利用</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -7890,23 +8112,27 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="9" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -7916,18 +8142,18 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D77" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E77" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
@@ -7936,7 +8162,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -7946,26 +8172,26 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -7980,18 +8206,18 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr"/>
@@ -8000,7 +8226,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8014,22 +8240,18 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -8055,7 +8277,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
@@ -8068,7 +8290,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8082,14 +8304,14 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
@@ -8098,7 +8320,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8112,23 +8334,27 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8142,23 +8368,27 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8172,22 +8402,18 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr"/>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -8206,14 +8432,14 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
@@ -8222,7 +8448,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8236,27 +8462,23 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8270,23 +8492,27 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8300,27 +8526,23 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8334,23 +8556,27 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8364,27 +8590,23 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H91" s="8" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8398,23 +8620,27 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8428,27 +8654,23 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8462,23 +8684,27 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8492,27 +8718,23 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8522,26 +8744,26 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -8556,18 +8778,18 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
@@ -8586,7 +8808,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D98" s="6" t="n">
@@ -8597,7 +8819,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -8624,18 +8846,22 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -8654,14 +8880,14 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr"/>
@@ -8691,7 +8917,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -8704,7 +8930,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -8714,31 +8940,27 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -8748,18 +8970,18 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D103" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
@@ -8768,7 +8990,7 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -8778,27 +9000,31 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -8808,27 +9034,31 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -8838,26 +9068,22 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr"/>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -8876,14 +9102,14 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E107" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
@@ -8892,7 +9118,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -8906,27 +9132,23 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -8940,18 +9162,22 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -8977,7 +9203,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr"/>
@@ -9007,7 +9233,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
@@ -9030,18 +9256,18 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr"/>
@@ -9050,7 +9276,7 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9060,26 +9286,22 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -9094,7 +9316,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
@@ -9105,7 +9327,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -9118,7 +9340,7 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9128,31 +9350,27 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+          <t>分野 / 関係機関 / 連携の内容</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9162,31 +9380,31 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9196,31 +9414,31 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9234,48 +9452,48 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr"/>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
@@ -9288,28 +9506,28 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr"/>
@@ -9322,41 +9540,41 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9366,31 +9584,31 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr"/>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9400,27 +9618,31 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="9" t="inlineStr"/>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9430,82 +9652,86 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E126" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr"/>
@@ -9514,37 +9740,41 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -9554,31 +9784,27 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -9588,7 +9814,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
@@ -9599,7 +9825,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
@@ -9608,7 +9834,7 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -9618,82 +9844,82 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E132" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
@@ -9702,37 +9928,41 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -9742,22 +9972,112 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr"/>
       <c r="H134" s="9" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>表８-2</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>３　計画の策定経過</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="9" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="9" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図28点／表132点（データ表86・注記ボックス46）。図表番号は0件、図表目次もない</t>
+          <t>図28点／表134点（データ表87・注記ボックス47）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表132点のうち、直後に出所らしき行があるのは20点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表134点のうち、直後に出所らしき行があるのは20点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図28点／表132点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図28点／表134点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>表５-17　緊急時に働く仕組み（４つの場面）</t>
+          <t>表５-18　緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>表５-30　年齢到達に伴うサービスの移行</t>
+          <t>表５-31　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>表５-32　65歳到達時のサービスの区分</t>
+          <t>表５-33　65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>表５-35　関係機関と連携の内容</t>
+          <t>表５-36　関係機関と連携の内容</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -5794,7 +5794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7724,27 +7724,23 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>加減 / 項目 / 拠り所</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H64" s="9" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7758,23 +7754,27 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="9" t="inlineStr"/>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -7788,23 +7788,27 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -7818,22 +7822,18 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -7852,27 +7852,23 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -7886,23 +7882,27 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -7916,23 +7916,27 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E70" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E70" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -7946,22 +7950,18 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -7980,27 +7980,23 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8014,23 +8010,27 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8044,27 +8044,27 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8078,27 +8078,23 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援４人、生活介護及び就労継続支援Ｂ型の利用者について、計画期間の開始前から引き続き利用</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8112,27 +8108,27 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8146,23 +8142,27 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E78" s="6" t="n">
         <v>5</v>
@@ -8196,7 +8196,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E79" s="8" t="n">
         <v>5</v>
@@ -8226,7 +8226,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8236,27 +8236,31 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E80" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E80" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="9" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8266,26 +8270,22 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H81" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -8304,14 +8304,14 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8368,27 +8368,23 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8402,23 +8398,27 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8432,23 +8432,27 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8465,11 +8469,11 @@
         <v>5</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
@@ -8478,7 +8482,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8492,22 +8496,18 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr"/>
+          <t>備える事項 / 本村の取組み</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -8526,14 +8526,14 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr"/>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -8593,11 +8593,11 @@
         <v>7</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -8654,14 +8654,14 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -8718,14 +8718,14 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -8785,11 +8785,11 @@
         <v>5</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -8842,31 +8842,27 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -8876,27 +8872,31 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -8910,22 +8910,22 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -8944,14 +8944,14 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr"/>
@@ -8960,7 +8960,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -8974,23 +8974,27 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9004,27 +9008,23 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9034,31 +9034,27 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9068,27 +9064,31 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9098,27 +9098,31 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr"/>
-      <c r="H107" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9128,18 +9132,18 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr"/>
@@ -9148,7 +9152,7 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9162,22 +9166,18 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="inlineStr"/>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -9196,14 +9196,14 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
@@ -9260,14 +9260,14 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr"/>
@@ -9276,7 +9276,7 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9290,23 +9290,27 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9320,22 +9324,18 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr"/>
+          <t>確認する事項 / 確認の内容</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -9350,18 +9350,18 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E115" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -9404,7 +9404,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9418,27 +9418,23 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9448,31 +9444,31 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9482,31 +9478,31 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr"/>
-      <c r="H119" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9520,14 +9516,14 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr"/>
@@ -9540,7 +9536,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9554,48 +9550,48 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr"/>
@@ -9608,41 +9604,41 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9656,14 +9652,14 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr"/>
@@ -9676,7 +9672,7 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9686,31 +9682,31 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9720,22 +9716,26 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
@@ -9774,28 +9774,28 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr"/>
@@ -9804,37 +9804,41 @@
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -9844,18 +9848,18 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr"/>
@@ -9864,7 +9868,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -9874,31 +9878,27 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H131" s="8" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="9" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -9908,18 +9908,18 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E132" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr">
@@ -9962,28 +9962,28 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr"/>
@@ -9992,37 +9992,41 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10032,18 +10036,18 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10052,7 +10056,7 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10062,22 +10066,82 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E137" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr"/>
       <c r="H137" s="9" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="9" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図28点／表134点（データ表87・注記ボックス47）。図表番号は0件、図表目次もない</t>
+          <t>図28点／表135点（データ表88・注記ボックス47）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表134点のうち、直後に出所らしき行があるのは20点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表135点のうち、直後に出所らしき行があるのは20点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図28点／表134点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図28点／表135点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -5794,7 +5794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6554,41 +6554,37 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表２-9</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>第３章　第４次北塩原</t>
+          <t>第２章　本村の障がい</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>１　基本理念</t>
+          <t>７　アンケート調査の実施と結果</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr"/>
+          <t>用いること / 本村での例</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>表３-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -6598,31 +6594,31 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>３　基本施策の目標値と本計画期間</t>
+          <t>１　基本理念</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>基本施策 / 指標項目 / 現状 （R5） / 目標 （R11）</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>表３-2</t>
+          <t>表３-1</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -6636,57 +6632,57 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>区分 / 意味</t>
+          <t>基本施策 / 指標項目 / 現状 （R5） / 目標 （R11）</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="9" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>表４-1</t>
+          <t>表３-2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>第４章　障がい福祉計</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>１　第７期計画の成果目標の達成状</t>
+          <t>３　基本施策の目標値と本計画期間</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+          <t>区分 / 意味</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-1</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -6696,31 +6692,31 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>２　令和11年度に向けた成果目標</t>
+          <t>１　第７期計画の成果目標の達成状</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
+          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>表４-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -6734,23 +6730,27 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>表４-3</t>
+          <t>表４-2</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -6764,14 +6764,14 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr"/>
@@ -6780,7 +6780,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-3</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -6794,22 +6794,18 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr"/>
+          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -6835,7 +6831,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+          <t>【村へ確認（M-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -6848,7 +6844,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>表４-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -6862,23 +6858,27 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>表４-5</t>
+          <t>表４-4</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -6892,14 +6892,14 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -6908,7 +6908,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>表４-6</t>
+          <t>表４-5</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -6922,14 +6922,14 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>項目 / 値 / 考え方</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-6</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -6952,26 +6952,18 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-６）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>項目 / 値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -6997,7 +6989,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【県へ確認（Ｓ-６）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -7005,7 +6997,11 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -7031,7 +7027,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+          <t>【村へ確認（M-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -7044,7 +7040,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>表４-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -7058,23 +7054,27 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>表４-7</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -7088,14 +7088,14 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr"/>
@@ -7104,7 +7104,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -7118,22 +7118,18 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -7159,7 +7155,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -7172,7 +7168,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -7186,23 +7182,27 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr"/>
-      <c r="H47" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7216,27 +7216,23 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -7250,23 +7246,27 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7280,22 +7280,18 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -7321,7 +7317,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -7334,7 +7330,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -7348,23 +7344,27 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -7378,14 +7378,14 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E53" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr"/>
@@ -7394,7 +7394,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -7408,27 +7408,23 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr"/>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -7442,23 +7438,27 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr"/>
-      <c r="H55" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7472,27 +7472,23 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -7506,23 +7502,27 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7536,22 +7536,18 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -7577,7 +7573,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -7590,7 +7586,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7604,23 +7600,27 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7630,18 +7630,18 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr"/>
@@ -7650,28 +7650,28 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -7680,7 +7680,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7694,14 +7694,14 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr"/>
@@ -7710,7 +7710,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7724,14 +7724,14 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -7740,7 +7740,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7754,27 +7754,23 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -7788,27 +7784,27 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -7829,16 +7825,20 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="9" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -7852,14 +7852,14 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
@@ -7868,7 +7868,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -7882,27 +7882,23 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -7916,27 +7912,27 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -7957,16 +7953,20 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -7980,14 +7980,14 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E72" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E72" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -7996,7 +7996,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8010,27 +8010,23 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr"/>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8044,27 +8040,27 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8085,16 +8081,20 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="9" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8108,22 +8108,18 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -8149,7 +8145,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
@@ -8162,7 +8158,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8176,27 +8172,27 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8217,16 +8213,20 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8240,27 +8240,23 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E80" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8281,16 +8277,20 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8300,18 +8300,18 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E82" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
@@ -8320,7 +8320,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8334,27 +8334,23 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H83" s="8" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8368,23 +8364,27 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8398,22 +8398,18 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -8439,7 +8435,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -8452,7 +8448,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8466,23 +8462,27 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8496,14 +8496,14 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
@@ -8512,7 +8512,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8526,14 +8526,14 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E89" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr"/>
@@ -8542,7 +8542,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8556,27 +8556,23 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8590,23 +8586,27 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8620,27 +8620,23 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8654,23 +8650,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8684,27 +8684,23 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8718,23 +8714,27 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8748,27 +8748,23 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -8782,23 +8778,27 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -8812,27 +8812,23 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -8846,23 +8842,27 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -8876,27 +8876,23 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -8906,31 +8902,31 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -8951,16 +8947,20 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -8974,27 +8974,23 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9008,23 +9004,27 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9038,14 +9038,14 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
@@ -9054,7 +9054,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9068,22 +9068,18 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -9098,7 +9094,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D107" s="8" t="n">
@@ -9109,7 +9105,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -9122,7 +9118,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9136,23 +9132,27 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9162,18 +9162,18 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr"/>
@@ -9182,7 +9182,7 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9196,14 +9196,14 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr"/>
@@ -9212,7 +9212,7 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9226,27 +9226,23 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9260,23 +9256,27 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9290,27 +9290,23 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9324,23 +9320,27 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9354,14 +9354,14 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
@@ -9370,7 +9370,7 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9384,27 +9384,23 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9414,27 +9410,31 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9448,22 +9448,18 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -9489,7 +9485,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
@@ -9502,7 +9498,7 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9512,31 +9508,31 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9550,14 +9546,14 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E121" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E121" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9570,7 +9566,7 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9584,14 +9580,14 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E122" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr"/>
@@ -9604,7 +9600,7 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9618,61 +9614,61 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="inlineStr"/>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9686,14 +9682,14 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E125" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9706,7 +9702,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9720,14 +9716,14 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr"/>
@@ -9740,7 +9736,7 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9750,31 +9746,31 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H127" s="8" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -9788,23 +9784,27 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -9814,61 +9814,61 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H129" s="8" t="inlineStr"/>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -9878,18 +9878,18 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
@@ -9898,7 +9898,7 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -9908,18 +9908,18 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E132" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
@@ -9928,7 +9928,7 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -9942,27 +9942,23 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -9972,27 +9968,31 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10006,57 +10006,57 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H135" s="8" t="inlineStr"/>
+          <t>確かめる事項 / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10066,18 +10066,18 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr"/>
@@ -10086,7 +10086,7 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10096,18 +10096,18 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E138" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr"/>
@@ -10116,7 +10116,7 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-3</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10126,22 +10126,52 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>４　近年の障がい者施策の動向</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E139" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年 / 主な動向</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr"/>
       <c r="H139" s="9" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr"/>
+      <c r="H140" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図28点／表135点（データ表88・注記ボックス47）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表135点（データ表88・注記ボックス47）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図28点／表135点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表135点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>image23.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>image24.png</t>
+          <t>image25.png</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -1894,28 +1894,32 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　北塩原村高齢者福祉計画・</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>0241－23－3113（直通）</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
+          <t>二つめは成年後見制度の利用を支援する事業です。この名の事業は、障害者総合支援</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>図７-２　本計画と介護保険事業計画の関係</t>
+        </is>
+      </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>image13.png</t>
+          <t>image23.png</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>501×132</t>
+          <t>1307×1108</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -1948,15 +1952,53 @@
       <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>501×132</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>見分けられる</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>図29</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>0241－23－3113（直通）</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>image14.jpeg</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>128×128</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>見分けられる</t>
         </is>
@@ -1977,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4430,7 +4472,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>image23.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -4454,7 +4496,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>image23.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -4482,7 +4524,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>image23.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -4510,7 +4552,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>image23.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -4534,7 +4576,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>image23.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -4562,7 +4604,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>image23.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -4590,7 +4632,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>image23.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -4614,7 +4656,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>image24.png</t>
+          <t>image25.png</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -4642,7 +4684,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>image24.png</t>
+          <t>image25.png</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -4670,7 +4712,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>image24.png</t>
+          <t>image25.png</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -4698,7 +4740,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>image24.png</t>
+          <t>image25.png</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -4726,7 +4768,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>image24.png</t>
+          <t>image25.png</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -4750,7 +4792,7 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>image24.png</t>
+          <t>image25.png</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -5454,19 +5496,19 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>image13.png</t>
+          <t>image23.png</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>(29,93,59)</t>
+          <t>(243,180,92)</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>70</v>
+        <v>189</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="F133" s="5" t="inlineStr"/>
     </row>
@@ -5478,16 +5520,16 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>image13.png</t>
+          <t>image23.png</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>(214,214,214)</t>
+          <t>(152,152,152)</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="E134" s="6" t="n">
         <v>0</v>
@@ -5499,281 +5541,465 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>(219,219,219)</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="n">
+        <v>219</v>
+      </c>
+      <c r="E135" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>(134,134,134)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>(235,235,235)</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="n">
+        <v>235</v>
+      </c>
+      <c r="E137" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>(94,180,141)</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="F138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>図27</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>image23.png</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>(253,244,229)</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="n">
+        <v>245</v>
+      </c>
+      <c r="E139" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>図28</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>(29,93,59)</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>図28</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>image13.png</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>(214,214,214)</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>214</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>図29</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>image14.jpeg</t>
         </is>
       </c>
-      <c r="C135" s="8" t="inlineStr">
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>(227,215,193)</t>
         </is>
       </c>
-      <c r="D135" s="8" t="n">
+      <c r="D142" s="6" t="n">
         <v>216</v>
       </c>
-      <c r="E135" s="8" t="n">
+      <c r="E142" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="F135" s="4" t="inlineStr"/>
-    </row>
-    <row r="137" ht="30" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="F142" s="5" t="inlineStr"/>
+    </row>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>潰れる組</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t>グレー値の差</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>どこに出るか</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="10" t="inlineStr">
-        <is>
-          <t>RGB(37, 78, 147) と RGB(192, 0, 0)</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>図2 ほか（image2.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
-        <is>
-          <t>RGB(34, 127, 166) と RGB(57, 131, 197)</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="10" t="inlineStr">
-        <is>
-          <t>RGB(34, 127, 166) と RGB(121, 90, 166)</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="10" t="inlineStr">
-        <is>
-          <t>RGB(57, 131, 197) と RGB(121, 90, 166)</t>
-        </is>
-      </c>
-      <c r="B141" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>図3 ほか（image3.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="10" t="inlineStr">
-        <is>
-          <t>RGB(239, 156, 39) と RGB(142, 207, 164)</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>図4 ほか（image4.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="10" t="inlineStr">
-        <is>
-          <t>RGB(37, 154, 101) と RGB(53, 129, 196)</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>図5 ほか（image5.png）</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>RGB(46, 158, 107) と RGB(61, 134, 198)</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>RGB(46, 158, 107) と RGB(148, 115, 192)</t>
+          <t>RGB(37, 78, 147) と RGB(192, 0, 0)</t>
         </is>
       </c>
       <c r="B145" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>図7 ほか（image7.png）</t>
+          <t>図2 ほか（image2.png）</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>RGB(61, 134, 198) と RGB(148, 115, 192)</t>
+          <t>RGB(34, 127, 166) と RGB(57, 131, 197)</t>
         </is>
       </c>
       <c r="B146" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>図7 ほか（image7.png）</t>
+          <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>RGB(42, 156, 104) と RGB(61, 134, 198)</t>
+          <t>RGB(34, 127, 166) と RGB(121, 90, 166)</t>
         </is>
       </c>
       <c r="B147" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>図8 ほか（image8.png）</t>
+          <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>RGB(46, 158, 107) と RGB(59, 133, 197)</t>
+          <t>RGB(57, 131, 197) と RGB(121, 90, 166)</t>
         </is>
       </c>
       <c r="B148" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>図10 ほか（image10.png）</t>
+          <t>図3 ほか（image3.png）</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>RGB(103, 163, 218) と RGB(137, 192, 106)</t>
+          <t>RGB(239, 156, 39) と RGB(142, 207, 164)</t>
         </is>
       </c>
       <c r="B149" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>図18 ほか（image11.png）</t>
+          <t>図4 ほか（image4.png）</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>RGB(252, 228, 214) と RGB(219, 234, 223)</t>
+          <t>RGB(37, 154, 101) と RGB(53, 129, 196)</t>
         </is>
       </c>
       <c r="B150" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>図18 ほか（image11.png）</t>
+          <t>図5 ほか（image5.png）</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>RGB(252, 228, 214) と RGB(210, 230, 211)</t>
+          <t>RGB(46, 158, 107) と RGB(61, 134, 198)</t>
         </is>
       </c>
       <c r="B151" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>図18 ほか（image11.png）</t>
+          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>RGB(219, 234, 223) と RGB(210, 230, 211)</t>
+          <t>RGB(46, 158, 107) と RGB(148, 115, 192)</t>
         </is>
       </c>
       <c r="B152" s="8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>図18 ほか（image11.png）</t>
+          <t>図7 ほか（image7.png）</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
+          <t>RGB(61, 134, 198) と RGB(148, 115, 192)</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>図7 ほか（image7.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>RGB(42, 156, 104) と RGB(61, 134, 198)</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>図8 ほか（image8.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>RGB(46, 158, 107) と RGB(59, 133, 197)</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>図10 ほか（image10.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>RGB(103, 163, 218) と RGB(137, 192, 106)</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>RGB(252, 228, 214) と RGB(219, 234, 223)</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t>RGB(252, 228, 214) と RGB(210, 230, 211)</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="inlineStr">
+        <is>
+          <t>RGB(219, 234, 223) と RGB(210, 230, 211)</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>図18 ほか（image11.png）</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="inlineStr">
+        <is>
           <t>RGB(102, 163, 218) と RGB(222, 100, 134)</t>
         </is>
       </c>
-      <c r="B153" s="8" t="n">
+      <c r="B160" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C160" s="4" t="inlineStr">
         <is>
           <t>図26 ほか（image12.png）</t>
         </is>
@@ -5936,7 +6162,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>3</v>

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -1919,7 +1919,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>1307×1108</t>
+          <t>1307×1144</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>(243,180,92)</t>
+          <t>(243,183,98)</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F133" s="5" t="inlineStr"/>
     </row>
@@ -5553,11 +5553,11 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>(219,219,219)</t>
+          <t>(218,218,218)</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E135" s="6" t="n">
         <v>0</v>
@@ -5581,11 +5581,11 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>(134,134,134)</t>
+          <t>(131,131,131)</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E136" s="6" t="n">
         <v>0</v>
@@ -5609,11 +5609,11 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>(235,235,235)</t>
+          <t>(228,228,228)</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E137" s="6" t="n">
         <v>0</v>
@@ -5637,14 +5637,14 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>(94,180,141)</t>
+          <t>(99,182,144)</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F138" s="5" t="inlineStr"/>
     </row>
@@ -5661,11 +5661,11 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>(253,244,229)</t>
+          <t>(255,246,231)</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E139" s="6" t="n">
         <v>24</v>

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表135点（データ表88・注記ボックス47）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表141点（データ表90・注記ボックス51）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表135点のうち、直後に出所らしき行があるのは20点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表141点のうち、直後に出所らしき行があるのは22点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表135点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表141点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>表５-18　緊急時に働く仕組み（４つの場面）</t>
+          <t>表５-20　緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>表５-31　年齢到達に伴うサービスの移行</t>
+          <t>表５-33　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>表５-33　65歳到達時のサービスの区分</t>
+          <t>表５-35　65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>表５-36　関係機関と連携の内容</t>
+          <t>表５-38　関係機関と連携の内容</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -7492,7 +7492,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7506,23 +7506,27 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7536,22 +7540,18 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -7590,7 +7590,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -7604,23 +7604,27 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr"/>
-      <c r="H53" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -7634,14 +7638,14 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr"/>
@@ -7650,7 +7654,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -7664,27 +7668,23 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="inlineStr"/>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7698,23 +7698,27 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -7728,27 +7732,23 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7762,23 +7762,27 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7792,22 +7796,18 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7860,23 +7860,27 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7886,18 +7890,18 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -7906,28 +7910,28 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr"/>
@@ -7936,7 +7940,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7950,14 +7954,14 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -7966,7 +7970,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7980,14 +7984,14 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E65" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr"/>
@@ -7996,7 +8000,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8010,27 +8014,23 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -8044,27 +8044,27 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8085,16 +8085,20 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="9" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -8108,14 +8112,14 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
@@ -8124,7 +8128,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8138,27 +8142,23 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8172,27 +8172,27 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8213,16 +8213,20 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8236,14 +8240,14 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E73" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E73" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
@@ -8252,7 +8256,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8266,27 +8270,27 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr"/>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8300,17 +8304,21 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr"/>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8320,7 +8328,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8341,16 +8349,20 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="9" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8364,22 +8376,18 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -8405,7 +8413,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -8418,7 +8426,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8432,27 +8440,27 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8473,16 +8481,20 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="9" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8496,27 +8508,23 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E81" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8537,16 +8545,20 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="9" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8556,18 +8568,18 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D83" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E83" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr"/>
@@ -8576,7 +8588,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8586,31 +8598,27 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8620,27 +8628,31 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8654,22 +8666,18 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -8695,7 +8703,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -8729,7 +8737,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
@@ -8738,7 +8746,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8752,23 +8760,27 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8782,14 +8794,14 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E90" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr"/>
@@ -8819,7 +8831,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -8832,7 +8844,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8846,23 +8858,27 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8876,27 +8892,23 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr"/>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8910,14 +8922,14 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E94" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr"/>
@@ -8926,7 +8938,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8940,27 +8952,23 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8974,23 +8982,27 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9004,27 +9016,23 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9038,23 +9046,27 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9068,27 +9080,23 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H99" s="8" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9102,23 +9110,27 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9132,27 +9144,23 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9162,31 +9170,31 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9196,18 +9204,18 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
@@ -9226,7 +9234,7 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
@@ -9237,7 +9245,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -9250,7 +9258,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9260,18 +9268,18 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E105" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
@@ -9280,7 +9288,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9290,22 +9298,26 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -9320,7 +9332,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D107" s="8" t="n">
@@ -9331,7 +9343,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -9344,7 +9356,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9354,31 +9366,31 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9388,18 +9400,18 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E109" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr"/>
@@ -9408,7 +9420,7 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9418,27 +9430,31 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9448,18 +9464,18 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
@@ -9468,7 +9484,7 @@
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9478,31 +9494,27 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9512,22 +9524,26 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -9542,7 +9558,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
@@ -9553,7 +9569,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -9566,7 +9582,7 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9576,18 +9592,18 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
@@ -9596,7 +9612,7 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9610,14 +9626,14 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E116" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr"/>
@@ -9626,7 +9642,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9640,27 +9656,23 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9670,27 +9682,31 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9700,26 +9716,22 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -9734,7 +9746,7 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
@@ -9745,7 +9757,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -9758,7 +9770,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9768,31 +9780,27 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9802,7 +9810,7 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
@@ -9813,20 +9821,16 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H122" s="9" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9836,31 +9840,31 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9870,120 +9874,116 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="9" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E127" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr"/>
@@ -9996,66 +9996,70 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="9" t="inlineStr"/>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -10065,12 +10069,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
@@ -10081,7 +10085,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -10094,92 +10098,104 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="9" t="inlineStr"/>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="9" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -10189,12 +10205,12 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
@@ -10205,7 +10221,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -10218,28 +10234,28 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E135" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr"/>
@@ -10253,12 +10269,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
@@ -10269,7 +10285,7 @@
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -10282,28 +10298,28 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr"/>
@@ -10312,28 +10328,28 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E138" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr"/>
@@ -10342,28 +10358,28 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E139" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr"/>
@@ -10372,32 +10388,220 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>表７-4</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>４　北塩原村こども・子育て計画と</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>確かめる事項 / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="9" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>４　北塩原村こども・子育て計画と</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>表８-1</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>２　北塩原村障がい者自立支援協議</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="9" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>表８-2</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>３　計画の策定経過</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="9" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="9" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
           <t>表８-4</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>第８章　資料編</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>５　用語解説</t>
         </is>
       </c>
-      <c r="D140" s="6" t="n">
+      <c r="D146" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="E140" s="6" t="n">
+      <c r="E146" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F140" s="5" t="inlineStr">
+      <c r="F146" s="5" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="9" t="inlineStr"/>
+      <c r="G146" s="6" t="inlineStr"/>
+      <c r="H146" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表141点（データ表90・注記ボックス51）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表143点（データ表91・注記ボックス52）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表141点のうち、直後に出所らしき行があるのは22点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表143点のうち、直後に出所らしき行があるのは23点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表141点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表143点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7748,7 +7748,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7762,27 +7762,27 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr"/>
+          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7796,18 +7796,22 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -7833,7 +7837,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -7846,7 +7850,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7860,27 +7864,23 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="9" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7894,23 +7894,27 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7920,48 +7924,52 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -7970,28 +7978,28 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr"/>
@@ -8000,7 +8008,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8014,14 +8022,14 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -8030,7 +8038,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -8044,27 +8052,23 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr"/>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8078,27 +8082,23 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>加減 / 項目 / 拠り所</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -8112,23 +8112,27 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="9" t="inlineStr"/>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8142,23 +8146,27 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8172,27 +8180,23 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8206,27 +8210,23 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8240,23 +8240,27 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8270,14 +8274,14 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E74" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E74" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -8290,7 +8294,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8304,31 +8308,23 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8342,14 +8338,14 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -8362,7 +8358,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8376,23 +8372,31 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8406,27 +8410,27 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8440,27 +8444,23 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8474,27 +8474,27 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8508,23 +8508,27 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8538,7 +8542,7 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>5</v>
@@ -8558,7 +8562,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8572,7 +8576,7 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E83" s="8" t="n">
         <v>5</v>
@@ -8588,7 +8592,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8602,23 +8606,27 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8632,27 +8640,23 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8662,18 +8666,18 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
@@ -8692,7 +8696,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D87" s="8" t="n">
@@ -8703,7 +8707,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -8716,7 +8720,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8730,14 +8734,14 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+          <t>記録する事項 / ４町村で揃える定義</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
@@ -8767,7 +8771,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -8780,7 +8784,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8794,14 +8798,14 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr"/>
@@ -8831,7 +8835,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -8844,7 +8848,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8858,27 +8862,23 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8892,23 +8892,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8922,23 +8926,27 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8955,11 +8963,11 @@
         <v>5</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
@@ -8968,7 +8976,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8982,27 +8990,23 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr"/>
+          <t>備える事項 / 本村の取組み</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9016,14 +9020,14 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
@@ -9053,7 +9057,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -9066,7 +9070,7 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9083,11 +9087,11 @@
         <v>7</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
@@ -9117,7 +9121,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -9130,7 +9134,7 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9144,14 +9148,14 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr"/>
@@ -9181,7 +9185,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -9194,7 +9198,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9208,14 +9212,14 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
@@ -9245,7 +9249,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -9258,7 +9262,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9275,11 +9279,11 @@
         <v>5</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
@@ -9309,7 +9313,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -9322,7 +9326,7 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9336,27 +9340,23 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9366,31 +9366,31 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9400,27 +9400,31 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9434,27 +9438,27 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9468,14 +9472,14 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
@@ -9484,7 +9488,7 @@
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9498,23 +9502,27 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9528,27 +9536,23 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9558,31 +9562,27 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9592,27 +9592,31 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9622,27 +9626,31 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9652,18 +9660,18 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr"/>
@@ -9672,7 +9680,7 @@
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9686,27 +9694,23 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr"/>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9720,14 +9724,14 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
@@ -9757,7 +9761,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -9770,7 +9774,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9784,14 +9788,14 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9800,7 +9804,7 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9814,23 +9818,27 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9844,27 +9852,23 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="inlineStr"/>
+          <t>確認する事項 / 確認の内容</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="9" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9874,18 +9878,18 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E124" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr"/>
@@ -9904,7 +9908,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D125" s="8" t="n">
@@ -9915,7 +9919,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
@@ -9928,7 +9932,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9942,27 +9946,23 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9972,31 +9972,31 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr"/>
-      <c r="H127" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10006,31 +10006,31 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10044,14 +10044,14 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
@@ -10064,7 +10064,7 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10078,48 +10078,48 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
@@ -10132,41 +10132,41 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10180,14 +10180,14 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr"/>
@@ -10200,7 +10200,7 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10210,31 +10210,31 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H134" s="6" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10244,22 +10244,26 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="9" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -10274,7 +10278,7 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
@@ -10285,7 +10289,7 @@
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -10298,28 +10302,28 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr"/>
@@ -10328,37 +10332,41 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10368,18 +10376,18 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr"/>
@@ -10388,7 +10396,7 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10398,31 +10406,27 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H140" s="6" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr"/>
+      <c r="H140" s="9" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10432,18 +10436,18 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E141" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr"/>
@@ -10462,7 +10466,7 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
@@ -10473,7 +10477,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
@@ -10486,28 +10490,28 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr"/>
@@ -10516,37 +10520,41 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10556,18 +10564,18 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr"/>
@@ -10576,7 +10584,7 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10586,22 +10594,82 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E146" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
       <c r="H146" s="9" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="9" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E148" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表143点（データ表91・注記ボックス52）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表144点（データ表91・注記ボックス53）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表143点のうち、直後に出所らしき行があるのは23点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表144点のうち、直後に出所らしき行があるのは23点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表143点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表144点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7978,7 +7978,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7988,48 +7988,52 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -8038,7 +8042,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -8052,14 +8056,14 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr"/>
@@ -8068,7 +8072,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8082,14 +8086,14 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E68" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
@@ -8098,7 +8102,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -8112,27 +8116,23 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8146,27 +8146,27 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8187,16 +8187,20 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8210,14 +8214,14 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -8226,7 +8230,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8240,27 +8244,23 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8274,27 +8274,27 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8315,16 +8315,20 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="9" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8338,27 +8342,23 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E76" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E76" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8372,21 +8372,17 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8396,7 +8392,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8410,17 +8406,21 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8430,7 +8430,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8451,16 +8451,20 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8474,22 +8478,18 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
@@ -8528,7 +8528,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8542,27 +8542,27 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8583,16 +8583,20 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="9" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8606,27 +8610,23 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E84" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8647,16 +8647,20 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8670,14 +8674,14 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
@@ -8686,7 +8690,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8700,27 +8704,23 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8730,27 +8730,31 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8764,27 +8768,23 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8798,23 +8798,27 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8828,27 +8832,23 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H91" s="8" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8862,23 +8862,27 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8892,22 +8896,18 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -8946,7 +8946,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8960,23 +8960,27 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8990,14 +8994,14 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr"/>
@@ -9006,7 +9010,7 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9020,14 +9024,14 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E97" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
@@ -9036,7 +9040,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9050,27 +9054,23 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9084,23 +9084,27 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9114,27 +9118,23 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9148,23 +9148,27 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9178,27 +9182,23 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9212,23 +9212,27 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9242,27 +9246,23 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9276,23 +9276,27 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9306,27 +9310,23 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9340,23 +9340,27 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr"/>
-      <c r="H107" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9370,22 +9374,18 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9434,31 +9434,31 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9479,16 +9479,20 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="9" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9502,27 +9506,23 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9536,23 +9536,27 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9566,14 +9570,14 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr"/>
@@ -9582,7 +9586,7 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9596,22 +9600,18 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H115" s="8" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9664,23 +9664,27 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9690,18 +9694,18 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr"/>
@@ -9710,7 +9714,7 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9724,14 +9728,14 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
@@ -9740,7 +9744,7 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9754,27 +9758,23 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9788,23 +9788,27 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9818,27 +9822,23 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="9" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9852,23 +9852,27 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9882,14 +9886,14 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr"/>
@@ -9898,7 +9902,7 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9912,27 +9916,23 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9942,27 +9942,31 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9976,22 +9980,18 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H127" s="8" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -10030,7 +10030,7 @@
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10040,31 +10040,31 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10078,14 +10078,14 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E130" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E130" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr"/>
@@ -10098,7 +10098,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10112,14 +10112,14 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E131" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
@@ -10132,7 +10132,7 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10146,61 +10146,61 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr"/>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10214,14 +10214,14 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E134" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr"/>
@@ -10234,7 +10234,7 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10248,14 +10248,14 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr"/>
@@ -10268,7 +10268,7 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10278,31 +10278,31 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10316,23 +10316,27 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10342,61 +10346,61 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr"/>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="9" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10406,18 +10410,18 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10426,7 +10430,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10436,18 +10440,18 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E141" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr"/>
@@ -10456,7 +10460,7 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10470,27 +10474,23 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="9" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10500,27 +10500,31 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr"/>
-      <c r="H143" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10534,57 +10538,57 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H144" s="6" t="inlineStr"/>
+          <t>確かめる事項 / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="9" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr"/>
-      <c r="H145" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10594,18 +10598,18 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
@@ -10614,7 +10618,7 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10624,18 +10628,18 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E147" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr"/>
@@ -10644,7 +10648,7 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-3</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10654,22 +10658,52 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>４　近年の障がい者施策の動向</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E148" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年 / 主な動向</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr"/>
       <c r="H148" s="9" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr"/>
+      <c r="H149" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -7901,7 +7901,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-12）】意思決定支援ガイドラインの改定の状況（令和８年７月10日の社会保障審議会障害者部会に第２版の案が</t>
+          <t>【県へ確認（S-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E120" s="6" t="n">
         <v>2</v>

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表144点（データ表91・注記ボックス53）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表146点（データ表91・注記ボックス55）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表144点のうち、直後に出所らしき行があるのは23点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表146点のうち、直後に出所らしき行があるのは23点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表144点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表146点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8012,7 +8012,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8026,44 +8026,48 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr"/>
@@ -8072,7 +8076,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8086,14 +8090,14 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
@@ -8102,7 +8106,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -8116,14 +8120,14 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E69" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
@@ -8132,7 +8136,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8146,27 +8150,23 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8180,27 +8180,27 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8221,16 +8221,20 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8244,14 +8248,14 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
@@ -8260,7 +8264,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8274,27 +8278,23 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8308,27 +8308,27 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8349,16 +8349,20 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="9" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8372,27 +8376,23 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E77" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E77" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8406,21 +8406,17 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
       <c r="H78" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8430,7 +8426,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8444,17 +8440,21 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr"/>
+          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8464,7 +8464,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8485,16 +8485,20 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="9" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8508,22 +8512,18 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H81" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -8562,7 +8562,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8576,27 +8576,27 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8617,16 +8617,20 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8640,27 +8644,23 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E85" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8681,16 +8681,20 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8704,14 +8708,14 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
@@ -8720,7 +8724,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8734,27 +8738,23 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8764,22 +8764,26 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -8805,7 +8809,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -8818,7 +8822,7 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8832,14 +8836,14 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+          <t>記録する事項 / ４町村で揃える定義</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
@@ -8869,7 +8873,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -8882,7 +8886,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8896,14 +8900,14 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr"/>
@@ -8933,7 +8937,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -8946,7 +8950,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8960,27 +8964,23 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8994,23 +8994,27 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9024,23 +9028,27 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9057,11 +9065,11 @@
         <v>5</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr"/>
@@ -9070,7 +9078,7 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9084,27 +9092,23 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H99" s="8" t="inlineStr"/>
+          <t>備える事項 / 本村の取組み</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9118,14 +9122,14 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr"/>
@@ -9155,7 +9159,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -9168,7 +9172,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9185,11 +9189,11 @@
         <v>7</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr"/>
@@ -9219,7 +9223,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
@@ -9232,7 +9236,7 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9246,14 +9250,14 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr"/>
@@ -9283,7 +9287,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -9296,7 +9300,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9310,14 +9314,14 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr"/>
@@ -9347,7 +9351,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -9360,7 +9364,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9377,11 +9381,11 @@
         <v>5</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr"/>
@@ -9411,7 +9415,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -9424,7 +9428,7 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9438,27 +9442,23 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9468,31 +9468,31 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9502,27 +9502,31 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9536,27 +9540,27 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9570,14 +9574,14 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr"/>
@@ -9586,7 +9590,7 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9600,23 +9604,27 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9630,27 +9638,23 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9660,31 +9664,27 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9694,27 +9694,31 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9724,27 +9728,31 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr"/>
-      <c r="H119" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9754,18 +9762,18 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr"/>
@@ -9774,7 +9782,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9788,27 +9796,23 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="inlineStr"/>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9822,14 +9826,14 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr"/>
@@ -9859,7 +9863,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
@@ -9872,7 +9876,7 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9886,14 +9890,14 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr"/>
@@ -9902,7 +9906,7 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9916,23 +9920,27 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9946,27 +9954,23 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr"/>
+          <t>確認する事項 / 確認の内容</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9976,18 +9980,18 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E127" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr"/>
@@ -10006,7 +10010,7 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
@@ -10017,7 +10021,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -10030,7 +10034,7 @@
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10044,27 +10048,23 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H129" s="8" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10074,31 +10074,31 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10108,31 +10108,31 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10146,14 +10146,14 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10180,48 +10180,48 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr"/>
@@ -10234,41 +10234,41 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10282,14 +10282,14 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10302,7 +10302,7 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10312,31 +10312,31 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10346,22 +10346,26 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="9" t="inlineStr"/>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
@@ -10376,7 +10380,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
@@ -10387,7 +10391,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
@@ -10400,28 +10404,28 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10430,37 +10434,41 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr"/>
-      <c r="H141" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10470,18 +10478,18 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr"/>
@@ -10490,7 +10498,7 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10500,31 +10508,27 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="9" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10534,18 +10538,18 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E144" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
@@ -10564,7 +10568,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
@@ -10575,7 +10579,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
@@ -10588,28 +10592,28 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
@@ -10618,37 +10622,41 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr"/>
-      <c r="H147" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10658,18 +10666,18 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr"/>
@@ -10678,7 +10686,7 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10688,22 +10696,82 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E149" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr"/>
       <c r="H149" s="9" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E150" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="9" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr"/>
+      <c r="H151" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表146点（データ表91・注記ボックス55）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表148点（データ表92・注記ボックス56）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表146点のうち、直後に出所らしき行があるのは23点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表148点のうち、直後に出所らしき行があるのは23点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表146点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表148点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>本村には障がい福祉サービスの事業所が３カ所しかありませんが、介護保険の事業所</t>
+          <t>数を増やすことが目的ではありません。介護保険と障がい福祉では、通所の例でいえ</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>表５-38　関係機関と連携の内容</t>
+          <t>表５-39　関係機関と連携の内容</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8886,7 +8886,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8900,23 +8900,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8930,27 +8934,23 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8964,23 +8964,27 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -8994,22 +8998,18 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -9048,7 +9048,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9062,23 +9062,27 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9092,14 +9096,14 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
@@ -9108,7 +9112,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9122,14 +9126,14 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr"/>
@@ -9138,7 +9142,7 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9152,27 +9156,23 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9186,23 +9186,27 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9216,27 +9220,23 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9250,23 +9250,27 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9280,27 +9284,23 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9314,23 +9314,27 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9344,27 +9348,23 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9378,23 +9378,27 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9408,27 +9412,23 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9442,23 +9442,27 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9472,22 +9476,18 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9536,31 +9536,31 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9581,16 +9581,20 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="9" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9604,27 +9608,23 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H115" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9638,23 +9638,27 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9668,14 +9672,14 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr"/>
@@ -9684,7 +9688,7 @@
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9698,22 +9702,18 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
@@ -9752,7 +9752,7 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9766,23 +9766,27 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9792,18 +9796,18 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9812,7 +9816,7 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9826,14 +9830,14 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr"/>
@@ -9842,7 +9846,7 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9856,27 +9860,23 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="9" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9890,23 +9890,27 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9920,27 +9924,23 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9954,23 +9954,27 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9984,14 +9988,14 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr"/>
@@ -10000,7 +10004,7 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10014,22 +10018,18 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+          <t>確認する事項 / 確認の内容</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -10044,18 +10044,18 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E129" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -10098,7 +10098,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10112,27 +10112,23 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H131" s="8" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="9" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10142,31 +10138,31 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10176,31 +10172,31 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10214,14 +10210,14 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr"/>
@@ -10234,7 +10230,7 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10248,48 +10244,48 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H135" s="8" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10302,41 +10298,41 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10350,14 +10346,14 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr"/>
@@ -10370,7 +10366,7 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10380,31 +10376,31 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H139" s="8" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10414,22 +10410,26 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="9" t="inlineStr"/>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr">
@@ -10468,28 +10468,28 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr"/>
@@ -10498,37 +10498,41 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr"/>
-      <c r="H143" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10538,18 +10542,18 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
@@ -10558,7 +10562,7 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10568,31 +10572,27 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="9" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10602,18 +10602,18 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E146" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
@@ -10656,28 +10656,28 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr"/>
@@ -10686,37 +10686,41 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr"/>
-      <c r="H149" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10726,18 +10730,18 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr"/>
@@ -10746,7 +10750,7 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10756,22 +10760,82 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E151" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr"/>
       <c r="H151" s="9" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E152" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr"/>
+      <c r="H152" s="9" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr"/>
+      <c r="H153" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表148点（データ表92・注記ボックス56）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表150点（データ表93・注記ボックス57）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表148点のうち、直後に出所らしき行があるのは23点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表150点のうち、直後に出所らしき行があるのは24点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表148点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表150点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>表５-20　緊急時に働く仕組み（４つの場面）</t>
+          <t>表５-21　緊急時に働く仕組み（４つの場面）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>表５-33　年齢到達に伴うサービスの移行</t>
+          <t>表５-34　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>表５-35　65歳到達時のサービスの区分</t>
+          <t>表５-36　65歳到達時のサービスの区分</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>表５-39　関係機関と連携の内容</t>
+          <t>表５-40　関係機関と連携の内容</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8836,18 +8836,22 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="9" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -8873,7 +8877,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -8886,7 +8890,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8900,27 +8904,23 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8934,18 +8934,22 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -8971,7 +8975,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
@@ -8998,14 +9002,14 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr"/>
@@ -9035,7 +9039,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -9048,7 +9052,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9062,27 +9066,23 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9096,23 +9096,27 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
+          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9126,23 +9130,27 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="9" t="inlineStr"/>
+          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9159,11 +9167,11 @@
         <v>5</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr"/>
@@ -9172,7 +9180,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9186,22 +9194,18 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr"/>
+          <t>備える事項 / 本村の取組み</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -9220,14 +9224,14 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
@@ -9257,7 +9261,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -9287,11 +9291,11 @@
         <v>7</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
@@ -9321,7 +9325,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -9348,14 +9352,14 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
@@ -9385,7 +9389,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -9412,14 +9416,14 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr"/>
@@ -9449,7 +9453,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -9479,11 +9483,11 @@
         <v>5</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
@@ -9513,7 +9517,7 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -9526,7 +9530,7 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9540,27 +9544,23 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9570,31 +9570,31 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9604,27 +9604,31 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9638,22 +9642,22 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
@@ -9672,14 +9676,14 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr"/>
@@ -9688,7 +9692,7 @@
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9702,23 +9706,27 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9732,27 +9740,23 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9762,31 +9766,27 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9796,27 +9796,31 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9826,27 +9830,31 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9856,18 +9864,18 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr"/>
@@ -9876,7 +9884,7 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9890,22 +9898,18 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr"/>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="9" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -9924,14 +9928,14 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9961,7 +9965,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -9988,14 +9992,14 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr"/>
@@ -10004,7 +10008,7 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10018,23 +10022,27 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10048,14 +10056,14 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
@@ -10064,7 +10072,7 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10078,22 +10086,18 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr"/>
+          <t>確認する事項 / 確認の内容</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -10108,18 +10112,18 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E131" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
@@ -10138,7 +10142,7 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
@@ -10149,7 +10153,7 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -10162,7 +10166,7 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10176,27 +10180,23 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10206,31 +10206,31 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10240,31 +10240,31 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10278,14 +10278,14 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10298,7 +10298,7 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10312,48 +10312,48 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr"/>
@@ -10366,41 +10366,41 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10414,14 +10414,14 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10434,7 +10434,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10444,31 +10444,31 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H141" s="8" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10478,22 +10478,26 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="9" t="inlineStr"/>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
@@ -10508,7 +10512,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
@@ -10519,7 +10523,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
@@ -10532,28 +10536,28 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
@@ -10562,37 +10566,41 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr"/>
-      <c r="H145" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10602,18 +10610,18 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
@@ -10622,7 +10630,7 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10632,31 +10640,27 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H147" s="8" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="9" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10666,18 +10670,18 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E148" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr"/>
@@ -10696,7 +10700,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
@@ -10707,7 +10711,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
@@ -10720,28 +10724,28 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr"/>
@@ -10750,37 +10754,41 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr"/>
-      <c r="H151" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10790,18 +10798,18 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr"/>
@@ -10810,7 +10818,7 @@
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -10820,22 +10828,82 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E153" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr"/>
       <c r="H153" s="9" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E154" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr"/>
+      <c r="H154" s="9" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr"/>
+      <c r="H155" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表150点（データ表93・注記ボックス57）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表152点（データ表94・注記ボックス58）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表150点のうち、直後に出所らしき行があるのは24点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表152点のうち、直後に出所らしき行があるのは25点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表150点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表152点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>表５-40　関係機関と連携の内容</t>
+          <t>表５-41　関係機関と連携の内容</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10176,22 +10176,26 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E133" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -10206,7 +10210,7 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
@@ -10217,7 +10221,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -10230,7 +10234,7 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10244,27 +10248,23 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H135" s="8" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10274,31 +10274,31 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10308,31 +10308,31 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10346,14 +10346,14 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr"/>
@@ -10366,7 +10366,7 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10380,48 +10380,48 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H139" s="8" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10434,41 +10434,41 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr"/>
-      <c r="H141" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10482,14 +10482,14 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10512,31 +10512,31 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10546,22 +10546,26 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="9" t="inlineStr"/>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
@@ -10576,7 +10580,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
@@ -10587,7 +10591,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
@@ -10600,28 +10604,28 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
@@ -10630,37 +10634,41 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr"/>
-      <c r="H147" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10670,18 +10678,18 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr"/>
@@ -10690,7 +10698,7 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10700,31 +10708,27 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H149" s="8" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr"/>
+      <c r="H149" s="9" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10734,18 +10738,18 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E150" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr"/>
@@ -10764,7 +10768,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
@@ -10775,7 +10779,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
@@ -10788,28 +10792,28 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr"/>
@@ -10818,37 +10822,41 @@
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr"/>
-      <c r="H153" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -10858,18 +10866,18 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E154" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr"/>
@@ -10878,7 +10886,7 @@
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -10888,22 +10896,82 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E155" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
       <c r="H155" s="9" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E156" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr"/>
+      <c r="H156" s="9" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr"/>
+      <c r="H157" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -7057,7 +7057,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
+          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-６）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
+          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
+          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの入</t>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（M-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（S-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（M-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（S-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+          <t>【村・県へ確認（Ｓ-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>図はカラーで進めることとしたが、緑 RGB(46,158,107) と 青 RGB(61,134,198) はグレー値がいずれも119で、白黒コピーすると見分けられない。手帳の種類別のように3系列並べる図では、青を橙（グレー値171）に替えるか、網かけを足すことを提案したい</t>
+          <t>図はカラーで進めることとしたが、緑 RGB(46,158,107) と 青 RGB(61,134,198) はグレー値がいずれも119で、白黒コピーすると見分けられない。手帳の種類別のように３系列並べる図では、青を橙（グレー値171）に替えるか、網かけを足すことを提案したい</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>図表番号を振り、目次の後に図表目次を置くことを提案したい。番号の形（図１-１・表１-１）と、注記ボックスには番号を振らないことを合わせたい。令和8年10月10日に当方で図24点・表84点に番号と表題を付け、図表目次を置いた（北塩原村_図表番号一覧.xlsx）。これに伴う確認3件はＳ-22〜Ｓ-24として同書に立てている</t>
+          <t>図表番号を振り、目次の後に図表目次を置くことを提案したい。番号の形（図１-１・表１-１）と、注記ボックスには番号を振らないことを合わせたい。令和8年10月10日に当方で図26点・表94点に番号と表題を付け、図表目次を置いた（北塩原村_図表番号一覧.xlsx）。これに伴う確認３件はＳ-22〜Ｓ-24として同書に立てている</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表152点（データ表94・注記ボックス58）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表153点（データ表94・注記ボックス59）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表152点のうち、直後に出所らしき行があるのは25点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表153点のうち、直後に出所らしき行があるのは25点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表152点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表153点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6490,41 +6490,41 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>表２-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>第２章　本村の障がい</t>
+          <t>第１章　計画の策定に</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>１　人口の推移</t>
+          <t>６　計画の推進体制</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和８年度 （現状） / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-110）】本村に障害者基本法第36条第１項又は第４項の合議制の機関（障害者施策推進協議会等の名称で置かれ</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表２-1</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -6534,31 +6534,31 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>２　障がい者手帳の所持者数</t>
+          <t>１　人口の推移</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-32）】手帳を所持していないが対象疾病に該当してサービスを利用している方、又は利用しうる方の人数を確認し</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr"/>
+          <t>区分 / 令和８年度 （現状） / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>表２-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -6568,27 +6568,31 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>６　障がい児の就学状況</t>
+          <t>２　障がい者手帳の所持者数</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>学校名 / 小学部 / 中学部 / 高等部</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-32）】手帳を所持していないが対象疾病に該当してサービスを利用している方、又は利用しうる方の人数を確認し</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>表２-3</t>
+          <t>表２-2</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -6602,14 +6606,14 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>学校名 / 在籍者数</t>
+          <t>学校名 / 小学部 / 中学部 / 高等部</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
@@ -6618,7 +6622,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>表２-4</t>
+          <t>表２-3</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -6628,18 +6632,18 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>７　アンケート調査の実施と結果</t>
+          <t>６　障がい児の就学状況</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>項目 / 障がい者調査 / 障がい児調査</t>
+          <t>学校名 / 在籍者数</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr"/>
@@ -6648,7 +6652,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>表２-5</t>
+          <t>表２-4</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -6665,24 +6669,20 @@
         <v>4</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>調査区分 / 配布数 / 有効回答数 / 有効回答率</t>
+          <t>項目 / 障がい者調査 / 障がい児調査</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>表２-6</t>
+          <t>表２-5</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -6696,14 +6696,14 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>分野 / 主な調査結果 / 割合</t>
+          <t>調査区分 / 配布数 / 有効回答数 / 有効回答率</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr"/>
@@ -6716,7 +6716,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>表２-7</t>
+          <t>表２-6</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -6730,14 +6730,14 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>項目 / 全体 （n=38） / 身体障がい （n=29） / 知的障がい （n=2）</t>
+          <t>分野 / 主な調査結果 / 割合</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>表２-8</t>
+          <t>表２-7</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -6764,23 +6764,27 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>主な課題 / 主な調査結果 / 本計画での主な対応（関連箇所）</t>
+          <t>項目 / 全体 （n=38） / 身体障がい （n=29） / 知的障がい （n=2）</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="9" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>表２-9</t>
+          <t>表２-8</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -6794,14 +6798,14 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>用いること / 本村での例</t>
+          <t>主な課題 / 主な調査結果 / 本計画での主な対応（関連箇所）</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
@@ -6810,41 +6814,37 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表２-9</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>第３章　第４次北塩原</t>
+          <t>第２章　本村の障がい</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>１　基本理念</t>
+          <t>７　アンケート調査の実施と結果</t>
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr"/>
+          <t>用いること / 本村での例</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>表３-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -6854,31 +6854,31 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>３　基本施策の目標値と本計画期間</t>
+          <t>１　基本理念</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>基本施策 / 指標項目 / 現状 （R5） / 目標 （R11）</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>表３-2</t>
+          <t>表３-1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -6892,57 +6892,57 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>区分 / 意味</t>
+          <t>基本施策 / 指標項目 / 現状 （R5） / 目標 （R11）</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="9" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>表４-1</t>
+          <t>表３-2</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>第４章　障がい福祉計</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>１　第７期計画の成果目標の達成状</t>
+          <t>３　基本施策の目標値と本計画期間</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+          <t>区分 / 意味</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-1</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -6952,31 +6952,31 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>２　令和11年度に向けた成果目標</t>
+          <t>１　第７期計画の成果目標の達成状</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr"/>
+          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>表４-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -6990,23 +6990,27 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>表４-3</t>
+          <t>表４-2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -7020,14 +7024,14 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr"/>
@@ -7036,7 +7040,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-3</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -7050,22 +7054,18 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
+          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -7104,7 +7104,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>表４-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -7118,23 +7118,27 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>表４-5</t>
+          <t>表４-4</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -7148,14 +7152,14 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr"/>
@@ -7164,7 +7168,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>表４-6</t>
+          <t>表４-5</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -7178,14 +7182,14 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>項目 / 値 / 考え方</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr"/>
@@ -7194,7 +7198,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-6</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -7208,26 +7212,18 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>項目 / 値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -7253,7 +7249,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -7261,7 +7257,11 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -7300,7 +7300,7 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>表４-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -7314,23 +7314,27 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr"/>
-      <c r="H44" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>表４-7</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -7344,14 +7348,14 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr"/>
@@ -7360,7 +7364,7 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -7374,22 +7378,18 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -7428,7 +7428,7 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7442,23 +7442,27 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -7472,22 +7476,18 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7540,23 +7540,27 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr"/>
-      <c r="H51" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -7570,22 +7574,18 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -7624,7 +7624,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -7638,23 +7638,27 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -7668,14 +7672,14 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr"/>
@@ -7684,7 +7688,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7698,27 +7702,23 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -7732,23 +7732,27 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7762,27 +7766,23 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7796,22 +7796,22 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="inlineStr"/>
+          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -7850,7 +7850,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7864,23 +7864,27 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7894,22 +7898,18 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="9" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -7948,7 +7948,7 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7962,23 +7962,27 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7992,22 +7996,18 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -8060,44 +8060,48 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
@@ -8106,7 +8110,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -8120,14 +8124,14 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
@@ -8136,7 +8140,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8150,14 +8154,14 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E70" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -8166,7 +8170,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8180,27 +8184,23 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8214,27 +8214,27 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8255,16 +8255,20 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="9" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8278,14 +8282,14 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -8294,7 +8298,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8308,27 +8312,23 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8342,27 +8342,27 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8383,16 +8383,20 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8406,27 +8410,23 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E78" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E78" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8440,21 +8440,17 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr"/>
       <c r="H79" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8464,7 +8460,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8478,17 +8474,21 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8498,7 +8498,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8519,16 +8519,20 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8542,22 +8546,18 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -8596,7 +8596,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8610,27 +8610,27 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8651,16 +8651,20 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8674,27 +8678,23 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8715,16 +8715,20 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8738,14 +8742,14 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
@@ -8754,7 +8758,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8768,22 +8772,18 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D90" s="6" t="n">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -8822,7 +8822,7 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8836,27 +8836,27 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8870,27 +8870,27 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr"/>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8904,23 +8904,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8934,22 +8938,18 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
@@ -8988,7 +8988,7 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -9002,23 +9002,27 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9032,27 +9036,23 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9066,23 +9066,27 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9096,22 +9100,18 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H99" s="8" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -9150,7 +9150,7 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9164,23 +9164,27 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9194,14 +9198,14 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr"/>
@@ -9210,7 +9214,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9224,14 +9228,14 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E103" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
@@ -9240,7 +9244,7 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9254,27 +9258,23 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9288,23 +9288,27 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9318,27 +9322,23 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9352,23 +9352,27 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr"/>
-      <c r="H107" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9382,27 +9386,23 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9416,23 +9416,27 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9446,27 +9450,23 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9480,23 +9480,27 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9510,27 +9514,23 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9544,23 +9544,27 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9574,22 +9578,18 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
@@ -9628,7 +9628,7 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9638,31 +9638,31 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9683,16 +9683,20 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="9" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9706,27 +9710,23 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9740,23 +9740,27 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr"/>
-      <c r="H119" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9770,14 +9774,14 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr"/>
@@ -9786,7 +9790,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9800,22 +9804,18 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -9854,7 +9854,7 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9868,23 +9868,27 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9894,18 +9898,18 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr"/>
@@ -9914,7 +9918,7 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9928,14 +9932,14 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9944,7 +9948,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9958,27 +9962,23 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9992,23 +9992,27 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10022,27 +10026,23 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10056,23 +10056,27 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10086,14 +10090,14 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E130" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr"/>
@@ -10102,7 +10106,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10116,14 +10120,14 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
@@ -10132,7 +10136,7 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10146,27 +10150,23 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="9" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10180,27 +10180,27 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10214,27 +10214,27 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H134" s="6" t="inlineStr"/>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10244,27 +10244,31 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10278,22 +10282,18 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="9" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr">
@@ -10332,7 +10332,7 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10342,31 +10342,31 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10380,14 +10380,14 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E139" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E139" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr"/>
@@ -10400,7 +10400,7 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10414,14 +10414,14 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E140" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10434,7 +10434,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10448,61 +10448,61 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H141" s="8" t="inlineStr"/>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10516,14 +10516,14 @@
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E143" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr"/>
@@ -10536,7 +10536,7 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10550,14 +10550,14 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
@@ -10570,7 +10570,7 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10580,31 +10580,31 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10618,23 +10618,27 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10644,61 +10648,61 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（Ｓ-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H147" s="8" t="inlineStr"/>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="9" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（Ｓ-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10708,18 +10712,18 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr"/>
@@ -10728,7 +10732,7 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10738,18 +10742,18 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E150" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr"/>
@@ -10758,7 +10762,7 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10772,27 +10776,23 @@
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H151" s="8" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr"/>
+      <c r="H151" s="9" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10802,27 +10802,31 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -10836,57 +10840,57 @@
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H153" s="8" t="inlineStr"/>
+          <t>確かめる事項 / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr"/>
+      <c r="H153" s="9" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E154" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -10896,18 +10900,18 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
@@ -10916,7 +10920,7 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -10926,18 +10930,18 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E156" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr"/>
@@ -10946,7 +10950,7 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-3</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -10956,22 +10960,52 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>４　近年の障がい者施策の動向</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E157" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年 / 主な動向</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr"/>
       <c r="H157" s="9" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E158" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表153点（データ表94・注記ボックス59）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表154点（データ表94・注記ボックス60）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表153点のうち、直後に出所らしき行があるのは25点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表154点のうち、直後に出所らしき行があるのは25点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表153点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表154点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6912,7 +6912,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>表３-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -6926,57 +6926,57 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>区分 / 意味</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-111）】村の生涯学習、スポーツ及び文化の事業について、障がいのある方の参加の実績（令和６年度・令和７年</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>表４-1</t>
+          <t>表３-2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>第４章　障がい福祉計</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>１　第７期計画の成果目標の達成状</t>
+          <t>３　基本施策の目標値と本計画期間</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+          <t>区分 / 意味</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-1</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -6986,31 +6986,31 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>２　令和11年度に向けた成果目標</t>
+          <t>１　第７期計画の成果目標の達成状</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr"/>
+          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>表４-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -7024,23 +7024,27 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>表４-3</t>
+          <t>表４-2</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -7054,14 +7058,14 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
@@ -7070,7 +7074,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-3</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -7084,22 +7088,18 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr"/>
+          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -7138,7 +7138,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>表４-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -7152,23 +7152,27 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr"/>
-      <c r="H39" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>表４-5</t>
+          <t>表４-4</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -7182,14 +7186,14 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr"/>
@@ -7198,7 +7202,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>表４-6</t>
+          <t>表４-5</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -7212,14 +7216,14 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>項目 / 値 / 考え方</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr"/>
@@ -7228,7 +7232,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-6</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -7242,26 +7246,18 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>項目 / 値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -7287,7 +7283,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -7295,7 +7291,11 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -7334,7 +7334,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>表４-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -7348,23 +7348,27 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr"/>
-      <c r="H45" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>表４-7</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -7378,14 +7382,14 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr"/>
@@ -7394,7 +7398,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -7408,22 +7412,18 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -7462,7 +7462,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -7476,23 +7476,27 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7506,22 +7510,18 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -7560,7 +7560,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -7574,23 +7574,27 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -7604,22 +7608,18 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -7658,7 +7658,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -7672,23 +7672,27 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr"/>
-      <c r="H55" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7702,14 +7706,14 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr"/>
@@ -7718,7 +7722,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -7732,27 +7736,23 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="inlineStr"/>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7766,23 +7766,27 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7796,27 +7800,23 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7830,22 +7830,22 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr"/>
+          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -7884,7 +7884,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7898,23 +7898,27 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7928,22 +7932,18 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -7982,7 +7982,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7996,23 +7996,27 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8026,22 +8030,18 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D67" s="8" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -8080,7 +8080,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8094,44 +8094,48 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
@@ -8140,7 +8144,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8154,14 +8158,14 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -8170,7 +8174,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8184,14 +8188,14 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E71" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr"/>
@@ -8200,7 +8204,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8214,27 +8218,23 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr"/>
+      <c r="H72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8248,27 +8248,27 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8289,16 +8289,20 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="9" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8312,14 +8316,14 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
@@ -8328,7 +8332,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8342,27 +8346,23 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8376,27 +8376,27 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8417,16 +8417,20 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="9" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8440,27 +8444,23 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E79" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E79" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8474,21 +8474,17 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
       <c r="H80" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8498,7 +8494,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8512,17 +8508,21 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8532,7 +8532,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8553,16 +8553,20 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="9" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8576,22 +8580,18 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H83" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -8630,7 +8630,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8644,27 +8644,27 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8685,16 +8685,20 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8708,27 +8712,23 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E87" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8749,16 +8749,20 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8772,14 +8776,14 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr"/>
@@ -8788,7 +8792,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8802,22 +8806,18 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D91" s="8" t="n">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -8856,7 +8856,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8870,27 +8870,27 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8904,27 +8904,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr"/>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8938,23 +8938,27 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8968,22 +8972,18 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9036,23 +9036,27 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9066,27 +9070,23 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9100,23 +9100,27 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9130,22 +9134,18 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -9184,7 +9184,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9198,23 +9198,27 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9228,14 +9232,14 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
@@ -9244,7 +9248,7 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9258,14 +9262,14 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E104" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr"/>
@@ -9274,7 +9278,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9288,27 +9292,23 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9322,23 +9322,27 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9352,27 +9356,23 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9386,23 +9386,27 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9416,27 +9420,23 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9450,23 +9450,27 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9480,27 +9484,23 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9514,23 +9514,27 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9544,27 +9548,23 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9578,23 +9578,27 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9608,22 +9612,18 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H115" s="8" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -9662,7 +9662,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9672,31 +9672,31 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9717,16 +9717,20 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="9" t="inlineStr"/>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9740,27 +9744,23 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9774,23 +9774,27 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9804,14 +9808,14 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9820,7 +9824,7 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9834,22 +9838,18 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="9" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
@@ -9888,7 +9888,7 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9902,23 +9902,27 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9928,18 +9932,18 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9948,7 +9952,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9962,14 +9966,14 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr"/>
@@ -9978,7 +9982,7 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9992,27 +9996,23 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H127" s="8" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10026,23 +10026,27 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10056,27 +10060,23 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H129" s="8" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10090,23 +10090,27 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10120,14 +10124,14 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E131" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
@@ -10136,7 +10140,7 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10150,14 +10154,14 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
@@ -10166,7 +10170,7 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10180,27 +10184,23 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10214,27 +10214,27 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10248,27 +10248,27 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H135" s="8" t="inlineStr"/>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10278,27 +10278,31 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10312,22 +10316,18 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="9" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -10366,7 +10366,7 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10376,31 +10376,31 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10414,14 +10414,14 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E140" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E140" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10434,7 +10434,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10448,14 +10448,14 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E141" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr"/>
@@ -10468,7 +10468,7 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10482,61 +10482,61 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="inlineStr"/>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr"/>
-      <c r="H143" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10550,14 +10550,14 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E144" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
@@ -10570,7 +10570,7 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10584,14 +10584,14 @@
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr"/>
@@ -10604,7 +10604,7 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10614,31 +10614,31 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H146" s="6" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr"/>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10652,23 +10652,27 @@
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr"/>
-      <c r="H147" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10678,61 +10682,61 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>【村・県へ確認（Ｓ-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H148" s="6" t="inlineStr"/>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="9" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr"/>
-      <c r="H149" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（Ｓ-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10742,18 +10746,18 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr"/>
@@ -10762,7 +10766,7 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10772,18 +10776,18 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E151" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr"/>
@@ -10792,7 +10796,7 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10806,27 +10810,23 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H152" s="6" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr"/>
+      <c r="H152" s="9" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -10836,27 +10836,31 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr"/>
-      <c r="H153" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -10870,57 +10874,57 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E154" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H154" s="6" t="inlineStr"/>
+          <t>確かめる事項 / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr"/>
+      <c r="H154" s="9" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G155" s="8" t="inlineStr"/>
-      <c r="H155" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -10930,18 +10934,18 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E156" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr"/>
@@ -10950,7 +10954,7 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -10960,18 +10964,18 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E157" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr"/>
@@ -10980,7 +10984,7 @@
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-3</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -10990,22 +10994,52 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>４　近年の障がい者施策の動向</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E158" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年 / 主な動向</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr"/>
       <c r="H158" s="9" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D159" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr"/>
+      <c r="H159" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表154点（データ表94・注記ボックス60）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表157点（データ表94・注記ボックス63）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表154点のうち、直後に出所らしき行があるのは25点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表157点のうち、直後に出所らしき行があるのは25点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表154点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表157点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -978,11 +978,7 @@
           <t>２　障がい者手帳の所持者数</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>なお、障がい福祉サービスの対象となるのは手帳の所持者だけではありません。障害</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>図２-２　障がい者手帳所持者数の推移</t>
@@ -6020,7 +6016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6592,7 +6588,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>表２-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -6602,27 +6598,31 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>６　障がい児の就学状況</t>
+          <t>２　障がい者手帳の所持者数</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>学校名 / 小学部 / 中学部 / 高等部</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-113）】障がい者手帳所持者数について、令和６年・令和７年・令和８年の各４月１日現在の数値を、身体障害者</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>表２-3</t>
+          <t>表２-2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -6636,14 +6636,14 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>学校名 / 在籍者数</t>
+          <t>学校名 / 小学部 / 中学部 / 高等部</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr"/>
@@ -6652,7 +6652,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>表２-4</t>
+          <t>表２-3</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -6662,18 +6662,18 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>７　アンケート調査の実施と結果</t>
+          <t>６　障がい児の就学状況</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>項目 / 障がい者調査 / 障がい児調査</t>
+          <t>学校名 / 在籍者数</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr"/>
@@ -6682,7 +6682,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>表２-5</t>
+          <t>表２-4</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -6699,24 +6699,20 @@
         <v>4</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>調査区分 / 配布数 / 有効回答数 / 有効回答率</t>
+          <t>項目 / 障がい者調査 / 障がい児調査</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>表２-6</t>
+          <t>表２-5</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -6730,14 +6726,14 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>分野 / 主な調査結果 / 割合</t>
+          <t>調査区分 / 配布数 / 有効回答数 / 有効回答率</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
@@ -6750,7 +6746,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>表２-7</t>
+          <t>表２-6</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -6764,14 +6760,14 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>項目 / 全体 （n=38） / 身体障がい （n=29） / 知的障がい （n=2）</t>
+          <t>分野 / 主な調査結果 / 割合</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr"/>
@@ -6784,7 +6780,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>表２-8</t>
+          <t>表２-7</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -6798,23 +6794,27 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>主な課題 / 主な調査結果 / 本計画での主な対応（関連箇所）</t>
+          <t>項目 / 全体 （n=38） / 身体障がい （n=29） / 知的障がい （n=2）</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>表２-9</t>
+          <t>表２-8</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -6828,14 +6828,14 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>用いること / 本村での例</t>
+          <t>主な課題 / 主な調査結果 / 本計画での主な対応（関連箇所）</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr"/>
@@ -6844,41 +6844,37 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表２-9</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第３章　第４次北塩原</t>
+          <t>第２章　本村の障がい</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>１　基本理念</t>
+          <t>７　アンケート調査の実施と結果</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr"/>
+          <t>用いること / 本村での例</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>表３-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -6888,31 +6884,31 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>３　基本施策の目標値と本計画期間</t>
+          <t>１　基本理念</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>基本施策 / 指標項目 / 現状 （R5） / 目標 （R11）</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>「障がいのあるなしに関わらず、お互いの人格や個性を尊重し、多様な価値観を認め合い、誰もが自分らしく輝くむら」</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表３-1</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -6926,27 +6922,27 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-111）】村の生涯学習、スポーツ及び文化の事業について、障がいのある方の参加の実績（令和６年度・令和７年</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
+          <t>基本施策 / 指標項目 / 現状 （R5） / 目標 （R11）</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>表３-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -6960,57 +6956,57 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>区分 / 意味</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-111）】村の生涯学習、スポーツ及び文化の事業について、障がいのある方の参加の実績（令和６年度・令和７年</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>表４-1</t>
+          <t>表３-2</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>第４章　障がい福祉計</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>１　第７期計画の成果目標の達成状</t>
+          <t>３　基本施策の目標値と本計画期間</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+          <t>区分 / 意味</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-1</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -7020,31 +7016,31 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>２　令和11年度に向けた成果目標</t>
+          <t>１　第７期計画の成果目標の達成状</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr"/>
+          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>表４-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -7058,23 +7054,27 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>表４-3</t>
+          <t>表４-2</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -7088,14 +7088,14 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E37" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr"/>
@@ -7104,7 +7104,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-3</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -7118,22 +7118,18 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr"/>
+          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7159,7 +7155,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -7172,7 +7168,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>表４-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -7186,23 +7182,27 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>表４-5</t>
+          <t>表４-4</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -7216,14 +7216,14 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr"/>
@@ -7232,7 +7232,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>表４-6</t>
+          <t>表４-5</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -7246,14 +7246,14 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>項目 / 値 / 考え方</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr"/>
@@ -7262,7 +7262,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-6</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -7276,26 +7276,18 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>項目 / 値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -7321,7 +7313,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -7329,7 +7321,11 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -7355,7 +7351,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -7368,7 +7364,7 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>表４-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -7382,23 +7378,27 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>表４-7</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -7412,14 +7412,14 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr"/>
@@ -7428,7 +7428,7 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7442,22 +7442,18 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -7483,7 +7479,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -7496,7 +7492,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7510,23 +7506,27 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7540,22 +7540,18 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7581,7 +7577,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -7594,7 +7590,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -7608,23 +7604,27 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr"/>
-      <c r="H53" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -7638,22 +7638,18 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -7679,7 +7675,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -7692,7 +7688,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7706,23 +7702,27 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -7736,14 +7736,14 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E57" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr"/>
@@ -7752,7 +7752,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7766,27 +7766,23 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr"/>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7800,23 +7796,27 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7830,27 +7830,23 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7864,22 +7860,22 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr"/>
+          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -7905,7 +7901,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -7918,7 +7914,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7932,23 +7928,27 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7962,22 +7962,18 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="9" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -8003,7 +7999,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -8016,7 +8012,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8030,23 +8026,27 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -8060,22 +8060,18 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -8090,7 +8086,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
@@ -8101,7 +8097,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -8114,7 +8110,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -8128,44 +8124,48 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -8174,7 +8174,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8188,14 +8188,14 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr"/>
@@ -8204,7 +8204,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8218,14 +8218,14 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -8234,7 +8234,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8248,27 +8248,23 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8282,27 +8278,27 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8323,16 +8319,20 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="9" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8346,14 +8346,14 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -8362,7 +8362,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8376,27 +8376,23 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8410,27 +8406,27 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8451,16 +8447,20 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8474,27 +8474,23 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E80" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E80" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8508,21 +8504,17 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr"/>
       <c r="H81" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8532,7 +8524,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8546,17 +8538,21 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8566,7 +8562,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8587,16 +8583,20 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="9" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8610,22 +8610,18 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -8651,7 +8647,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -8664,7 +8660,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8678,27 +8674,27 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8719,16 +8715,20 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8742,27 +8742,23 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8776,23 +8772,27 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8806,23 +8806,27 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="9" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8836,27 +8840,23 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H91" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8866,31 +8866,27 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8900,26 +8896,26 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -8945,7 +8941,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -8958,7 +8954,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8972,18 +8968,22 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9036,27 +9036,23 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9070,18 +9066,22 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -9120,7 +9120,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9134,14 +9134,14 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr"/>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -9184,7 +9184,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9198,27 +9198,23 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9232,23 +9228,27 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9262,23 +9262,27 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9295,11 +9299,11 @@
         <v>5</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
@@ -9308,7 +9312,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9322,27 +9326,23 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr"/>
+          <t>備える事項 / 本村の取組み</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9356,14 +9356,14 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -9406,7 +9406,7 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9423,11 +9423,11 @@
         <v>7</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr"/>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -9470,7 +9470,7 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9484,14 +9484,14 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -9534,7 +9534,7 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9548,14 +9548,14 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr"/>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -9598,7 +9598,7 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9615,11 +9615,11 @@
         <v>5</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -9662,7 +9662,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9676,27 +9676,23 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9706,31 +9702,31 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9740,27 +9736,31 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr"/>
-      <c r="H119" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9774,27 +9774,27 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9808,14 +9808,14 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9838,18 +9838,22 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -9875,7 +9879,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
@@ -9888,7 +9892,7 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9898,31 +9902,27 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="9" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9932,18 +9932,18 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D125" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9952,7 +9952,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9962,27 +9962,31 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9992,27 +9996,31 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10022,31 +10030,27 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10060,14 +10064,14 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E129" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
@@ -10076,7 +10080,7 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10090,27 +10094,23 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10124,23 +10124,27 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10154,14 +10158,14 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
@@ -10170,7 +10174,7 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10184,23 +10188,27 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10214,27 +10222,23 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H134" s="6" t="inlineStr"/>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="9" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10248,27 +10252,23 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10282,27 +10282,23 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="9" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10312,27 +10308,31 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10342,26 +10342,26 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr"/>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
@@ -10400,7 +10400,7 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10410,31 +10410,27 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+          <t>分野 / 関係機関 / 連携の内容</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H140" s="9" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10444,31 +10440,31 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr"/>
-      <c r="H141" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10478,31 +10474,31 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10516,48 +10512,48 @@
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="inlineStr"/>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
@@ -10570,28 +10566,28 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr"/>
@@ -10604,41 +10600,41 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10648,31 +10644,31 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H147" s="8" t="inlineStr"/>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10682,27 +10678,31 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="9" t="inlineStr"/>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10712,82 +10712,86 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>【村・県へ確認（Ｓ-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H149" s="8" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr"/>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E151" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr"/>
@@ -10796,37 +10800,41 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="9" t="inlineStr"/>
+          <t>【村・県へ確認（Ｓ-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -10836,31 +10844,27 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H153" s="8" t="inlineStr"/>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr"/>
+      <c r="H153" s="9" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -10870,7 +10874,7 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
@@ -10881,7 +10885,7 @@
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr"/>
@@ -10890,7 +10894,7 @@
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -10900,82 +10904,82 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G155" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H155" s="8" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr"/>
+      <c r="H155" s="9" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E156" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr"/>
-      <c r="H156" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E157" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr"/>
@@ -10984,37 +10988,41 @@
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E158" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -11024,22 +11032,112 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr"/>
       <c r="H159" s="9" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>表８-2</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>３　計画の策定経過</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E160" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="9" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D161" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G161" s="8" t="inlineStr"/>
+      <c r="H161" s="9" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E162" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表157点（データ表94・注記ボックス63）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表159点（データ表94・注記ボックス65）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表157点のうち、直後に出所らしき行があるのは25点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表159点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表157点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表159点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>５　地域における権利擁護の支</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -6016,7 +6016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8293,12 +8293,16 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8312,27 +8316,27 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8353,16 +8357,20 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="9" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8376,14 +8384,14 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
@@ -8392,7 +8400,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8406,27 +8414,23 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8440,27 +8444,27 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8481,16 +8485,20 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="9" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8504,27 +8512,23 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E81" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E81" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8538,21 +8542,17 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8562,7 +8562,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8576,17 +8576,21 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8596,7 +8600,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8617,16 +8621,20 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8640,22 +8648,18 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -8681,7 +8685,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -8694,7 +8698,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8708,27 +8712,27 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8749,16 +8753,20 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8772,27 +8780,23 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8806,27 +8810,27 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8847,16 +8851,20 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="9" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8870,14 +8878,14 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr"/>
@@ -8886,7 +8894,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8900,22 +8908,18 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -8930,7 +8934,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D94" s="6" t="n">
@@ -8941,7 +8945,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -8954,7 +8958,7 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8968,27 +8972,27 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -9002,27 +9006,27 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr"/>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9036,23 +9040,27 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9066,22 +9074,18 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -9107,7 +9111,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -9120,7 +9124,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9134,23 +9138,27 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9164,27 +9172,23 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9198,23 +9202,27 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9228,22 +9236,18 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -9269,7 +9273,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日を確認</t>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -9282,7 +9286,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9296,23 +9300,27 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9326,14 +9334,14 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr"/>
@@ -9342,7 +9350,7 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9356,14 +9364,14 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E107" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
@@ -9372,7 +9380,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9386,27 +9394,27 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9420,23 +9428,31 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9450,27 +9466,23 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9484,23 +9496,27 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9514,27 +9530,23 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9548,23 +9560,27 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9578,27 +9594,23 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9612,23 +9624,27 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9642,27 +9658,23 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H116" s="6" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9676,23 +9688,27 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9706,22 +9722,18 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -9747,7 +9759,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
@@ -9760,7 +9772,7 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9770,31 +9782,31 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9815,16 +9827,20 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="9" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9838,22 +9854,18 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="9" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -9879,7 +9891,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
@@ -9892,7 +9904,7 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9906,23 +9918,27 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9936,14 +9952,14 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9952,7 +9968,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9966,22 +9982,18 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -9996,7 +10008,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
@@ -10007,7 +10019,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
@@ -10020,7 +10032,7 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10034,23 +10046,27 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10060,18 +10076,18 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
@@ -10080,7 +10096,7 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10094,14 +10110,14 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr"/>
@@ -10110,7 +10126,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10124,27 +10140,23 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H131" s="8" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="9" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10158,23 +10170,27 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10188,27 +10204,23 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10222,23 +10234,27 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10252,14 +10268,14 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E135" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr"/>
@@ -10268,7 +10284,7 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10282,14 +10298,14 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10298,7 +10314,7 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10312,27 +10328,23 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="9" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10346,27 +10358,27 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10380,27 +10392,27 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H139" s="8" t="inlineStr"/>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10410,27 +10422,31 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10444,22 +10460,18 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H141" s="8" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="9" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -10485,7 +10497,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
@@ -10498,7 +10510,7 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10508,31 +10520,31 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr"/>
-      <c r="H143" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10546,14 +10558,14 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E144" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E144" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
@@ -10566,7 +10578,7 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10580,14 +10592,14 @@
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E145" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr"/>
@@ -10600,7 +10612,7 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10614,61 +10626,61 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H146" s="6" t="inlineStr"/>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr"/>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr"/>
-      <c r="H147" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10682,14 +10694,14 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E148" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr"/>
@@ -10702,7 +10714,7 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10716,14 +10728,14 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr"/>
@@ -10736,7 +10748,7 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10746,31 +10758,31 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H150" s="6" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10784,23 +10796,27 @@
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr"/>
-      <c r="H151" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10810,91 +10826,95 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>【村・県へ確認（Ｓ-13）】民法等の一部を改正する法律（成年後見等関係）の法律番号、公布日及び施行期日を確認してください</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H152" s="6" t="inlineStr"/>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr"/>
+      <c r="H152" s="9" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr"/>
-      <c r="H153" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>５　地域における権利擁護の支援の</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E154" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -10904,18 +10924,18 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
@@ -10924,7 +10944,7 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -10934,31 +10954,27 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E156" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H156" s="6" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr"/>
+      <c r="H156" s="9" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -10968,18 +10984,18 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E157" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr"/>
@@ -10998,7 +11014,7 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
@@ -11009,7 +11025,7 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -11022,28 +11038,28 @@
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr"/>
@@ -11052,37 +11068,41 @@
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -11092,18 +11112,18 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr"/>
@@ -11112,7 +11132,7 @@
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -11122,22 +11142,82 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E162" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr"/>
       <c r="H162" s="9" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr"/>
+      <c r="H163" s="9" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E164" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr"/>
+      <c r="H164" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表159点（データ表94・注記ボックス65）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表162点（データ表94・注記ボックス68）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表159点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表162点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表159点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表162点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6016,7 +6016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6976,7 +6976,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>表３-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -6990,57 +6990,57 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>区分 / 意味</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-119）】①避難行動要支援者名簿の掲載者数、平常時からの提供に同意している方の人数、及び名簿を提供してい</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>表４-1</t>
+          <t>表３-2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>第４章　障がい福祉計</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>１　第７期計画の成果目標の達成状</t>
+          <t>３　基本施策の目標値と本計画期間</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+          <t>区分 / 意味</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-1</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -7050,31 +7050,31 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>２　令和11年度に向けた成果目標</t>
+          <t>１　第７期計画の成果目標の達成状</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
+          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>表４-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -7088,23 +7088,27 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>表４-3</t>
+          <t>表４-2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -7118,14 +7122,14 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -7134,7 +7138,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-3</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -7148,22 +7152,18 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr"/>
+          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -7202,7 +7202,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>表４-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -7216,23 +7216,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>表４-5</t>
+          <t>表４-4</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -7246,14 +7250,14 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr"/>
@@ -7262,7 +7266,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>表４-6</t>
+          <t>表４-5</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -7276,14 +7280,14 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>項目 / 値 / 考え方</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr"/>
@@ -7292,7 +7296,7 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-6</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -7306,26 +7310,18 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>項目 / 値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -7351,7 +7347,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -7359,7 +7355,11 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -7398,7 +7398,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>表４-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -7412,23 +7412,27 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr"/>
-      <c r="H47" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>表４-7</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7442,14 +7446,14 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr"/>
@@ -7458,7 +7462,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -7472,22 +7476,18 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7540,23 +7540,27 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr"/>
-      <c r="H51" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -7570,22 +7574,18 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -7624,7 +7624,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -7638,18 +7638,22 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-120）】医療的ケアについて、①村内及び圏域に喀痰吸引等の研修を修了して認定を受けた方がいるか（人数、所</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -7675,7 +7679,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
+          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -7688,7 +7692,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7702,27 +7706,23 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -7736,23 +7736,27 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7766,23 +7770,27 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7796,27 +7804,23 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7837,7 +7841,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
@@ -7846,7 +7850,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7860,27 +7864,27 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr"/>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7894,27 +7898,23 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="9" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7928,27 +7928,27 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr"/>
+          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7962,18 +7962,22 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -7999,7 +8003,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -8012,7 +8016,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8026,27 +8030,23 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -8060,18 +8060,22 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -8097,7 +8101,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -8110,7 +8114,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -8120,31 +8124,27 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8154,78 +8154,86 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -8234,7 +8242,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8248,14 +8256,14 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
@@ -8264,7 +8272,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8278,31 +8286,23 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8316,27 +8316,23 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8350,17 +8346,21 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8370,7 +8370,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8384,23 +8384,27 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8414,23 +8418,27 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="9" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8444,27 +8452,23 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8478,27 +8482,23 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8512,23 +8512,27 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8542,14 +8546,14 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E82" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
@@ -8562,7 +8566,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8576,31 +8580,23 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H83" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8614,14 +8610,14 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
@@ -8634,7 +8630,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8648,23 +8644,31 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8678,27 +8682,27 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8712,27 +8716,23 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8746,27 +8746,27 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8780,23 +8780,27 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8810,27 +8814,27 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8844,27 +8848,23 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E91" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8878,23 +8878,27 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8908,23 +8912,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="9" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8938,27 +8946,23 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8968,31 +8972,27 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H95" s="8" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -9002,26 +9002,26 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -9060,7 +9060,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9074,18 +9074,22 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -9111,7 +9115,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -9145,7 +9149,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -9158,7 +9162,7 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9172,14 +9176,14 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+          <t>記録する事項 / ４町村で揃える定義</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr"/>
@@ -9209,7 +9213,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -9222,7 +9226,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9236,23 +9240,27 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9266,22 +9274,18 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -9307,7 +9311,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -9320,7 +9324,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9334,14 +9338,14 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr"/>
@@ -9350,7 +9354,7 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9364,23 +9368,27 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr"/>
-      <c r="H107" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9394,27 +9402,27 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9428,31 +9436,23 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9466,14 +9466,14 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr"/>
@@ -9482,7 +9482,7 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9496,27 +9496,27 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9530,23 +9530,31 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9560,27 +9568,23 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9594,23 +9598,27 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9624,27 +9632,23 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H115" s="8" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9658,23 +9662,27 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9688,27 +9696,23 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -9722,23 +9726,27 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9752,22 +9760,18 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -9793,7 +9797,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -9806,7 +9810,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9816,31 +9820,27 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9850,22 +9850,26 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -9880,7 +9884,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
@@ -9891,7 +9895,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
@@ -9904,7 +9908,7 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9918,27 +9922,27 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9952,14 +9956,14 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9968,7 +9972,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9982,18 +9986,22 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -10019,7 +10027,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
@@ -10032,7 +10040,7 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10042,31 +10050,27 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10076,18 +10080,18 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr"/>
@@ -10096,7 +10100,7 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10106,27 +10110,31 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10136,27 +10144,31 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10166,31 +10178,27 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr"/>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="9" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10204,14 +10212,14 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E133" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr"/>
@@ -10220,7 +10228,7 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10234,27 +10242,23 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H134" s="6" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="9" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10268,23 +10272,27 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10298,14 +10306,14 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10314,7 +10322,7 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10328,23 +10336,27 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10358,27 +10370,23 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr"/>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="9" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10392,27 +10400,23 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H139" s="9" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10426,27 +10430,23 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H140" s="6" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr"/>
+      <c r="H140" s="9" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10456,27 +10456,31 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr"/>
-      <c r="H141" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10486,26 +10490,26 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="inlineStr"/>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
@@ -10520,7 +10524,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
@@ -10531,7 +10535,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
@@ -10544,7 +10548,7 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10554,31 +10558,27 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+          <t>分野 / 関係機関 / 連携の内容</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H144" s="9" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10588,31 +10588,31 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr"/>
-      <c r="H145" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10622,31 +10622,31 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10660,48 +10660,48 @@
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H147" s="8" t="inlineStr"/>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr"/>
@@ -10714,28 +10714,28 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr"/>
@@ -10748,41 +10748,41 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10792,31 +10792,31 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H151" s="8" t="inlineStr"/>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr"/>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10826,27 +10826,31 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="9" t="inlineStr"/>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -10856,26 +10860,26 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H153" s="8" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr"/>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -10890,7 +10894,7 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>５　地域における権利擁護の支援の</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
@@ -10901,7 +10905,7 @@
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
@@ -10914,28 +10918,28 @@
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
@@ -10944,67 +10948,75 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E156" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr"/>
-      <c r="H156" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>５　地域における権利擁護の支援の</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
-        </is>
-      </c>
-      <c r="G157" s="8" t="inlineStr"/>
-      <c r="H157" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H157" s="8" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -11014,31 +11026,27 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E158" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H158" s="6" t="inlineStr"/>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="9" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -11048,7 +11056,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
@@ -11059,7 +11067,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr"/>
@@ -11068,7 +11076,7 @@
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -11078,82 +11086,82 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H160" s="6" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="9" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G161" s="8" t="inlineStr"/>
-      <c r="H161" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E162" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr"/>
@@ -11162,37 +11170,41 @@
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D163" s="8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
-        </is>
-      </c>
-      <c r="G163" s="8" t="inlineStr"/>
-      <c r="H163" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
@@ -11202,22 +11214,112 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E164" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr"/>
       <c r="H164" s="9" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>表８-2</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>３　計画の策定経過</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr"/>
+      <c r="H165" s="9" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E166" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr"/>
+      <c r="H166" s="9" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E167" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr"/>
+      <c r="H167" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表162点（データ表94・注記ボックス68）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表164点（データ表95・注記ボックス69）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表162点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表164点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表162点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表164点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6016,7 +6016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-113）】障がい者手帳所持者数について、令和６年・令和７年・令和８年の各４月１日現在の数値を、身体障害者</t>
+          <t>【村へ確認（Ｍ-113・Ｍ-124）】障がい者手帳所持者数について、身体障害者手帳の令和６年・令和７年の各４月１日現在の</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -7040,36 +7040,32 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>表４-1</t>
+          <t>表３-3</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>第４章　障がい福祉計</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>１　第７期計画の成果目標の達成状</t>
+          <t>４　本計画で新たに加える施策</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
+          <t>新たに加える施策 / 主な内容 / 本計画での位置と対応する基本施策</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7079,12 +7075,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>第４章　障がい福祉計</t>
+          <t>第３章　第４次北塩原</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>２　令和11年度に向けた成果目標</t>
+          <t>４　本計画で新たに加える施策</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
@@ -7095,7 +7091,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
+          <t>【表３-３の読み方】ここに掲げた施策は、いずれも本計画の第４章から第６章までに具体的な内容を書いています。本節はその所在</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -7108,7 +7104,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>表４-2</t>
+          <t>表４-1</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -7118,27 +7114,31 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>２　令和11年度に向けた成果目標</t>
+          <t>１　第７期計画の成果目標の達成状</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
+          <t>成果目標 / 項目 / 第７期目標 （令和８年度末） / 実績 （見込み）</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>表４-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -7152,23 +7152,27 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の方法 / 確認の時期</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr"/>
-      <c r="H39" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和７年度末の施設入所者数の６％以上が地域生活に移行 ② 令和７年度末時点の施設入所者数から５％以</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-2</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -7182,27 +7186,23 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-3</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -7216,27 +7216,23 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr"/>
+          <t>確認する事項 / 確認の方法 / 確認の時期</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>表４-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -7250,23 +7246,27 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>表４-5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -7280,23 +7280,27 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 精神病床から退院後１年以内の地域における平均生活日数：319.3日以上（県） ② 精神病床への再入</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>表４-6</t>
+          <t>表４-4</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -7310,14 +7314,14 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>項目 / 値 / 考え方</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr"/>
@@ -7326,7 +7330,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-5</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -7340,31 +7344,23 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-6</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -7378,22 +7374,18 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr"/>
+          <t>項目 / 値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -7419,7 +7411,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -7427,12 +7419,16 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>表４-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7446,23 +7442,27 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -7476,23 +7476,27 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-7</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7506,27 +7510,23 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7540,27 +7540,23 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -7574,18 +7570,22 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="9" t="inlineStr"/>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -7624,7 +7624,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -7638,22 +7638,18 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-120）】医療的ケアについて、①村内及び圏域に喀痰吸引等の研修を修了して認定を受けた方がいるか（人数、所</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -7679,7 +7675,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -7692,7 +7688,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7706,18 +7702,22 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-120）】医療的ケアについて、①村内及び圏域に喀痰吸引等の研修を修了して認定を受けた方がいるか（人数、所</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
+          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7770,27 +7770,23 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -7804,23 +7800,27 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7834,23 +7834,27 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7864,27 +7868,23 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="9" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -7914,7 +7914,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7928,27 +7928,27 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7962,27 +7962,23 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="9" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7996,27 +7992,27 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr"/>
+          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8030,18 +8026,22 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -8080,7 +8080,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8094,27 +8094,23 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -8128,18 +8124,22 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -8178,7 +8178,7 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8188,31 +8188,27 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8222,78 +8218,86 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -8302,7 +8306,7 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -8316,14 +8320,14 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
@@ -8332,7 +8336,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8346,31 +8350,23 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8384,27 +8380,23 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8418,17 +8410,21 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8438,7 +8434,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8452,23 +8448,27 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8482,23 +8482,27 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="9" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8512,27 +8516,23 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H81" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8546,27 +8546,23 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8580,23 +8576,27 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8610,14 +8610,14 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E84" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8644,31 +8644,23 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8682,14 +8674,14 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
@@ -8702,7 +8694,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8716,23 +8708,31 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8746,27 +8746,27 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8780,27 +8780,23 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8814,27 +8810,27 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8848,23 +8844,27 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8878,27 +8878,27 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8912,27 +8912,23 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E93" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8946,23 +8942,27 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8976,23 +8976,27 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -9006,27 +9010,23 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9036,31 +9036,27 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H97" s="8" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9070,26 +9066,26 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -9115,7 +9111,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -9128,7 +9124,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9142,27 +9138,27 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr"/>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9176,18 +9172,22 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -9226,7 +9226,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9240,27 +9240,23 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9274,18 +9270,22 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -9324,7 +9324,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9338,14 +9338,14 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -9388,7 +9388,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9402,27 +9402,23 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9436,23 +9432,27 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9466,23 +9466,27 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9499,24 +9503,20 @@
         <v>5</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9530,31 +9530,23 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>備える事項 / 本村の取組み</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9568,18 +9560,22 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -9605,7 +9601,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -9613,12 +9609,16 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H114" s="6" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9635,11 +9635,11 @@
         <v>7</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -9682,7 +9682,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9696,14 +9696,14 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr"/>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -9746,7 +9746,7 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9760,14 +9760,14 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -9810,7 +9810,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9827,11 +9827,11 @@
         <v>5</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -9874,7 +9874,7 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9888,27 +9888,23 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="9" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9918,31 +9914,31 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9952,27 +9948,31 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9986,27 +9986,27 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -10020,27 +10020,23 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H127" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10054,23 +10050,27 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10084,23 +10084,27 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10114,27 +10118,23 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10144,31 +10144,27 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H131" s="8" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="9" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10178,27 +10174,31 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10208,27 +10208,31 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10238,18 +10242,18 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr"/>
@@ -10258,7 +10262,7 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10272,27 +10276,23 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H135" s="8" t="inlineStr"/>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10306,14 +10306,14 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr">
@@ -10356,7 +10356,7 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10370,14 +10370,14 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr"/>
@@ -10386,7 +10386,7 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10400,23 +10400,27 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10430,14 +10434,14 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10446,7 +10450,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10460,27 +10464,23 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H141" s="8" t="inlineStr"/>
+          <t>確認する事項 / 確認の内容</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="9" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10501,15 +10501,11 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H142" s="9" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
@@ -10535,7 +10531,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
@@ -10548,7 +10544,7 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10558,22 +10554,26 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E144" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="9" t="inlineStr"/>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10626,27 +10626,23 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H146" s="6" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr"/>
+      <c r="H146" s="9" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10656,31 +10652,31 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr"/>
-      <c r="H147" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10690,31 +10686,31 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10728,14 +10724,14 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr"/>
@@ -10748,7 +10744,7 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10762,48 +10758,48 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H150" s="6" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr"/>
@@ -10816,41 +10812,41 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -10864,14 +10860,14 @@
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr"/>
@@ -10884,7 +10880,7 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -10894,31 +10890,31 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E154" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H154" s="6" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr"/>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -10928,22 +10924,26 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
-      <c r="H155" s="9" t="inlineStr"/>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -10982,7 +10982,7 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -10992,91 +10992,95 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>５　地域における権利擁護の支援の</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
-        </is>
-      </c>
-      <c r="G157" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H157" s="8" t="inlineStr"/>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr"/>
+      <c r="H157" s="9" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E158" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>５　地域における権利擁護の支援の</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G159" s="8" t="inlineStr"/>
-      <c r="H159" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H159" s="8" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -11086,18 +11090,18 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr"/>
@@ -11106,7 +11110,7 @@
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -11116,31 +11120,27 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G161" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H161" s="8" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G161" s="8" t="inlineStr"/>
+      <c r="H161" s="9" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -11150,18 +11150,18 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E162" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr"/>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D163" s="8" t="n">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
@@ -11204,28 +11204,28 @@
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E164" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr"/>
@@ -11234,37 +11234,41 @@
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G165" s="8" t="inlineStr"/>
-      <c r="H165" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H165" s="8" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -11274,18 +11278,18 @@
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E166" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr"/>
@@ -11294,7 +11298,7 @@
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -11304,22 +11308,82 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E167" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr"/>
       <c r="H167" s="9" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E168" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr"/>
+      <c r="H168" s="9" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr"/>
+      <c r="H169" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12217,7 +12281,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>図表番号を振り、目次の後に図表目次を置くことを提案したい。番号の形（図１-１・表１-１）と、注記ボックスには番号を振らないことを合わせたい。令和8年10月10日に当方で図26点・表94点に番号と表題を付け、図表目次を置いた（北塩原村_図表番号一覧.xlsx）。これに伴う確認３件はＳ-22〜Ｓ-24として同書に立てている</t>
+          <t>図表番号を振り、目次の後に図表目次を置くことを提案したい。番号の形（図１-１・表１-１）と、注記ボックスには番号を振らないことを合わせたい。令和8年10月10日に当方で図26点・表95点に番号と表題を付け、図表目次を置いた（北塩原村_図表番号一覧.xlsx）。これに伴う確認３件はＳ-22〜Ｓ-24として同書に立てている</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表164点（データ表95・注記ボックス69）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表166点（データ表95・注記ボックス71）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表164点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表166点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表164点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表166点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6016,7 +6016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7756,7 +7756,7 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7770,18 +7770,22 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr"/>
+          <t>【医療的ケア者の数え方】基本指針の改正案は、医療的ケア者を二つに分けて定めています。一つは、日常生活及び社会生活を営むた</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -7807,7 +7811,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
+          <t>【村へ確認（Ｍ-126）】①県の医療的ケア児等支援地域協議会の設置の時期と、本村が参画できるかどうか。②本村が設ける協議</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -7820,7 +7824,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7834,27 +7838,23 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7868,23 +7868,27 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7898,23 +7902,27 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7928,27 +7936,23 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7969,7 +7973,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -7978,7 +7982,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7992,27 +7996,27 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8026,27 +8030,23 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -8060,27 +8060,27 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr"/>
+          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8094,18 +8094,22 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -8131,7 +8135,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -8144,7 +8148,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8158,27 +8162,23 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8192,18 +8192,22 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -8229,7 +8233,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -8242,7 +8246,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8252,31 +8256,27 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8286,78 +8286,86 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -8366,7 +8374,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -8380,14 +8388,14 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
@@ -8396,7 +8404,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8410,31 +8418,23 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8448,27 +8448,23 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr"/>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8482,17 +8478,21 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8502,7 +8502,7 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -8516,23 +8516,27 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8546,23 +8550,27 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="9" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8576,27 +8584,23 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H83" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8610,27 +8614,23 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>確かめる側 / 確かめる事項</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8644,23 +8644,27 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8674,14 +8678,14 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E86" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E86" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
@@ -8694,7 +8698,7 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8708,31 +8712,23 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8746,14 +8742,14 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
@@ -8766,7 +8762,7 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8780,23 +8776,31 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8810,27 +8814,27 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8844,27 +8848,23 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H91" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8878,27 +8878,27 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8912,23 +8912,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8942,27 +8946,27 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8976,27 +8980,23 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E95" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -9010,23 +9010,27 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9040,23 +9044,27 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9070,27 +9078,23 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9100,31 +9104,27 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H99" s="8" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9134,26 +9134,26 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9206,27 +9206,27 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr"/>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9240,18 +9240,22 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -9277,7 +9281,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -9290,7 +9294,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9304,27 +9308,23 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H105" s="8" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9338,18 +9338,22 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -9375,7 +9379,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -9388,7 +9392,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9402,14 +9406,14 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr"/>
@@ -9439,7 +9443,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -9452,7 +9456,7 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9466,27 +9470,23 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9500,23 +9500,27 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9530,23 +9534,27 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9563,24 +9571,20 @@
         <v>5</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9594,31 +9598,23 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>備える事項 / 本村の取組み</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9632,18 +9628,22 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>確かめること / 確かめ方</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="9" t="inlineStr"/>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -9677,12 +9677,16 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H116" s="6" t="inlineStr"/>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9699,11 +9703,11 @@
         <v>7</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr"/>
@@ -9733,7 +9737,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -9746,7 +9750,7 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9760,14 +9764,14 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
@@ -9797,7 +9801,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -9810,7 +9814,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9824,14 +9828,14 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9861,7 +9865,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -9874,7 +9878,7 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9891,11 +9895,11 @@
         <v>5</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr"/>
@@ -9925,7 +9929,7 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -9938,7 +9942,7 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9952,27 +9956,23 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9982,31 +9982,31 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -10016,27 +10016,31 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10050,27 +10054,27 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10084,27 +10088,23 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H129" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10118,23 +10118,27 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10148,23 +10152,27 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10178,27 +10186,23 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="9" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10208,31 +10212,27 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -10242,27 +10242,31 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10272,27 +10276,31 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10302,18 +10310,18 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10322,7 +10330,7 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10336,27 +10344,23 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="inlineStr"/>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="9" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10370,14 +10374,14 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr"/>
@@ -10407,7 +10411,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
@@ -10420,7 +10424,7 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10434,14 +10438,14 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10450,7 +10454,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10464,23 +10468,27 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr"/>
-      <c r="H141" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10494,14 +10502,14 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr"/>
@@ -10510,7 +10518,7 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10524,27 +10532,23 @@
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="inlineStr"/>
+          <t>確認する事項 / 確認の内容</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="9" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10565,15 +10569,11 @@
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+          <t>時期 / 行うこと / 担当</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H144" s="9" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10622,22 +10622,26 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E146" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="9" t="inlineStr"/>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
@@ -10652,7 +10656,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D147" s="8" t="n">
@@ -10663,7 +10667,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
@@ -10676,7 +10680,7 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10690,27 +10694,23 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H148" s="6" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="9" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10720,31 +10720,31 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr"/>
-      <c r="H149" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10754,31 +10754,31 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10792,14 +10792,14 @@
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr"/>
@@ -10812,7 +10812,7 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10826,48 +10826,48 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H152" s="6" t="inlineStr"/>
+          <t>区分 / 金額 / 構成比</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr"/>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr"/>
@@ -10880,41 +10880,41 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E154" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -10928,14 +10928,14 @@
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
@@ -10948,7 +10948,7 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -10958,31 +10958,31 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E156" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H156" s="6" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr"/>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -10992,22 +10992,26 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr"/>
-      <c r="H157" s="9" t="inlineStr"/>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
@@ -11022,7 +11026,7 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
@@ -11033,7 +11037,7 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -11046,7 +11050,7 @@
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -11056,91 +11060,95 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>５　地域における権利擁護の支援の</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
-        </is>
-      </c>
-      <c r="G159" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H159" s="8" t="inlineStr"/>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr"/>
+      <c r="H159" s="9" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>５　地域における権利擁護の支援の</t>
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G161" s="8" t="inlineStr"/>
-      <c r="H161" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+        </is>
+      </c>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -11150,18 +11158,18 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E162" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr"/>
@@ -11170,7 +11178,7 @@
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -11180,31 +11188,27 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D163" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G163" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H163" s="8" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr"/>
+      <c r="H163" s="9" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
@@ -11214,18 +11218,18 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E164" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>事項 / 両計画での扱い</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr"/>
@@ -11244,7 +11248,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D165" s="8" t="n">
@@ -11255,7 +11259,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
@@ -11268,28 +11272,28 @@
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E166" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr"/>
@@ -11298,37 +11302,41 @@
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
-        </is>
-      </c>
-      <c r="G167" s="8" t="inlineStr"/>
-      <c r="H167" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H167" s="8" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -11338,18 +11346,18 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr"/>
@@ -11358,7 +11366,7 @@
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -11368,22 +11376,82 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D169" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E169" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr"/>
       <c r="H169" s="9" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E170" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr"/>
+      <c r="H170" s="9" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr"/>
+      <c r="H171" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>3</v>

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表166点（データ表95・注記ボックス71）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表171点（データ表96・注記ボックス75）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表166点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表171点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表166点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表171点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6016,7 +6016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>3</v>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【村へ確認（Ｓ-38）】精神科病床における１年以上の入院患者数について、第７期福島県障がい福祉計画は令和６年度の計画で令</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -7496,7 +7496,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>表４-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -7510,23 +7510,27 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 一般就労への移行者数：令和６年度実績の1.31倍以上 ② 就労移行支援事業利用終了者に占める一般就</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>表４-7</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -7540,14 +7544,14 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr"/>
@@ -7556,7 +7560,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -7570,22 +7574,18 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -7624,7 +7624,7 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -7638,23 +7638,27 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -7668,22 +7672,18 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-120）】医療的ケアについて、①村内及び圏域に喀痰吸引等の研修を修了して認定を受けた方がいるか（人数、所</t>
+          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-120）】医療的ケアについて、①村内及び圏域に喀痰吸引等の研修を修了して認定を受けた方がいるか（人数、所</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>【医療的ケア者の数え方】基本指針の改正案は、医療的ケア者を二つに分けて定めています。一つは、日常生活及び社会生活を営むた</t>
+          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-126）】①県の医療的ケア児等支援地域協議会の設置の時期と、本村が参画できるかどうか。②本村が設ける協議</t>
+          <t>【医療的ケア者の数え方】基本指針の改正案は、医療的ケア者を二つに分けて定めています。一つは、日常生活及び社会生活を営むた</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -7824,7 +7824,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7838,23 +7838,27 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-126）】①県の医療的ケア児等支援地域協議会の設置の時期と、本村が参画できるかどうか。②本村が設ける協議</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-10</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7868,22 +7872,18 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr"/>
+          <t>記録する事項 / ねらい</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="9" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+          <t>【村へ確認（Ｍ-76・Ｍ-77）】上表の令和６・７年度の数値を確認します。本村は対象となる児童が少なく、実数を載せると個</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -7922,7 +7922,7 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>表４-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -7936,23 +7936,27 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までの間、各市町村において地域生活支援拠点等を整備するとともに、コーディネーターの配</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>表４-12</t>
+          <t>表４-11</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7966,14 +7970,14 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -7982,7 +7986,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-12</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -7996,27 +8000,23 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr"/>
+          <t>機能 / 本村での確保の方法 / 記録する実績</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>表４-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8030,23 +8030,27 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに各市町村において基幹相談支援センターを設置等し、相談支援体制の強化を図る体制を</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>表４-14</t>
+          <t>表４-13</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -8060,27 +8064,23 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E67" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+          <t>項目 / 数値 / 考え方</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-14</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8094,22 +8094,22 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr"/>
+          <t>基幹相談支援センター / 設置の形 / 対象となる市町村</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+          <t>【村へ確認（Ｍ-98）】会津北部４町村での広域設置について、令和８年度の協議の状況と、会津西部基幹相談支援センターの例に</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -8148,7 +8148,7 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>表４-15</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8162,23 +8162,27 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 都道府県における人材確保・生産性向上に関するワンストップ窓口の設置【新規】 ② 生産性向上等に向け</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-15</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -8192,22 +8196,18 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+          <t>【県へ確認（Ｓ-12）】意思決定支援ガイドライン（第２版）は令和８年９月に公表されました。県が実施する研修において第２版</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>表４-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -8260,23 +8260,27 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>項目 / 数値 / 考え方</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 令和11年度末までに都道府県及び市町村において障害福祉サービス等の質を向上させるための取組みに係る</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-16</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8290,22 +8294,18 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr"/>
+          <t>項目 / 数値 / 考え方</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>３　発達障がい者等に対する支援</t>
+          <t>２　令和11年度に向けた成果目標</t>
         </is>
       </c>
       <c r="D75" s="8" t="n">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+          <t>【村へ確認（Ｍ-103・Ｍ-104）】村が運営する障害福祉サービス等の事業所の有無と、村内の対象事業所の公表・更新の状況</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -8344,7 +8344,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>表４-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8358,44 +8358,48 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-105）】家庭・教育・福祉の連携を進める事業及び地域連携推進マネジャーの配置について、本村での実施の意向</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>表５-1</t>
+          <t>表４-17</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>第５章　障がい福祉サ</t>
+          <t>第４章　障がい福祉計</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>１　障がい福祉サービスの見込量</t>
+          <t>３　発達障がい者等に対する支援</t>
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>区分 / 主なサービス・事業</t>
+          <t>活動指標 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
@@ -8404,7 +8408,7 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>表５-2</t>
+          <t>表５-1</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8418,14 +8422,14 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>段階 / 何を見るか / 見落とすと起きること</t>
+          <t>区分 / 主なサービス・事業</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
@@ -8434,7 +8438,7 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>表５-3</t>
+          <t>表５-2</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -8448,14 +8452,14 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E79" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>加減 / 項目 / 拠り所</t>
+          <t>段階 / 何を見るか / 見落とすと起きること</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr"/>
@@ -8464,7 +8468,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-3</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -8478,26 +8482,18 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>加減 / 項目 / 拠り所</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -8523,7 +8519,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
+          <t>【本計画の見込量の位置づけ】本計画の策定時点では、65歳到達の台帳、卒業予定者の一覧及び事業所の受入余力の照会の回答が整</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
@@ -8531,12 +8527,16 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>表５-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -8550,27 +8550,27 @@
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-118）】サービスの量の中長期的な推計について、本計画に載せるか、次期計画（第９期）から載せるかの扱いを</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>表５-4</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -8591,16 +8591,20 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="9" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8614,14 +8618,14 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
@@ -8630,7 +8634,7 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8644,27 +8648,23 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8678,27 +8678,27 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8719,16 +8719,20 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8742,27 +8746,23 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E88" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E88" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8776,21 +8776,17 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
       <c r="H89" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8800,7 +8796,7 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8814,17 +8810,21 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -8834,7 +8834,7 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8855,16 +8855,20 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="9" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8878,22 +8882,18 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -8932,7 +8932,7 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8946,27 +8946,27 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8987,16 +8987,20 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -9010,27 +9014,23 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -9044,27 +9044,27 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9085,16 +9085,20 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9108,14 +9112,14 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
@@ -9124,7 +9128,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9138,22 +9142,18 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr"/>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D101" s="8" t="n">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -9206,27 +9206,27 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9240,22 +9240,22 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr"/>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -9308,23 +9308,27 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9338,22 +9342,18 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -9392,7 +9392,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9406,23 +9406,27 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9436,27 +9440,23 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H109" s="8" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9470,23 +9470,27 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9500,22 +9504,18 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -9554,7 +9554,7 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -9568,23 +9568,27 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9598,14 +9602,14 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr"/>
@@ -9614,7 +9618,7 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9628,27 +9632,23 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E115" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9662,21 +9662,17 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr"/>
       <c r="H116" s="6" t="inlineStr">
         <is>
           <t>あり</t>
@@ -9686,7 +9682,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9700,18 +9696,26 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -9737,7 +9741,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+          <t>【村へ確認（Ｓ-38）】福島県における災害拠点精神科病院の指定の状況（指定の有無、指定された病院の名称及び所在）と、ＤＰ</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -9750,7 +9754,7 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9767,11 +9771,11 @@
         <v>7</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr"/>
@@ -9801,7 +9805,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -9814,7 +9818,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9828,14 +9832,14 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr"/>
@@ -9865,7 +9869,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -9878,7 +9882,7 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9892,14 +9896,14 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr"/>
@@ -9929,7 +9933,7 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -9942,7 +9946,7 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9959,11 +9963,11 @@
         <v>5</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>記録する事項 / 記録の仕方</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr"/>
@@ -9993,7 +9997,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -10006,7 +10010,7 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -10020,27 +10024,23 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H127" s="8" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10050,31 +10050,31 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-129）】本村の救急搬送を担う消防本部と、冬季における搬送に要する時間（平時との差）を確かめてください。</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -10084,22 +10084,26 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -10114,7 +10118,7 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
@@ -10125,7 +10129,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -10138,7 +10142,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10152,27 +10156,27 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H131" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10186,14 +10190,14 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
@@ -10202,7 +10206,7 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10216,18 +10220,22 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -10253,7 +10261,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -10266,7 +10274,7 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10276,31 +10284,27 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H135" s="8" t="inlineStr"/>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10310,18 +10314,18 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10330,7 +10334,7 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10340,27 +10344,31 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr"/>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10370,27 +10378,31 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10400,31 +10412,27 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H139" s="8" t="inlineStr"/>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="9" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10438,14 +10446,14 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E140" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10454,7 +10462,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10468,27 +10476,23 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H141" s="8" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="9" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10502,23 +10506,27 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10532,14 +10540,14 @@
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>区分 / 該当するサービス / 扱い</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr"/>
@@ -10548,7 +10556,7 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10562,23 +10570,27 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10592,27 +10604,23 @@
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="inlineStr"/>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="9" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10626,27 +10634,23 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H146" s="9" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10660,27 +10664,23 @@
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H147" s="8" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="9" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10690,27 +10690,31 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10720,26 +10724,26 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H149" s="8" t="inlineStr"/>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr"/>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -10754,7 +10758,7 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
@@ -10765,7 +10769,7 @@
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -10778,7 +10782,7 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10788,31 +10792,27 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+          <t>分野 / 関係機関 / 連携の内容</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr"/>
-      <c r="H151" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H151" s="9" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10822,31 +10822,31 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -10856,31 +10856,31 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr"/>
-      <c r="H153" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -10894,48 +10894,48 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E154" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H154" s="6" t="inlineStr"/>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr"/>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
@@ -10948,28 +10948,28 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E156" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr"/>
@@ -10982,41 +10982,41 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G157" s="8" t="inlineStr"/>
-      <c r="H157" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H157" s="8" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -11026,31 +11026,31 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E158" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H158" s="6" t="inlineStr"/>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -11060,27 +11060,31 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr"/>
-      <c r="H159" s="9" t="inlineStr"/>
+      <c r="H159" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -11090,26 +11094,26 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H160" s="6" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
@@ -11124,7 +11128,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>５　地域における権利擁護の支援の</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D161" s="8" t="n">
@@ -11135,7 +11139,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
@@ -11148,28 +11152,28 @@
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E162" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr"/>
@@ -11178,67 +11182,75 @@
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D163" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G163" s="8" t="inlineStr"/>
-      <c r="H163" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>５　地域における権利擁護の支援の</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E164" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
-        </is>
-      </c>
-      <c r="G164" s="6" t="inlineStr"/>
-      <c r="H164" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -11248,31 +11260,27 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H165" s="8" t="inlineStr"/>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr"/>
+      <c r="H165" s="9" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -11282,7 +11290,7 @@
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D166" s="6" t="n">
@@ -11293,7 +11301,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr"/>
@@ -11302,7 +11310,7 @@
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -11312,82 +11320,82 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G167" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H167" s="8" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr"/>
+      <c r="H167" s="9" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G168" s="6" t="inlineStr"/>
-      <c r="H168" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D169" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E169" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr"/>
@@ -11396,28 +11404,28 @@
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表７-5</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>５　第８次福島県医療計画との連携</t>
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E170" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>医療計画の分野 / 県の主な内容 / 本計画での連携</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr"/>
@@ -11426,32 +11434,190 @@
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>５　第８次福島県医療計画との連携</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-129）】第８次福島県医療計画のうち第３章（医療圏と基準病床数）及び第10章（医療機関相互の連携、医療Ｄ</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H171" s="8" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>５　第８次福島県医療計画との連携</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>表８-1</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>２　北塩原村障がい者自立支援協議</t>
+        </is>
+      </c>
+      <c r="D173" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr"/>
+      <c r="H173" s="9" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>表８-2</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>３　計画の策定経過</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E174" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr"/>
+      <c r="H174" s="9" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G175" s="8" t="inlineStr"/>
+      <c r="H175" s="9" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
           <t>表８-4</t>
         </is>
       </c>
-      <c r="B171" s="4" t="inlineStr">
+      <c r="B176" s="5" t="inlineStr">
         <is>
           <t>第８章　資料編</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
+      <c r="C176" s="5" t="inlineStr">
         <is>
           <t>５　用語解説</t>
         </is>
       </c>
-      <c r="D171" s="8" t="n">
+      <c r="D176" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="E171" s="8" t="n">
+      <c r="E176" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F171" s="4" t="inlineStr">
+      <c r="F176" s="5" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="G171" s="8" t="inlineStr"/>
-      <c r="H171" s="9" t="inlineStr"/>
+      <c r="G176" s="6" t="inlineStr"/>
+      <c r="H176" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12349,7 +12515,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>図表番号を振り、目次の後に図表目次を置くことを提案したい。番号の形（図１-１・表１-１）と、注記ボックスには番号を振らないことを合わせたい。令和8年10月10日に当方で図26点・表95点に番号と表題を付け、図表目次を置いた（北塩原村_図表番号一覧.xlsx）。これに伴う確認３件はＳ-22〜Ｓ-24として同書に立てている</t>
+          <t>図表番号を振り、目次の後に図表目次を置くことを提案したい。番号の形（図１-１・表１-１）と、注記ボックスには番号を振らないことを合わせたい。令和8年10月10日に当方で図26点・表96点に番号と表題を付け、図表目次を置いた（北塩原村_図表番号一覧.xlsx）。これに伴う確認３件はＳ-22〜Ｓ-24として同書に立てている</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>1112×614</t>
+          <t>1114×614</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>1210×638</t>
+          <t>1211×638</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>1046×591</t>
+          <t>1047×591</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -3753,20 +3753,16 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>(234,244,238)</t>
+          <t>(244,184,101)</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -3781,16 +3777,20 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>(244,184,101)</t>
+          <t>(234,244,238)</t>
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>143</v>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -3805,11 +3805,11 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>(178,178,178)</t>
+          <t>(147,147,147)</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="E70" s="8" t="n">
         <v>0</v>
@@ -3857,11 +3857,11 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>(185,185,185)</t>
+          <t>(132,132,132)</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="E72" s="8" t="n">
         <v>0</v>
@@ -3909,11 +3909,11 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>(133,133,133)</t>
+          <t>(183,183,183)</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="E74" s="8" t="n">
         <v>0</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>(212,212,212)</t>
+          <t>(204,204,204)</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>0</v>
@@ -4069,11 +4069,11 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>(136,136,136)</t>
+          <t>(137,137,137)</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E80" s="6" t="n">
         <v>0</v>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>(155,155,155)</t>
+          <t>(158,158,158)</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E89" s="6" t="n">
         <v>0</v>
@@ -4341,14 +4341,14 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>(201,201,201)</t>
+          <t>(233,245,240)</t>
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -4369,20 +4369,16 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>(233,245,240)</t>
+          <t>(53,161,112)</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>241</v>
+        <v>123</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="F91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -4397,16 +4393,20 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>(53,161,112)</t>
+          <t>(216,216,216)</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>123</v>
+        <v>216</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>108</v>
-      </c>
-      <c r="F92" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -4421,11 +4421,11 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>(134,134,134)</t>
+          <t>(137,137,137)</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E93" s="6" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>(176,176,176)</t>
+          <t>(180,180,180)</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E96" s="8" t="n">
         <v>0</v>
@@ -4525,20 +4525,16 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>(223,223,223)</t>
+          <t>(128,196,165)</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -4553,16 +4549,20 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>(128,196,165)</t>
+          <t>(138,138,138)</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="F98" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -4577,11 +4577,11 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>(206,206,206)</t>
+          <t>(223,223,223)</t>
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E99" s="8" t="n">
         <v>0</v>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>(138,138,138)</t>
+          <t>(206,206,206)</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="E100" s="8" t="n">
         <v>0</v>
@@ -4685,14 +4685,14 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>(181,181,181)</t>
+          <t>(234,244,238)</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
@@ -4713,14 +4713,14 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>(234,244,238)</t>
+          <t>(181,181,181)</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -4929,11 +4929,11 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>(100,100,100)</t>
+          <t>(99,99,99)</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E112" s="8" t="n">
         <v>0</v>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>(37,154,100)</t>
+          <t>(37,154,101)</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
@@ -4981,11 +4981,11 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>(221,221,221)</t>
+          <t>(235,235,235)</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E114" s="6" t="n">
         <v>0</v>
@@ -5037,11 +5037,11 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>(129,129,129)</t>
+          <t>(179,179,179)</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="E116" s="6" t="n">
         <v>0</v>
@@ -5065,11 +5065,11 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>(164,164,164)</t>
+          <t>(131,131,131)</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="E117" s="6" t="n">
         <v>0</v>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>(228,228,228)</t>
+          <t>(234,234,234)</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E120" s="8" t="n">
         <v>0</v>
@@ -5173,14 +5173,14 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>(211,206,208)</t>
+          <t>(191,191,191)</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
@@ -5229,11 +5229,11 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>(165,165,165)</t>
+          <t>(140,140,140)</t>
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="E123" s="8" t="n">
         <v>0</v>
@@ -5257,11 +5257,11 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>(217,217,217)</t>
+          <t>(223,223,223)</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E124" s="6" t="n">
         <v>0</v>
@@ -5285,11 +5285,11 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>(227,227,227)</t>
+          <t>(211,211,211)</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="E125" s="6" t="n">
         <v>0</v>
@@ -5313,11 +5313,11 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>(154,154,154)</t>
+          <t>(91,91,91)</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="E126" s="6" t="n">
         <v>0</v>
@@ -5341,11 +5341,11 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>(91,91,91)</t>
+          <t>(154,154,154)</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="E127" s="6" t="n">
         <v>0</v>
@@ -5357,30 +5357,30 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>図26</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>image12.png</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
-        <is>
-          <t>(102,163,218)</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="n">
-        <v>151</v>
-      </c>
-      <c r="E128" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>ほかの系列と同じ濃さになる</t>
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>図25</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>image18.png</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>(131,131,131)</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
         </is>
       </c>
     </row>
@@ -5397,14 +5397,14 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>(222,100,134)</t>
+          <t>(102,163,218)</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
@@ -5425,16 +5425,20 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>(239,181,63)</t>
-        </is>
-      </c>
-      <c r="D130" s="8" t="n">
-        <v>185</v>
+          <t>(222,100,134)</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>140</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>176</v>
-      </c>
-      <c r="F130" s="4" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>ほかの系列と同じ濃さになる</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -5449,14 +5453,14 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>(27,52,97)</t>
+          <t>(239,181,63)</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="F131" s="4" t="inlineStr"/>
     </row>
@@ -5473,40 +5477,40 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
+          <t>(27,52,97)</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="F132" s="4" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>図26</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>image12.png</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
           <t>(210,231,197)</t>
         </is>
       </c>
-      <c r="D132" s="8" t="n">
+      <c r="D133" s="8" t="n">
         <v>221</v>
       </c>
-      <c r="E132" s="8" t="n">
+      <c r="E133" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="F132" s="4" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>図27</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>image23.png</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>(243,183,98)</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="n">
-        <v>191</v>
-      </c>
-      <c r="E133" s="6" t="n">
-        <v>145</v>
-      </c>
-      <c r="F133" s="5" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -5521,20 +5525,16 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>(152,152,152)</t>
+          <t>(243,183,98)</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>グレー（目盛線・軸・網かけ）</t>
-        </is>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -5549,11 +5549,11 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>(218,218,218)</t>
+          <t>(149,149,149)</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>218</v>
+        <v>149</v>
       </c>
       <c r="E135" s="6" t="n">
         <v>0</v>
@@ -5577,11 +5577,11 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>(131,131,131)</t>
+          <t>(218,218,218)</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="E136" s="6" t="n">
         <v>0</v>
@@ -5605,11 +5605,11 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>(228,228,228)</t>
+          <t>(131,131,131)</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>228</v>
+        <v>131</v>
       </c>
       <c r="E137" s="6" t="n">
         <v>0</v>
@@ -5633,16 +5633,20 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>(99,182,144)</t>
+          <t>(228,228,228)</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>83</v>
-      </c>
-      <c r="F138" s="5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>グレー（目盛線・軸・網かけ）</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -5657,14 +5661,14 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>(255,246,231)</t>
+          <t>(99,182,144)</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="F139" s="5" t="inlineStr"/>
     </row>

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表171点（データ表96・注記ボックス75）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表172点（データ表96・注記ボックス76）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表171点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表172点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表171点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表172点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+          <t>【村へ確認（Ｍ-131）】①ＮＥＴ１１９の本村における登録者数と登録勧奨の実績（令和６年度・令和７年度）、②村の窓口及び</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9244,27 +9244,27 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr"/>
-      <c r="H103" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9278,22 +9278,22 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr"/>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -9332,7 +9332,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -9346,23 +9346,27 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9376,22 +9380,18 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H107" s="8" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -9430,7 +9430,7 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -9444,23 +9444,27 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9474,27 +9478,23 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9508,23 +9508,27 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9538,22 +9542,18 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr"/>
+          <t>照会する事項 / 確保できる量との関係</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -9592,7 +9592,7 @@
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9606,23 +9606,27 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="9" t="inlineStr"/>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9636,14 +9640,14 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
@@ -9652,7 +9656,7 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9666,27 +9670,23 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E116" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9700,21 +9700,17 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
       <c r="H117" s="8" t="inlineStr">
         <is>
           <t>あり</t>
@@ -9745,7 +9741,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｓ-38）】福島県における災害拠点精神科病院の指定の状況（指定の有無、指定された病院の名称及び所在）と、ＤＰ</t>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -9753,12 +9749,16 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H118" s="6" t="inlineStr"/>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9772,23 +9772,27 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr"/>
-      <c r="H119" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｓ-38）】福島県における災害拠点精神科病院の指定の状況（指定の有無、指定された病院の名称及び所在）と、ＤＰ</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9802,27 +9806,23 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr"/>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9836,23 +9836,27 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9866,27 +9870,23 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr"/>
+          <t>把握する事項 / 見込量への影響</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="9" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9900,23 +9900,27 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9930,27 +9934,23 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr"/>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="9" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9964,23 +9964,27 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9994,27 +9998,23 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -10028,23 +10028,27 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10058,22 +10062,18 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-129）】本村の救急搬送を担う消防本部と、冬季における搬送に要する時間（平時との差）を確かめてください。</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="inlineStr"/>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
+          <t>【村へ確認（Ｍ-129）】本村の救急搬送を担う消防本部と、冬季における搬送に要する時間（平時との差）を確かめてください。</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -10146,7 +10146,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -10156,31 +10156,31 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10201,16 +10201,20 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="9" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10224,22 +10228,18 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H133" s="8" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -10278,7 +10278,7 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10292,23 +10292,27 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10322,14 +10326,14 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
@@ -10338,7 +10342,7 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10352,22 +10356,18 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="inlineStr"/>
+          <t>事項 / 本村の取扱い</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="9" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10420,23 +10420,27 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10446,18 +10450,18 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr"/>
@@ -10466,7 +10470,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10480,14 +10484,14 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr"/>
@@ -10496,7 +10500,7 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10510,27 +10514,23 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="inlineStr"/>
+          <t>確認する事項 / 見込量への反映</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="9" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10544,23 +10544,27 @@
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr"/>
-      <c r="H143" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10574,27 +10578,23 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H144" s="6" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="9" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10608,23 +10608,27 @@
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr"/>
-      <c r="H145" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10638,14 +10642,14 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E146" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
@@ -10654,7 +10658,7 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10668,14 +10672,14 @@
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr"/>
@@ -10684,7 +10688,7 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10698,27 +10702,23 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H148" s="6" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="9" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10732,27 +10732,27 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr"/>
-      <c r="H149" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10766,27 +10766,27 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H150" s="6" t="inlineStr"/>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10796,27 +10796,31 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr"/>
-      <c r="H151" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10830,22 +10834,18 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H152" s="6" t="inlineStr"/>
+          <t>分野 / 関係機関 / 連携の内容</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr"/>
+      <c r="H152" s="9" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
@@ -10884,7 +10884,7 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -10894,31 +10894,31 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E154" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -10932,14 +10932,14 @@
         </is>
       </c>
       <c r="D155" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E155" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E155" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
@@ -10952,7 +10952,7 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -10966,14 +10966,14 @@
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E156" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr"/>
@@ -10986,7 +10986,7 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -11000,61 +11000,61 @@
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
-        </is>
-      </c>
-      <c r="G157" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H157" s="8" t="inlineStr"/>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr"/>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E158" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -11068,14 +11068,14 @@
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E159" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr"/>
@@ -11088,7 +11088,7 @@
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -11102,14 +11102,14 @@
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr"/>
@@ -11122,7 +11122,7 @@
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -11132,31 +11132,31 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G161" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H161" s="8" t="inlineStr"/>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G161" s="8" t="inlineStr"/>
+      <c r="H161" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -11170,23 +11170,27 @@
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E162" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -11196,26 +11200,22 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D163" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
-        </is>
-      </c>
-      <c r="G163" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H163" s="8" t="inlineStr"/>
+          <t>指標 / 何を数えるか</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr"/>
+      <c r="H163" s="9" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>５　地域における権利擁護の支援の</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -11254,37 +11254,41 @@
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>５　地域における権利擁護の支援の</t>
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
-        </is>
-      </c>
-      <c r="G165" s="8" t="inlineStr"/>
-      <c r="H165" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H165" s="8" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -11294,18 +11298,18 @@
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E166" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr"/>
@@ -11314,7 +11318,7 @@
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -11324,18 +11328,18 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E167" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>総合振興計画の位置づけ / 内容</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr"/>
@@ -11344,7 +11348,7 @@
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -11358,27 +11362,23 @@
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
-        </is>
-      </c>
-      <c r="G168" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H168" s="6" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr"/>
+      <c r="H168" s="9" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -11388,27 +11388,31 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D169" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G169" s="8" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>表７-5</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -11418,18 +11422,18 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>５　第８次福島県医療計画との連携</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D170" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E170" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>医療計画の分野 / 県の主な内容 / 本計画での連携</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr"/>
@@ -11438,7 +11442,7 @@
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-5</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -11452,22 +11456,18 @@
         </is>
       </c>
       <c r="D171" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E171" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-129）】第８次福島県医療計画のうち第３章（医療圏と基準病床数）及び第10章（医療機関相互の連携、医療Ｄ</t>
-        </is>
-      </c>
-      <c r="G171" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H171" s="8" t="inlineStr"/>
+          <t>医療計画の分野 / 県の主な内容 / 本計画での連携</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr"/>
+      <c r="H171" s="9" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+          <t>【村へ確認（Ｍ-129）】第８次福島県医療計画のうち第３章（医療圏と基準病床数）及び第10章（医療機関相互の連携、医療Ｄ</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -11506,37 +11506,41 @@
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>５　第８次福島県医療計画との連携</t>
         </is>
       </c>
       <c r="D173" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E173" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G173" s="8" t="inlineStr"/>
-      <c r="H173" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H173" s="8" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表８-1</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -11546,18 +11550,18 @@
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>２　北塩原村障がい者自立支援協議</t>
         </is>
       </c>
       <c r="D174" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E174" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr"/>
@@ -11566,7 +11570,7 @@
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表８-2</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -11576,18 +11580,18 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>３　計画の策定経過</t>
         </is>
       </c>
       <c r="D175" s="8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E175" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>年月日 / 内容</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr"/>
@@ -11596,7 +11600,7 @@
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>表８-4</t>
+          <t>表８-3</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
@@ -11606,22 +11610,52 @@
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>５　用語解説</t>
+          <t>４　近年の障がい者施策の動向</t>
         </is>
       </c>
       <c r="D176" s="6" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E176" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>用語 / 説明</t>
+          <t>年 / 主な動向</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr"/>
       <c r="H176" s="9" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>表８-4</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>５　用語解説</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>用語 / 説明</t>
+        </is>
+      </c>
+      <c r="G177" s="8" t="inlineStr"/>
+      <c r="H177" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -7257,7 +7257,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-23）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
+          <t>【村へ確認（Ｍ-94）】施設入所者４人について、上表の６項目のうち現時点で確認できている事項を教えてください。匿名の整理</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-6）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の考</t>
+          <t>【県へ確認（Ｍ-99）】福島県の第８期障がい福祉計画における基盤整備量（利用者数）の算定値と、市町村がこれを勘案する際の</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-27）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
+          <t>【村へ確認（Ｍ-93）】１年以上入院している方について、退院後の住まい（グループホーム・一般住宅・家族との同居）、日中活</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表172点（データ表96・注記ボックス76）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表177点（データ表96・注記ボックス81）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表172点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表177点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表172点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表177点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8608,7 +8608,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>表５-5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -8622,23 +8622,27 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-136・Ｍ-137）】第５章の実績の表（表５-４から表５-14まで及び表５-29）の令和６・７年度は、「</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>表５-6</t>
+          <t>表５-5</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -8652,14 +8656,14 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>確かめる側 / 確かめる事項</t>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr"/>
@@ -8668,7 +8672,7 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-6</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -8682,27 +8686,23 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr"/>
+          <t>確かめる側 / 確かめる事項</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>表５-7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -8716,27 +8716,27 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-87・Ｍ-88）】上表の本人の側の各事項に該当する方の人数と、供給の側の事業所・有資格者の状況を確認しま</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>表５-8</t>
+          <t>表５-7</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -8757,16 +8757,20 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>表５-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -8780,27 +8784,27 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-136・Ｍ-137）】生活介護の利用者のうち４人は、台帳の利用先から、施設入所支援をあわせて利用している</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-8</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -8814,31 +8818,23 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>表５-10</t>
+          <t>表５-9</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -8852,14 +8848,14 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 現在の人数 / 令和９年度 / 令和10年度</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
@@ -8872,7 +8868,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>表５-11</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -8886,23 +8882,31 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-22）】上表の人数を確認してください。強度行動障害は障害支援区分の認定調査の行動関連項目の合計点（10点</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-10</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -8916,27 +8920,27 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-11</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -8950,27 +8954,23 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>表５-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -8984,27 +8984,27 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-139）】共同生活援助の利用者は、令和８年度の途中までの平均で月11.7人であり、表５-11の見込量（令</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>表５-13</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -9018,18 +9018,22 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-72）】村内の高齢者向けの共同生活の住まいの名称、定員、運営主体及び認知症対応型共同生活介護の指定の有無</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -9055,7 +9059,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
+          <t>【村へ確認（Ｍ-109）】施設入所支援の利用者４人について、上に述べた継続入所者（旧指定知的障害児施設等からの引き続きの</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -9068,7 +9072,7 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>表５-14</t>
+          <t>表５-12</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -9082,7 +9086,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E98" s="6" t="n">
         <v>5</v>
@@ -9102,7 +9106,7 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>表５-15</t>
+          <t>表５-13</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -9116,7 +9120,7 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E99" s="8" t="n">
         <v>5</v>
@@ -9132,7 +9136,7 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>表５-16</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -9146,23 +9150,27 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-115）】計画相談支援について、①本村を担当する相談支援専門員の人数（事業所別、兼務を含む）、②令和６年</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-14</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -9176,22 +9184,22 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和６年度 / 令和７年度</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -9206,7 +9214,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
@@ -9217,7 +9225,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-131）】①ＮＥＴ１１９の本村における登録者数と登録勧奨の実績（令和６年度・令和７年度）、②村の窓口及び</t>
+          <t>【村へ確認（Ｍ-137）】障がい児のサービスは、台帳のご提供がなかったため、令和８年度を「―」としています。児童発達支援</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -9230,7 +9238,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-15</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -9240,31 +9248,27 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="inlineStr"/>
+          <t>サービス種別 / 単位 / 令和９年度 / 令和10年度</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>表５-17</t>
+          <t>表５-16</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -9274,7 +9278,7 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
@@ -9285,15 +9289,11 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+          <t>サービス / 本村の設置数 / 確保の経路と確かめること</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>２　必要な見込量の確保のための方</t>
+          <t>１　障がい福祉サービスの見込量</t>
         </is>
       </c>
       <c r="D105" s="8" t="n">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
+          <t>【村へ確認（Ｍ-99・Ｍ-102）】上表の確保の経路について、会津圏域の最新の指定の状況と、本村の住民が実際に利用できる</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
+          <t>【村へ確認（Ｍ-131）】①ＮＥＴ１１９の本村における登録者数と登録勧奨の実績（令和６年度・令和７年度）、②村の窓口及び</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>表５-18</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -9380,23 +9380,27 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ４町村で揃える定義</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr"/>
-      <c r="H107" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-99）】福島県の高次脳機能障害者支援センター及び支援コーディネーターの設置の状況、会津圏域における相談の</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-17</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -9410,22 +9414,22 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr"/>
+          <t>区分 / 施行令での扱い / 相談をつなぐ先</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -9451,7 +9455,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
+          <t>【村へ確認（Ｍ-107）】高次脳機能障害者支援法の施行に伴う県の体制について、支援センターの指定の状況、地域協議会に村が</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -9464,7 +9468,7 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>表５-19</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -9478,23 +9482,27 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-18</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -9508,27 +9516,23 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="inlineStr"/>
+          <t>記録する事項 / ４町村で揃える定義</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>表５-20</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -9542,18 +9546,22 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>照会する事項 / 確保できる量との関係</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-98）】上表の定義について、猪苗代町、磐梯町及び湯川村との協議の場で合意が得られるかを確認してください。</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -9579,7 +9587,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+          <t>【村へ確認（Ｍ-106）】村内の障がい福祉サービスの３事業所及び介護保険の訪問介護・通所介護の事業所について、現在の指定</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -9592,7 +9600,7 @@
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-19</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -9606,27 +9614,23 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr"/>
+          <t>場面 / まず確かめる一般の子育て施策 / 足りない場合の障がい福祉</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>表５-21</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -9640,23 +9644,27 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>場面 / 想定される事態 / 働く仕組み</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-74・Ｍ-75）】子育て短期支援事業の要件（対象年齢、利用日数の上限、利用者負担）と委託先、障がい特性・</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>表５-22</t>
+          <t>表５-20</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -9670,14 +9678,14 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E116" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>備える事項 / 本村の取組み</t>
+          <t>照会する事項 / 確保できる量との関係</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr"/>
@@ -9686,7 +9694,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>表５-23</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9700,22 +9708,22 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>確かめること / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-24）】本村の住民が利用している村外の事業所の一覧（サービス種別・事業所名・所在地）をいただければ、上表</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -9741,7 +9749,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+          <t>【県へ確認（Ｓ-11）】特定地域サービス等について、国が定める対象地域の客観的な基準の内容と示される時期、県が定める区域</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -9749,16 +9757,12 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-21</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9772,27 +9776,23 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｓ-38）】福島県における災害拠点精神科病院の指定の状況（指定の有無、指定された病院の名称及び所在）と、ＤＰ</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H119" s="8" t="inlineStr"/>
+          <t>場面 / 想定される事態 / 働く仕組み</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>表５-24</t>
+          <t>表５-22</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -9806,14 +9806,14 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>段階 / 本村の取組み / 用いるサービス等</t>
+          <t>備える事項 / 本村の取組み</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr"/>
@@ -9822,7 +9822,7 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-23</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9836,27 +9836,27 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="inlineStr"/>
+          <t>確かめること / 確かめ方</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>表５-25</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -9870,18 +9870,26 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>把握する事項 / 見込量への影響</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-83）】個別避難計画の対象となる方への情報の伝え方、戸別受信機の配布の有無と配布数、及び障がいの特性に応</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -9907,7 +9915,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
+          <t>【村へ確認（Ｓ-38）】福島県における災害拠点精神科病院の指定の状況（指定の有無、指定された病院の名称及び所在）と、ＤＰ</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
@@ -9920,7 +9928,7 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>表５-26</t>
+          <t>表５-24</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -9934,14 +9942,14 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E124" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>段階 / 確かめること / 確かめた後にすること</t>
+          <t>段階 / 本村の取組み / 用いるサービス等</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr"/>
@@ -9971,7 +9979,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
+          <t>【村へ確認（Ｍ-79）】人権相談の村での受付の経路、村が把握している相談件数（令和６・７年度）及びうち障がいに関するもの</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
@@ -9984,7 +9992,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>表５-27</t>
+          <t>表５-25</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -9998,14 +10006,14 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E126" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>記録する事項 / 記録の仕方</t>
+          <t>把握する事項 / 見込量への影響</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr"/>
@@ -10035,7 +10043,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
+          <t>【村へ確認（Ｍ-25）】村内３事業所及び本村の住民が利用している村外の主な事業所について、上表の事項を自立支援協議会の場</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
@@ -10048,7 +10056,7 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>表５-28</t>
+          <t>表５-26</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -10062,14 +10070,14 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E128" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>場面 / 主な医療資源 / 本計画での扱い</t>
+          <t>段階 / 確かめること / 確かめた後にすること</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr"/>
@@ -10099,7 +10107,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-129）】本村の救急搬送を担う消防本部と、冬季における搬送に要する時間（平時との差）を確かめてください。</t>
+          <t>【村へ確認（Ｍ-49・Ｍ-65）】重度心身障害者医療費の受給の対象となる方のみで構成される世帯の利用件数と、受給の対象と</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr">
@@ -10112,7 +10120,7 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-27</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -10126,22 +10134,18 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H130" s="6" t="inlineStr"/>
+          <t>記録する事項 / 記録の仕方</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -10167,7 +10171,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
+          <t>【村へ確認（Ｍ-85）】上表の令和６年度から令和８年度までの実績を確認します。記録がない場合は「記録していない」ことをそ</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr">
@@ -10180,7 +10184,7 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>表５-29</t>
+          <t>表５-28</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -10190,31 +10194,27 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
+          <t>場面 / 主な医療資源 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H132" s="9" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>表５-30</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -10224,22 +10224,26 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-129）】本村の救急搬送を担う消防本部と、冬季における搬送に要する時間（平時との差）を確かめてください。</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -10254,7 +10258,7 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
@@ -10265,7 +10269,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
+          <t>【村へ確認（Ｍ-99）】福島県医療的ケア児支援センター及び高次脳機能障害の専門相談について、村から案内できる窓口の名称、</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -10288,7 +10292,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>３　地域生活支援事業の実施目標</t>
+          <t>２　必要な見込量の確保のための方</t>
         </is>
       </c>
       <c r="D135" s="8" t="n">
@@ -10299,7 +10303,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
+          <t>【村へ確認（Ｍ-82・Ｍ-84）】救急電話相談について聴覚障がい又は言語障がいのある方が利用できる代替の手段（ファクシミ</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr">
@@ -10312,7 +10316,7 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>表５-31</t>
+          <t>表５-29</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -10326,23 +10330,27 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E136" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
+          <t>サービスの種類 / 令和６年度 / 令和７年度 / 令和８年度</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="9" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>表５-32</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10356,23 +10364,27 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>事項 / 本村の取扱い</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-136・Ｍ-138）】成年後見制度利用支援事業は、資料２－３では令和６・７年度とも利用が０人ですが、表６</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-30</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -10386,22 +10398,18 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr"/>
+          <t>サービスの種類 / 令和９年度 / 令和10年度 / 令和11年度</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="9" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
@@ -10416,7 +10424,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D139" s="8" t="n">
@@ -10427,7 +10435,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+          <t>【村へ確認（Ｍ-59・Ｍ-60）】公式動画の年度別の公開本数と再生回数、手話出前講座の年度別の開催団体数・参加者数・団体</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
@@ -10440,7 +10448,7 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>表５-33</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -10450,27 +10458,31 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>４　事業提供体制の確保のための方</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-114）】成年後見制度法人後見支援事業について、上の第一と第二のいずれで整理するかをご判断ください。第一</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>表５-34</t>
+          <t>表５-31</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10480,7 +10492,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
@@ -10491,7 +10503,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
+          <t>実績がない理由 / 確かめ方 / 確かめた後の扱い</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr"/>
@@ -10500,7 +10512,7 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>表５-35</t>
+          <t>表５-32</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -10510,18 +10522,18 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E142" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>確認する事項 / 見込量への反映</t>
+          <t>事項 / 本村の取扱い</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr"/>
@@ -10540,7 +10552,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>３　地域生活支援事業の実施目標</t>
         </is>
       </c>
       <c r="D143" s="8" t="n">
@@ -10551,7 +10563,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+          <t>【村へ確認】利用者負担の割合と負担上限月額、委託先、申請の手続について、本村の実際の取扱いを確認してください。上表は一般</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
@@ -10564,7 +10576,7 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>表５-36</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -10574,27 +10586,31 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>区分 / 該当するサービス / 扱い</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-61・Ｍ-62・Ｍ-63）】ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳の年度別の配布数と、障が</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-33</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10604,31 +10620,27 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>５　年齢到達に伴うサービスの移行</t>
+          <t>４　事業提供体制の確保のための方</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="inlineStr"/>
+          <t>道具 / 伝える場面 / 伝える相手 / 持ち方・置き方</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="9" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>表５-37</t>
+          <t>表５-34</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -10642,14 +10654,14 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+          <t>年齢 / 制度上の内容 / 本計画での扱い</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr"/>
@@ -10658,7 +10670,7 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>表５-38</t>
+          <t>表５-35</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10672,14 +10684,14 @@
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E147" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>確認する事項 / 確認の内容</t>
+          <t>確認する事項 / 見込量への反映</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr"/>
@@ -10688,7 +10700,7 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>表５-39</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -10702,23 +10714,27 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>時期 / 行うこと / 担当</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-21）】令和９～11年度に特別支援学校又は特別支援学級を卒業する予定の方について、卒業年度、在籍校、進路</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-36</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10732,27 +10748,23 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H149" s="8" t="inlineStr"/>
+          <t>区分 / 該当するサービス / 扱い</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr"/>
+      <c r="H149" s="9" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>表５-40</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -10766,27 +10778,27 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-15・Ｍ-20）】令和９～11年度に18歳、40歳、65歳に到達する利用者について、到達年度、現在利用し</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-37</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -10800,27 +10812,23 @@
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H151" s="8" t="inlineStr"/>
+          <t>いま利用している事業所の指定の形 / 65歳に達した後の続け方</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr"/>
+      <c r="H151" s="9" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>表５-41</t>
+          <t>表５-38</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -10830,18 +10838,18 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>分野 / 関係機関 / 連携の内容</t>
+          <t>確認する事項 / 確認の内容</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr"/>
@@ -10850,7 +10858,7 @@
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-39</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -10860,26 +10868,22 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H153" s="8" t="inlineStr"/>
+          <t>時期 / 行うこと / 担当</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr"/>
+      <c r="H153" s="9" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -10894,7 +10898,7 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>６　関係機関との連携</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
@@ -10905,7 +10909,7 @@
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+          <t>【村へ確認（Ｍ-71・Ｍ-81）】高齢者福祉の各事業について障がいのある方が対象となるかと利用実績、並びに地域包括支援セ</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
@@ -10918,7 +10922,7 @@
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>表５-42</t>
+          <t>表５-40</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -10928,18 +10932,18 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
+          <t>地域支援事業の区分 / 主な事業 / 対象者の定め</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr"/>
@@ -10952,7 +10956,7 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>表５-43</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -10962,31 +10966,31 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>５　年齢到達に伴うサービスの移行</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E156" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>区分 / 金額 / 構成比</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr"/>
-      <c r="H156" s="6" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認（Ｍ-108）】本村が実施している地域支援事業（任意事業を含む）の一覧と、各事業の要綱における対象者の定めを確</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>表５-44</t>
+          <t>表５-41</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -10996,26 +11000,22 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E157" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+          <t>分野 / 関係機関 / 連携の内容</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr"/>
-      <c r="H157" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+      <c r="H157" s="9" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>７　障がい福祉サービス等に係る費</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+          <t>【村へ確認（Ｍ-80）】罪を犯し矯正施設を退所した障がいのある方について村が相談を受けた実績、福島県地域生活定着支援セン</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -11054,62 +11054,62 @@
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>表６-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>６　関係機関との連携</t>
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
-        </is>
-      </c>
-      <c r="G159" s="8" t="inlineStr"/>
-      <c r="H159" s="8" t="inlineStr">
-        <is>
-          <t>あり</t>
-        </is>
-      </c>
+          <t>【村へ確認】就労関係機関（会津若松公共職業安定所、福島県障害者職業センター、障害者就業・生活支援センター）との連携の実態</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H159" s="8" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>表６-2</t>
+          <t>表５-42</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+          <t>年度 / 介護給付費等 / 障害児給付費 / 計</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr"/>
@@ -11122,28 +11122,28 @@
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>表６-3</t>
+          <t>表５-43</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>１　現状と課題</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
+          <t>区分 / 金額 / 構成比</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr"/>
@@ -11156,71 +11156,75 @@
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表５-44</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E162" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H162" s="6" t="inlineStr"/>
+          <t>サービス / 給付費（構成比） / 計画上の位置づけ</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t>表６-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>第６章　成年後見制度</t>
+          <t>第５章　障がい福祉サ</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>３　今後の取組み</t>
+          <t>７　障がい福祉サービス等に係る費</t>
         </is>
       </c>
       <c r="D163" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>指標 / 何を数えるか</t>
-        </is>
-      </c>
-      <c r="G163" s="8" t="inlineStr"/>
-      <c r="H163" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-37）】上表の財源構成は、給付費に法定負担割合を乗じた試算です。訪問系サービス等で国庫負担基準額を超過し</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-1</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
@@ -11230,31 +11234,31 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>４　制度の見直しへの対応</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E164" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
-        </is>
-      </c>
-      <c r="G164" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H164" s="6" t="inlineStr"/>
+          <t>年度 / 高齢化率 / 年度 / 高齢化率</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr"/>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表６-2</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -11264,101 +11268,109 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>５　地域における権利擁護の支援の</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
-        </is>
-      </c>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H165" s="8" t="inlineStr"/>
+          <t>年度 / 精神障がい者数（※１） / 知的障がい者数（※２） / 計</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr"/>
+      <c r="H165" s="8" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>表７-1</t>
+          <t>表６-3</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>１　第３次健康21・北塩原村グッ</t>
+          <t>１　現状と課題</t>
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E166" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
+          <t>区分 / 令和５年度 / 令和６年度 / 令和７年度</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr"/>
-      <c r="H166" s="9" t="inlineStr"/>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>表７-2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>２　北塩原村第五次総合振興計画と</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>総合振興計画の位置づけ / 内容</t>
-        </is>
-      </c>
-      <c r="G167" s="8" t="inlineStr"/>
-      <c r="H167" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-78）】「わたしの思いノート」の村での配布の有無と配布場所、年度別の配布数、及び障がいのある方・家族への</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H167" s="8" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>表７-3</t>
+          <t>表６-4</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>３　今後の取組み</t>
         </is>
       </c>
       <c r="D168" s="6" t="n">
@@ -11369,7 +11381,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>事項 / 両計画での扱い</t>
+          <t>指標 / 何を数えるか</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr"/>
@@ -11383,12 +11395,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>３　北塩原村高齢者福祉計画・介護</t>
+          <t>４　制度の見直しへの対応</t>
         </is>
       </c>
       <c r="D169" s="8" t="n">
@@ -11399,7 +11411,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+          <t>【村へ確認（Ｍ-116）】成年後見制度の見直しに伴い、①村長申立ての事務の流れ、②成年後見制度利用支援事業の助成の対象（</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
@@ -11412,37 +11424,41 @@
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>表７-4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>第７章　他計画との連</t>
+          <t>第６章　成年後見制度</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>４　北塩原村こども・子育て計画と</t>
+          <t>５　地域における権利擁護の支援の</t>
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E170" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>確かめる事項 / 確かめ方</t>
-        </is>
-      </c>
-      <c r="G170" s="6" t="inlineStr"/>
-      <c r="H170" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-117）】会津権利擁護・成年後見センターについて、①新しい制度における地域権利擁護相談支援センターとして</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>表７-5</t>
+          <t>表７-1</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -11452,18 +11468,18 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>５　第８次福島県医療計画との連携</t>
+          <t>１　第３次健康21・北塩原村グッ</t>
         </is>
       </c>
       <c r="D171" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E171" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>医療計画の分野 / 県の主な内容 / 本計画での連携</t>
+          <t>項目 / 健康21・グッドヘルスプラン / 本計画（第４次障がい者計画）</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr"/>
@@ -11472,7 +11488,7 @@
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-2</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -11482,31 +11498,27 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>５　第８次福島県医療計画との連携</t>
+          <t>２　北塩原村第五次総合振興計画と</t>
         </is>
       </c>
       <c r="D172" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E172" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-129）】第８次福島県医療計画のうち第３章（医療圏と基準病床数）及び第10章（医療機関相互の連携、医療Ｄ</t>
-        </is>
-      </c>
-      <c r="G172" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H172" s="6" t="inlineStr"/>
+          <t>総合振興計画の位置づけ / 内容</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr"/>
+      <c r="H172" s="9" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表７-3</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -11516,82 +11528,82 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>５　第８次福島県医療計画との連携</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D173" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E173" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
-        </is>
-      </c>
-      <c r="G173" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H173" s="8" t="inlineStr"/>
+          <t>事項 / 両計画での扱い</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr"/>
+      <c r="H173" s="9" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>表８-1</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>２　北塩原村障がい者自立支援協議</t>
+          <t>３　北塩原村高齢者福祉計画・介護</t>
         </is>
       </c>
       <c r="D174" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E174" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
-        </is>
-      </c>
-      <c r="G174" s="6" t="inlineStr"/>
-      <c r="H174" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-13・Ｍ-14・Ｍ-15）】施設入所支援４人の支給決定の内容（生活介護との同時支給決定か）、介護保険の第</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>表８-2</t>
+          <t>表７-4</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>３　計画の策定経過</t>
+          <t>４　北塩原村こども・子育て計画と</t>
         </is>
       </c>
       <c r="D175" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E175" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>年月日 / 内容</t>
+          <t>確かめる事項 / 確かめ方</t>
         </is>
       </c>
       <c r="G175" s="8" t="inlineStr"/>
@@ -11600,28 +11612,28 @@
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>表８-3</t>
+          <t>表７-5</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>第８章　資料編</t>
+          <t>第７章　他計画との連</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>４　近年の障がい者施策の動向</t>
+          <t>５　第８次福島県医療計画との連携</t>
         </is>
       </c>
       <c r="D176" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E176" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>年 / 主な動向</t>
+          <t>医療計画の分野 / 県の主な内容 / 本計画での連携</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr"/>
@@ -11630,32 +11642,190 @@
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
         <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>５　第８次福島県医療計画との連携</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-129）】第８次福島県医療計画のうち第３章（医療圏と基準病床数）及び第10章（医療機関相互の連携、医療Ｄ</t>
+        </is>
+      </c>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H177" s="8" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>第７章　他計画との連</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>５　第８次福島県医療計画との連携</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>【村へ確認（Ｍ-70）】本節で用いた計画名は村ホームページの記載によります。こども基本法第10条第２項の市町村こども計画</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>表８-1</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>２　北塩原村障がい者自立支援協議</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>区　分 / 氏　名 / 所　属 ・ 役　職 / 備考</t>
+        </is>
+      </c>
+      <c r="G179" s="8" t="inlineStr"/>
+      <c r="H179" s="9" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>表８-2</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>３　計画の策定経過</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E180" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>年月日 / 内容</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr"/>
+      <c r="H180" s="9" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>表８-3</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>第８章　資料編</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>４　近年の障がい者施策の動向</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>年 / 主な動向</t>
+        </is>
+      </c>
+      <c r="G181" s="8" t="inlineStr"/>
+      <c r="H181" s="9" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
           <t>表８-4</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B182" s="5" t="inlineStr">
         <is>
           <t>第８章　資料編</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C182" s="5" t="inlineStr">
         <is>
           <t>５　用語解説</t>
         </is>
       </c>
-      <c r="D177" s="8" t="n">
+      <c r="D182" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="E177" s="8" t="n">
+      <c r="E182" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr">
         <is>
           <t>用語 / 説明</t>
         </is>
       </c>
-      <c r="G177" s="8" t="inlineStr"/>
-      <c r="H177" s="9" t="inlineStr"/>
+      <c r="G182" s="6" t="inlineStr"/>
+      <c r="H182" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/output/北塩原村_図表一覧.xlsx
+++ b/output/北塩原村_図表一覧.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>図29点／表177点（データ表96・注記ボックス81）。図表番号は0件、図表目次もない</t>
+          <t>図29点／表179点（データ表96・注記ボックス83）。図表番号は0件、図表目次もない</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>表177点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
+          <t>表179点のうち、直後に出所らしき行があるのは28点のみ。数値の根拠を後から追えない。庁議・議会・パブリックコメントで必ず問われる</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>図29点／表177点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
+          <t>図29点／表179点／規約9件／グラフ候補6件／足りない図7件／確認事項4件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6020,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7564,7 +7564,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>表４-8</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -7578,23 +7578,27 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-140）】令和６年度末の就労定着支援事業の利用者数は、資料２－３と村の給付の台帳のいずれでも０人であるた</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-8</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -7608,22 +7612,18 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr"/>
+          <t>事業種別 / 令和６年度実績 / 国の基準 / 【目標値】令和11年度</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+          <t>【村へ確認】上表の内訳は、本村の令和６年度の実績が０人であることを前提に、一般就労への移行者１人を就労移行支援事業からの</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>表４-9</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -7676,23 +7676,27 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr"/>
-      <c r="H55" s="9" t="inlineStr"/>
+          <t>≪国の基本指針≫ ① 児童発達支援センター等における４つの中核機能の確保：各市町村又は圏域 　（ⅰ）幅広い高度な専門性に</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>表４-9</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7706,22 +7710,18 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>注記</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+          <t>項目 / 現状 （令和８年度見込み） / 目標値 （令和11年度末）</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-120）】医療的ケアについて、①村内及び圏域に喀痰吸引等の研修を修了して認定を受けた方がいるか（人数、所</t>
+          <t>【村へ確認（Ｍ-98・Ｍ-100）】協議の場の連携単位、及び医療的ケア児等コーディネーターとして数えている方の所属・配置</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
+          <t>【村へ確認（Ｍ-120）】医療的ケアについて、①村内及び圏域に喀痰吸引等の研修を修了して認定を受けた方がいるか（人数、所</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>【医療的ケア者の数え方】基本指針の改正案は、医療的ケア者を二つに分けて定めています。一つは、日常生活及び社会生活を営むた</t>
+          <t>【村へ確認（Ｍ-26）】18歳以上で恒常的に医療的ケアを受けている方（医療的ケア者）と、重症心身障害の状態にある成人の方</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>【村へ確認（Ｍ-126）】①県の医療的ケア児等支援地域協議会の設置の時期と、本村が参画できるかどうか。②本村が設ける協議</t>
+          <t>【医療的ケア者の数え方】基本指針の改正案は、医療的ケア者を二つに分けて定めています。一つは、日常生活及び社会生活を営むた</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -7862,7 +7862,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>表４-10</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -7876,23 +7876,27 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>記録する事項 / ねらい</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr"/>
+          <t>【村へ確認（Ｍ-126）】①県の医療的ケア児等支援地域協議会の設置の時期と、本村が参画できるかどうか。②本村が設ける協議</t>
+      